--- a/VerveStacks_CHN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_CHN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7882D6F2-6ECC-46B7-812A-994BA2946D53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AEDD55B6-E9E5-4EFF-8EA5-4347CBF12A62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5520" uniqueCount="1273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5522" uniqueCount="1273">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -733,18 +733,18 @@
     <t>solar resource -- CF class spv-CHN_29 -- cost class 5</t>
   </si>
   <si>
+    <t>e_spv-CHN_29_c4</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-CHN_29 -- cost class 4</t>
+  </si>
+  <si>
     <t>e_spv-CHN_29_c2</t>
   </si>
   <si>
     <t>solar resource -- CF class spv-CHN_29 -- cost class 2</t>
   </si>
   <si>
-    <t>e_spv-CHN_29_c4</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-CHN_29 -- cost class 4</t>
-  </si>
-  <si>
     <t>e_spv-CHN_28_c3</t>
   </si>
   <si>
@@ -973,18 +973,18 @@
     <t>solar resource -- CF class spv-CHN_21 -- cost class 3</t>
   </si>
   <si>
+    <t>e_spv-CHN_21_c4</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-CHN_21 -- cost class 4</t>
+  </si>
+  <si>
     <t>e_spv-CHN_21_c5</t>
   </si>
   <si>
     <t>solar resource -- CF class spv-CHN_21 -- cost class 5</t>
   </si>
   <si>
-    <t>e_spv-CHN_21_c4</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-CHN_21 -- cost class 4</t>
-  </si>
-  <si>
     <t>e_spv-CHN_20_c4</t>
   </si>
   <si>
@@ -1135,18 +1135,18 @@
     <t>solar resource -- CF class spv-CHN_16 -- cost class 5</t>
   </si>
   <si>
+    <t>e_spv-CHN_15_c4</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-CHN_15 -- cost class 4</t>
+  </si>
+  <si>
     <t>e_spv-CHN_15_c1</t>
   </si>
   <si>
     <t>solar resource -- CF class spv-CHN_15 -- cost class 1</t>
   </si>
   <si>
-    <t>e_spv-CHN_15_c4</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-CHN_15 -- cost class 4</t>
-  </si>
-  <si>
     <t>e_spv-CHN_15_c5</t>
   </si>
   <si>
@@ -1183,18 +1183,18 @@
     <t>solar resource -- CF class spv-CHN_14 -- cost class 3</t>
   </si>
   <si>
+    <t>e_spv-CHN_14_c5</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-CHN_14 -- cost class 5</t>
+  </si>
+  <si>
     <t>e_spv-CHN_14_c4</t>
   </si>
   <si>
     <t>solar resource -- CF class spv-CHN_14 -- cost class 4</t>
   </si>
   <si>
-    <t>e_spv-CHN_14_c5</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-CHN_14 -- cost class 5</t>
-  </si>
-  <si>
     <t>comm-out</t>
   </si>
   <si>
@@ -1366,18 +1366,18 @@
     <t>onshore wind resource -- CF class won-CHN_51 -- cost class 2</t>
   </si>
   <si>
+    <t>e_won-CHN_50_c5</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-CHN_50 -- cost class 5</t>
+  </si>
+  <si>
     <t>e_won-CHN_50_c4</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-CHN_50 -- cost class 4</t>
   </si>
   <si>
-    <t>e_won-CHN_50_c5</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-CHN_50 -- cost class 5</t>
-  </si>
-  <si>
     <t>e_won-CHN_50_c1</t>
   </si>
   <si>
@@ -1396,18 +1396,18 @@
     <t>onshore wind resource -- CF class won-CHN_50 -- cost class 2</t>
   </si>
   <si>
+    <t>e_won-CHN_49_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-CHN_49 -- cost class 2</t>
+  </si>
+  <si>
     <t>e_won-CHN_49_c5</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-CHN_49 -- cost class 5</t>
   </si>
   <si>
-    <t>e_won-CHN_49_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-CHN_49 -- cost class 2</t>
-  </si>
-  <si>
     <t>e_won-CHN_49_c3</t>
   </si>
   <si>
@@ -1828,6 +1828,12 @@
     <t>onshore wind resource -- CF class won-CHN_35 -- cost class 4</t>
   </si>
   <si>
+    <t>e_won-CHN_35_c5</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-CHN_35 -- cost class 5</t>
+  </si>
+  <si>
     <t>e_won-CHN_35_c3</t>
   </si>
   <si>
@@ -1840,10 +1846,10 @@
     <t>onshore wind resource -- CF class won-CHN_35 -- cost class 1</t>
   </si>
   <si>
-    <t>e_won-CHN_35_c5</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-CHN_35 -- cost class 5</t>
+    <t>e_won-CHN_34_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-CHN_34 -- cost class 2</t>
   </si>
   <si>
     <t>e_won-CHN_34_c4</t>
@@ -1852,12 +1858,6 @@
     <t>onshore wind resource -- CF class won-CHN_34 -- cost class 4</t>
   </si>
   <si>
-    <t>e_won-CHN_34_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-CHN_34 -- cost class 2</t>
-  </si>
-  <si>
     <t>e_won-CHN_34_c5</t>
   </si>
   <si>
@@ -1894,18 +1894,18 @@
     <t>onshore wind resource -- CF class won-CHN_33 -- cost class 2</t>
   </si>
   <si>
+    <t>e_won-CHN_33_c3</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-CHN_33 -- cost class 3</t>
+  </si>
+  <si>
     <t>e_won-CHN_33_c5</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-CHN_33 -- cost class 5</t>
   </si>
   <si>
-    <t>e_won-CHN_33_c3</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-CHN_33 -- cost class 3</t>
-  </si>
-  <si>
     <t>e_won-CHN_32_c1</t>
   </si>
   <si>
@@ -1978,42 +1978,42 @@
     <t>onshore wind resource -- CF class won-CHN_30 -- cost class 2</t>
   </si>
   <si>
+    <t>e_won-CHN_30_c4</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-CHN_30 -- cost class 4</t>
+  </si>
+  <si>
+    <t>e_won-CHN_30_c3</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-CHN_30 -- cost class 3</t>
+  </si>
+  <si>
     <t>e_won-CHN_30_c5</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-CHN_30 -- cost class 5</t>
   </si>
   <si>
-    <t>e_won-CHN_30_c4</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-CHN_30 -- cost class 4</t>
-  </si>
-  <si>
-    <t>e_won-CHN_30_c3</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-CHN_30 -- cost class 3</t>
-  </si>
-  <si>
     <t>e_won-CHN_29_c4</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-CHN_29 -- cost class 4</t>
   </si>
   <si>
+    <t>e_won-CHN_29_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-CHN_29 -- cost class 1</t>
+  </si>
+  <si>
     <t>e_won-CHN_29_c3</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-CHN_29 -- cost class 3</t>
   </si>
   <si>
-    <t>e_won-CHN_29_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-CHN_29 -- cost class 1</t>
-  </si>
-  <si>
     <t>e_won-CHN_29_c5</t>
   </si>
   <si>
@@ -2038,18 +2038,18 @@
     <t>onshore wind resource -- CF class won-CHN_28 -- cost class 2</t>
   </si>
   <si>
+    <t>e_won-CHN_28_c3</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-CHN_28 -- cost class 3</t>
+  </si>
+  <si>
     <t>e_won-CHN_28_c4</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-CHN_28 -- cost class 4</t>
   </si>
   <si>
-    <t>e_won-CHN_28_c3</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-CHN_28 -- cost class 3</t>
-  </si>
-  <si>
     <t>e_won-CHN_28_c5</t>
   </si>
   <si>
@@ -2098,18 +2098,18 @@
     <t>onshore wind resource -- CF class won-CHN_26 -- cost class 1</t>
   </si>
   <si>
+    <t>e_won-CHN_26_c4</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-CHN_26 -- cost class 4</t>
+  </si>
+  <si>
     <t>e_won-CHN_26_c5</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-CHN_26 -- cost class 5</t>
   </si>
   <si>
-    <t>e_won-CHN_26_c4</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-CHN_26 -- cost class 4</t>
-  </si>
-  <si>
     <t>e_won-CHN_26_c3</t>
   </si>
   <si>
@@ -2146,24 +2146,24 @@
     <t>onshore wind resource -- CF class won-CHN_25 -- cost class 3</t>
   </si>
   <si>
+    <t>e_won-CHN_24_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-CHN_24 -- cost class 1</t>
+  </si>
+  <si>
+    <t>e_won-CHN_24_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-CHN_24 -- cost class 2</t>
+  </si>
+  <si>
     <t>e_won-CHN_24_c4</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-CHN_24 -- cost class 4</t>
   </si>
   <si>
-    <t>e_won-CHN_24_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-CHN_24 -- cost class 1</t>
-  </si>
-  <si>
-    <t>e_won-CHN_24_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-CHN_24 -- cost class 2</t>
-  </si>
-  <si>
     <t>e_won-CHN_24_c3</t>
   </si>
   <si>
@@ -2188,18 +2188,18 @@
     <t>onshore wind resource -- CF class won-CHN_23 -- cost class 3</t>
   </si>
   <si>
+    <t>e_won-CHN_23_c4</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-CHN_23 -- cost class 4</t>
+  </si>
+  <si>
     <t>e_won-CHN_23_c5</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-CHN_23 -- cost class 5</t>
   </si>
   <si>
-    <t>e_won-CHN_23_c4</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-CHN_23 -- cost class 4</t>
-  </si>
-  <si>
     <t>e_won-CHN_23_c2</t>
   </si>
   <si>
@@ -2272,6 +2272,18 @@
     <t>onshore wind resource -- CF class won-CHN_20 -- cost class 3</t>
   </si>
   <si>
+    <t>e_won-CHN_20_c5</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-CHN_20 -- cost class 5</t>
+  </si>
+  <si>
+    <t>e_won-CHN_20_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-CHN_20 -- cost class 2</t>
+  </si>
+  <si>
     <t>e_won-CHN_20_c1</t>
   </si>
   <si>
@@ -2284,18 +2296,6 @@
     <t>onshore wind resource -- CF class won-CHN_20 -- cost class 4</t>
   </si>
   <si>
-    <t>e_won-CHN_20_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-CHN_20 -- cost class 2</t>
-  </si>
-  <si>
-    <t>e_won-CHN_20_c5</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-CHN_20 -- cost class 5</t>
-  </si>
-  <si>
     <t>e_won-CHN_19_c4</t>
   </si>
   <si>
@@ -2308,24 +2308,24 @@
     <t>onshore wind resource -- CF class won-CHN_19 -- cost class 1</t>
   </si>
   <si>
+    <t>e_won-CHN_19_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-CHN_19 -- cost class 2</t>
+  </si>
+  <si>
+    <t>e_won-CHN_19_c5</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-CHN_19 -- cost class 5</t>
+  </si>
+  <si>
     <t>e_won-CHN_19_c3</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-CHN_19 -- cost class 3</t>
   </si>
   <si>
-    <t>e_won-CHN_19_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-CHN_19 -- cost class 2</t>
-  </si>
-  <si>
-    <t>e_won-CHN_19_c5</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-CHN_19 -- cost class 5</t>
-  </si>
-  <si>
     <t>e_won-CHN_18_c3</t>
   </si>
   <si>
@@ -2362,30 +2362,36 @@
     <t>onshore wind resource -- CF class won-CHN_17 -- cost class 4</t>
   </si>
   <si>
+    <t>e_won-CHN_17_c3</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-CHN_17 -- cost class 3</t>
+  </si>
+  <si>
+    <t>e_won-CHN_17_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-CHN_17 -- cost class 1</t>
+  </si>
+  <si>
     <t>e_won-CHN_17_c2</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-CHN_17 -- cost class 2</t>
   </si>
   <si>
-    <t>e_won-CHN_17_c3</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-CHN_17 -- cost class 3</t>
-  </si>
-  <si>
-    <t>e_won-CHN_17_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-CHN_17 -- cost class 1</t>
-  </si>
-  <si>
     <t>e_won-CHN_17_c5</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-CHN_17 -- cost class 5</t>
   </si>
   <si>
+    <t>e_won-CHN_16_c5</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-CHN_16 -- cost class 5</t>
+  </si>
+  <si>
     <t>e_won-CHN_16_c1</t>
   </si>
   <si>
@@ -2398,12 +2404,6 @@
     <t>onshore wind resource -- CF class won-CHN_16 -- cost class 3</t>
   </si>
   <si>
-    <t>e_won-CHN_16_c5</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-CHN_16 -- cost class 5</t>
-  </si>
-  <si>
     <t>e_won-CHN_16_c2</t>
   </si>
   <si>
@@ -2452,6 +2452,12 @@
     <t>onshore wind resource -- CF class won-CHN_14 -- cost class 4</t>
   </si>
   <si>
+    <t>e_won-CHN_14_c3</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-CHN_14 -- cost class 3</t>
+  </si>
+  <si>
     <t>e_won-CHN_14_c5</t>
   </si>
   <si>
@@ -2464,12 +2470,6 @@
     <t>onshore wind resource -- CF class won-CHN_14 -- cost class 2</t>
   </si>
   <si>
-    <t>e_won-CHN_14_c3</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-CHN_14 -- cost class 3</t>
-  </si>
-  <si>
     <t>e_won-CHN_14_c1</t>
   </si>
   <si>
@@ -2488,18 +2488,18 @@
     <t>onshore wind resource -- CF class won-CHN_13 -- cost class 2</t>
   </si>
   <si>
+    <t>e_won-CHN_13_c5</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-CHN_13 -- cost class 5</t>
+  </si>
+  <si>
     <t>e_won-CHN_13_c4</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-CHN_13 -- cost class 4</t>
   </si>
   <si>
-    <t>e_won-CHN_13_c5</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-CHN_13 -- cost class 5</t>
-  </si>
-  <si>
     <t>e_won-CHN_13_c3</t>
   </si>
   <si>
@@ -2554,18 +2554,18 @@
     <t>onshore wind resource -- CF class won-CHN_11 -- cost class 1</t>
   </si>
   <si>
+    <t>e_won-CHN_11_c5</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-CHN_11 -- cost class 5</t>
+  </si>
+  <si>
     <t>e_won-CHN_11_c4</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-CHN_11 -- cost class 4</t>
   </si>
   <si>
-    <t>e_won-CHN_11_c5</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-CHN_11 -- cost class 5</t>
-  </si>
-  <si>
     <t>e_won-CHN_10_c3</t>
   </si>
   <si>
@@ -2632,18 +2632,18 @@
     <t>onshore wind resource -- CF class won-CHN_8 -- cost class 3</t>
   </si>
   <si>
+    <t>e_won-CHN_8_c5</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-CHN_8 -- cost class 5</t>
+  </si>
+  <si>
     <t>e_won-CHN_8_c4</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-CHN_8 -- cost class 4</t>
   </si>
   <si>
-    <t>e_won-CHN_8_c5</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-CHN_8 -- cost class 5</t>
-  </si>
-  <si>
     <t>e_won-CHN_8_c1</t>
   </si>
   <si>
@@ -2698,36 +2698,36 @@
     <t>onshore wind resource -- CF class won-CHN_6 -- cost class 3</t>
   </si>
   <si>
+    <t>e_won-CHN_6_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-CHN_6 -- cost class 1</t>
+  </si>
+  <si>
     <t>e_won-CHN_6_c2</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-CHN_6 -- cost class 2</t>
   </si>
   <si>
-    <t>e_won-CHN_6_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-CHN_6 -- cost class 1</t>
-  </si>
-  <si>
     <t>e_won-CHN_6_c5</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-CHN_6 -- cost class 5</t>
   </si>
   <si>
+    <t>e_won-CHN_5_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-CHN_5 -- cost class 2</t>
+  </si>
+  <si>
     <t>e_won-CHN_5_c1</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-CHN_5 -- cost class 1</t>
   </si>
   <si>
-    <t>e_won-CHN_5_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-CHN_5 -- cost class 2</t>
-  </si>
-  <si>
     <t>e_won-CHN_5_c4</t>
   </si>
   <si>
@@ -2758,6 +2758,12 @@
     <t>onshore wind resource -- CF class won-CHN_4 -- cost class 1</t>
   </si>
   <si>
+    <t>e_won-CHN_4_c5</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-CHN_4 -- cost class 5</t>
+  </si>
+  <si>
     <t>e_won-CHN_4_c4</t>
   </si>
   <si>
@@ -2770,12 +2776,6 @@
     <t>onshore wind resource -- CF class won-CHN_4 -- cost class 3</t>
   </si>
   <si>
-    <t>e_won-CHN_4_c5</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-CHN_4 -- cost class 5</t>
-  </si>
-  <si>
     <t>e_won-CHN_3_c1</t>
   </si>
   <si>
@@ -2794,18 +2794,18 @@
     <t>onshore wind resource -- CF class won-CHN_3 -- cost class 4</t>
   </si>
   <si>
+    <t>e_won-CHN_3_c5</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-CHN_3 -- cost class 5</t>
+  </si>
+  <si>
     <t>e_won-CHN_3_c3</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-CHN_3 -- cost class 3</t>
   </si>
   <si>
-    <t>e_won-CHN_3_c5</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-CHN_3 -- cost class 5</t>
-  </si>
-  <si>
     <t>e_won-CHN_2_c3</t>
   </si>
   <si>
@@ -2866,28 +2866,28 @@
     <t>onshore wind resource -- CF class won-CHN_1 -- cost class 4</t>
   </si>
   <si>
+    <t>e_won-CHN_0_c3</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-CHN_0 -- cost class 3</t>
+  </si>
+  <si>
+    <t>e_won-CHN_0_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-CHN_0 -- cost class 2</t>
+  </si>
+  <si>
+    <t>e_won-CHN_0_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-CHN_0 -- cost class 1</t>
+  </si>
+  <si>
     <t>e_won-CHN_0_c5</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-CHN_0 -- cost class 5</t>
-  </si>
-  <si>
-    <t>e_won-CHN_0_c3</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-CHN_0 -- cost class 3</t>
-  </si>
-  <si>
-    <t>e_won-CHN_0_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-CHN_0 -- cost class 2</t>
-  </si>
-  <si>
-    <t>e_won-CHN_0_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-CHN_0 -- cost class 1</t>
   </si>
   <si>
     <t>e_won-CHN_0_c4</t>
@@ -5486,7 +5486,9 @@
       <c r="F8" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="1"/>
+      <c r="G8" t="s">
+        <v>14</v>
+      </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1" t="str">
@@ -5522,7 +5524,9 @@
       <c r="F9" t="s">
         <v>10</v>
       </c>
-      <c r="G9" s="1"/>
+      <c r="G9" t="s">
+        <v>14</v>
+      </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="K9" s="1"/>
@@ -8804,7 +8808,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3762D021-1C31-4323-90D8-9186E68052FF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8DE9A15-E3DA-4898-A6A3-B17E53C8928F}">
   <dimension ref="B9:N95"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -8883,10 +8887,10 @@
         <v>359</v>
       </c>
       <c r="L11">
-        <v>6.7500000000000004E-2</v>
+        <v>5.282382420971473E-2</v>
       </c>
       <c r="M11">
-        <v>0.30921377365329539</v>
+        <v>0.3092137736532955</v>
       </c>
       <c r="N11">
         <v>1</v>
@@ -8921,7 +8925,7 @@
         <v>359</v>
       </c>
       <c r="L12">
-        <v>1.5E-3</v>
+        <v>1.1034460526739948E-3</v>
       </c>
       <c r="M12">
         <v>0.30287861207395528</v>
@@ -8959,10 +8963,10 @@
         <v>359</v>
       </c>
       <c r="L13">
-        <v>0.93899999999999995</v>
+        <v>0.71557707865168541</v>
       </c>
       <c r="M13">
-        <v>0.30174037647928653</v>
+        <v>0.30174037647928659</v>
       </c>
       <c r="N13">
         <v>2</v>
@@ -8997,7 +9001,7 @@
         <v>359</v>
       </c>
       <c r="L14">
-        <v>5.2500000000000003E-3</v>
+        <v>4.0465309072357783E-3</v>
       </c>
       <c r="M14">
         <v>0.29708063915557542</v>
@@ -9035,7 +9039,7 @@
         <v>359</v>
       </c>
       <c r="L15">
-        <v>0.19500000000000001</v>
+        <v>0.17261500384996151</v>
       </c>
       <c r="M15">
         <v>0.29608939122610078</v>
@@ -9073,10 +9077,10 @@
         <v>359</v>
       </c>
       <c r="L16">
-        <v>0.93974999999999997</v>
+        <v>0.66362745591331429</v>
       </c>
       <c r="M16">
-        <v>0.29297132193958603</v>
+        <v>0.29294098080011788</v>
       </c>
       <c r="N16">
         <v>3</v>
@@ -9111,10 +9115,10 @@
         <v>359</v>
       </c>
       <c r="L17">
-        <v>1.488</v>
+        <v>0.98581109256930199</v>
       </c>
       <c r="M17">
-        <v>0.29228401016333666</v>
+        <v>0.29230902488798644</v>
       </c>
       <c r="N17">
         <v>1</v>
@@ -9149,10 +9153,10 @@
         <v>359</v>
       </c>
       <c r="L18">
-        <v>2.952</v>
+        <v>2.0632252000068596</v>
       </c>
       <c r="M18">
-        <v>0.28988923944058009</v>
+        <v>0.28985526602656836</v>
       </c>
       <c r="N18">
         <v>5</v>
@@ -9187,13 +9191,13 @@
         <v>359</v>
       </c>
       <c r="L19">
-        <v>3.2250000000000001</v>
+        <v>3.3509764187415141</v>
       </c>
       <c r="M19">
-        <v>0.28690993050767033</v>
+        <v>0.28691868472823828</v>
       </c>
       <c r="N19">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="2:14">
@@ -9225,13 +9229,13 @@
         <v>359</v>
       </c>
       <c r="L20">
-        <v>4.6357499999999998</v>
+        <v>1.9907059792898678</v>
       </c>
       <c r="M20">
-        <v>0.28670214981465209</v>
+        <v>0.28690289357174487</v>
       </c>
       <c r="N20">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="2:14">
@@ -9263,10 +9267,10 @@
         <v>359</v>
       </c>
       <c r="L21">
-        <v>9.37425</v>
+        <v>6.1726003948759329</v>
       </c>
       <c r="M21">
-        <v>0.28049529847086763</v>
+        <v>0.28057679225992188</v>
       </c>
       <c r="N21">
         <v>3</v>
@@ -9301,10 +9305,10 @@
         <v>359</v>
       </c>
       <c r="L22">
-        <v>13.17225</v>
+        <v>9.1662563273219551</v>
       </c>
       <c r="M22">
-        <v>0.27944318682924091</v>
+        <v>0.27933705911893908</v>
       </c>
       <c r="N22">
         <v>1</v>
@@ -9339,10 +9343,10 @@
         <v>359</v>
       </c>
       <c r="L23">
-        <v>23.279250000000001</v>
+        <v>15.567605729496155</v>
       </c>
       <c r="M23">
-        <v>0.27873353111749222</v>
+        <v>0.27875218792222983</v>
       </c>
       <c r="N23">
         <v>4</v>
@@ -9377,10 +9381,10 @@
         <v>359</v>
       </c>
       <c r="L24">
-        <v>9.2512500000000006</v>
+        <v>6.4335006519841444</v>
       </c>
       <c r="M24">
-        <v>0.27802548038880942</v>
+        <v>0.27790989832041574</v>
       </c>
       <c r="N24">
         <v>2</v>
@@ -9415,10 +9419,10 @@
         <v>359</v>
       </c>
       <c r="L25">
-        <v>18.968250000000001</v>
+        <v>11.983934603734197</v>
       </c>
       <c r="M25">
-        <v>0.27732869402271754</v>
+        <v>0.27740191234231837</v>
       </c>
       <c r="N25">
         <v>5</v>
@@ -9453,10 +9457,10 @@
         <v>359</v>
       </c>
       <c r="L26">
-        <v>150.53325000000001</v>
+        <v>88.685709832234537</v>
       </c>
       <c r="M26">
-        <v>0.26964172280788073</v>
+        <v>0.2697217971915678</v>
       </c>
       <c r="N26">
         <v>3</v>
@@ -9491,10 +9495,10 @@
         <v>359</v>
       </c>
       <c r="L27">
-        <v>78.227249999999998</v>
+        <v>51.976185034992099</v>
       </c>
       <c r="M27">
-        <v>0.26843567229456539</v>
+        <v>0.26850219539270437</v>
       </c>
       <c r="N27">
         <v>2</v>
@@ -9529,10 +9533,10 @@
         <v>359</v>
       </c>
       <c r="L28">
-        <v>150.66149999999999</v>
+        <v>80.588953645411877</v>
       </c>
       <c r="M28">
-        <v>0.26795798755603095</v>
+        <v>0.26809952757798744</v>
       </c>
       <c r="N28">
         <v>4</v>
@@ -9567,10 +9571,10 @@
         <v>359</v>
       </c>
       <c r="L29">
-        <v>95.863500000000002</v>
+        <v>54.563937443888292</v>
       </c>
       <c r="M29">
-        <v>0.26739484535075664</v>
+        <v>0.26748687481319217</v>
       </c>
       <c r="N29">
         <v>1</v>
@@ -9605,10 +9609,10 @@
         <v>359</v>
       </c>
       <c r="L30">
-        <v>150.62700000000001</v>
+        <v>80.906945648493746</v>
       </c>
       <c r="M30">
-        <v>0.26709807711593492</v>
+        <v>0.26715796166041306</v>
       </c>
       <c r="N30">
         <v>5</v>
@@ -9643,10 +9647,10 @@
         <v>359</v>
       </c>
       <c r="L31">
-        <v>314.98950000000002</v>
+        <v>183.13100115927941</v>
       </c>
       <c r="M31">
-        <v>0.26134775320904374</v>
+        <v>0.26127966921495965</v>
       </c>
       <c r="N31">
         <v>5</v>
@@ -9681,10 +9685,10 @@
         <v>359</v>
       </c>
       <c r="L32">
-        <v>261.94725</v>
+        <v>170.7813912723704</v>
       </c>
       <c r="M32">
-        <v>0.2609216994424981</v>
+        <v>0.260606788277708</v>
       </c>
       <c r="N32">
         <v>3</v>
@@ -9719,10 +9723,10 @@
         <v>359</v>
       </c>
       <c r="L33">
-        <v>319.45800000000003</v>
+        <v>198.85241770470836</v>
       </c>
       <c r="M33">
-        <v>0.26042635672299774</v>
+        <v>0.2602515236487869</v>
       </c>
       <c r="N33">
         <v>4</v>
@@ -9757,10 +9761,10 @@
         <v>359</v>
       </c>
       <c r="L34">
-        <v>232.50149999999999</v>
+        <v>140.46874300952382</v>
       </c>
       <c r="M34">
-        <v>0.26001383012174584</v>
+        <v>0.25996581570657257</v>
       </c>
       <c r="N34">
         <v>2</v>
@@ -9795,10 +9799,10 @@
         <v>359</v>
       </c>
       <c r="L35">
-        <v>285.20325000000003</v>
+        <v>148.63797386666775</v>
       </c>
       <c r="M35">
-        <v>0.25968103993815705</v>
+        <v>0.25961287288544654</v>
       </c>
       <c r="N35">
         <v>1</v>
@@ -9833,10 +9837,10 @@
         <v>359</v>
       </c>
       <c r="L36">
-        <v>188.61600000000001</v>
+        <v>140.34839952541404</v>
       </c>
       <c r="M36">
-        <v>0.25126822421531841</v>
+        <v>0.25124447385002069</v>
       </c>
       <c r="N36">
         <v>5</v>
@@ -9871,10 +9875,10 @@
         <v>359</v>
       </c>
       <c r="L37">
-        <v>289.36574999999999</v>
+        <v>154.03594966445388</v>
       </c>
       <c r="M37">
-        <v>0.25036801661519176</v>
+        <v>0.25049386954595843</v>
       </c>
       <c r="N37">
         <v>2</v>
@@ -9909,10 +9913,10 @@
         <v>359</v>
       </c>
       <c r="L38">
-        <v>218.21475000000001</v>
+        <v>122.83132879129737</v>
       </c>
       <c r="M38">
-        <v>0.25034307611139539</v>
+        <v>0.25039795280109184</v>
       </c>
       <c r="N38">
         <v>3</v>
@@ -9947,10 +9951,10 @@
         <v>359</v>
       </c>
       <c r="L39">
-        <v>182.17724999999999</v>
+        <v>105.24905910055062</v>
       </c>
       <c r="M39">
-        <v>0.24932675507798363</v>
+        <v>0.24917524416223513</v>
       </c>
       <c r="N39">
         <v>4</v>
@@ -9985,10 +9989,10 @@
         <v>359</v>
       </c>
       <c r="L40">
-        <v>301.38825000000003</v>
+        <v>153.55299588874476</v>
       </c>
       <c r="M40">
-        <v>0.2482150587918181</v>
+        <v>0.24822192658469192</v>
       </c>
       <c r="N40">
         <v>1</v>
@@ -10023,10 +10027,10 @@
         <v>359</v>
       </c>
       <c r="L41">
-        <v>185.06475</v>
+        <v>106.33164464582663</v>
       </c>
       <c r="M41">
-        <v>0.23971049207361358</v>
+        <v>0.23960303881318146</v>
       </c>
       <c r="N41">
         <v>4</v>
@@ -10061,10 +10065,10 @@
         <v>359</v>
       </c>
       <c r="L42">
-        <v>271.37175000000002</v>
+        <v>147.1800439499072</v>
       </c>
       <c r="M42">
-        <v>0.23938979551310879</v>
+        <v>0.23934341857079497</v>
       </c>
       <c r="N42">
         <v>3</v>
@@ -10099,10 +10103,10 @@
         <v>359</v>
       </c>
       <c r="L43">
-        <v>278.24700000000001</v>
+        <v>138.43759412896168</v>
       </c>
       <c r="M43">
-        <v>0.23929083708198667</v>
+        <v>0.23933218113394086</v>
       </c>
       <c r="N43">
         <v>1</v>
@@ -10137,10 +10141,10 @@
         <v>359</v>
       </c>
       <c r="L44">
-        <v>272.63249999999999</v>
+        <v>141.4649403213547</v>
       </c>
       <c r="M44">
-        <v>0.23870442765819436</v>
+        <v>0.2387118084862459</v>
       </c>
       <c r="N44">
         <v>2</v>
@@ -10175,10 +10179,10 @@
         <v>359</v>
       </c>
       <c r="L45">
-        <v>168.17699999999999</v>
+        <v>106.77619198350204</v>
       </c>
       <c r="M45">
-        <v>0.23859616455714674</v>
+        <v>0.23850927852339651</v>
       </c>
       <c r="N45">
         <v>5</v>
@@ -10213,10 +10217,10 @@
         <v>359</v>
       </c>
       <c r="L46">
-        <v>237.98775000000001</v>
+        <v>114.97576083124079</v>
       </c>
       <c r="M46">
-        <v>0.23174605489478428</v>
+        <v>0.23172562395430776</v>
       </c>
       <c r="N46">
         <v>1</v>
@@ -10251,10 +10255,10 @@
         <v>359</v>
       </c>
       <c r="L47">
-        <v>193.76925</v>
+        <v>108.1767018663772</v>
       </c>
       <c r="M47">
-        <v>0.23064878050801743</v>
+        <v>0.23061655003271106</v>
       </c>
       <c r="N47">
         <v>3</v>
@@ -10289,10 +10293,10 @@
         <v>359</v>
       </c>
       <c r="L48">
-        <v>159.48824999999999</v>
+        <v>102.30209649916503</v>
       </c>
       <c r="M48">
-        <v>0.23002430393272391</v>
+        <v>0.23007951180318664</v>
       </c>
       <c r="N48">
         <v>5</v>
@@ -10327,10 +10331,10 @@
         <v>359</v>
       </c>
       <c r="L49">
-        <v>210.26775000000001</v>
+        <v>104.26985277272018</v>
       </c>
       <c r="M49">
-        <v>0.22986069462075451</v>
+        <v>0.22994069861902119</v>
       </c>
       <c r="N49">
         <v>2</v>
@@ -10365,10 +10369,10 @@
         <v>359</v>
       </c>
       <c r="L50">
-        <v>87.747749999999996</v>
+        <v>51.172065718315672</v>
       </c>
       <c r="M50">
-        <v>0.22891748385891636</v>
+        <v>0.22890792022977749</v>
       </c>
       <c r="N50">
         <v>4</v>
@@ -10403,10 +10407,10 @@
         <v>359</v>
       </c>
       <c r="L51">
-        <v>112.28400000000001</v>
+        <v>68.176498082673916</v>
       </c>
       <c r="M51">
-        <v>0.22048698138290967</v>
+        <v>0.22036117876451797</v>
       </c>
       <c r="N51">
         <v>4</v>
@@ -10441,10 +10445,10 @@
         <v>359</v>
       </c>
       <c r="L52">
-        <v>91.722750000000005</v>
+        <v>55.340749539955482</v>
       </c>
       <c r="M52">
-        <v>0.22012566542201106</v>
+        <v>0.22008386470225227</v>
       </c>
       <c r="N52">
         <v>3</v>
@@ -10479,10 +10483,10 @@
         <v>359</v>
       </c>
       <c r="L53">
-        <v>254.21924999999999</v>
+        <v>124.29572194331296</v>
       </c>
       <c r="M53">
-        <v>0.21951267587355491</v>
+        <v>0.21952843868448929</v>
       </c>
       <c r="N53">
         <v>1</v>
@@ -10517,10 +10521,10 @@
         <v>359</v>
       </c>
       <c r="L54">
-        <v>267.49124999999998</v>
+        <v>176.18131170895145</v>
       </c>
       <c r="M54">
-        <v>0.21946909955770352</v>
+        <v>0.21934475822331093</v>
       </c>
       <c r="N54">
         <v>5</v>
@@ -10555,10 +10559,10 @@
         <v>359</v>
       </c>
       <c r="L55">
-        <v>237.279</v>
+        <v>112.66136792381818</v>
       </c>
       <c r="M55">
-        <v>0.21889635437424623</v>
+        <v>0.21890575875302878</v>
       </c>
       <c r="N55">
         <v>2</v>
@@ -10593,10 +10597,10 @@
         <v>359</v>
       </c>
       <c r="L56">
-        <v>472.82324999999997</v>
+        <v>235.61583621401334</v>
       </c>
       <c r="M56">
-        <v>0.21182023068172601</v>
+        <v>0.21179569379240329</v>
       </c>
       <c r="N56">
         <v>1</v>
@@ -10631,10 +10635,10 @@
         <v>359</v>
       </c>
       <c r="L57">
-        <v>401.01150000000001</v>
+        <v>197.33053996356026</v>
       </c>
       <c r="M57">
-        <v>0.20975692806872756</v>
+        <v>0.209737961314722</v>
       </c>
       <c r="N57">
         <v>2</v>
@@ -10669,10 +10673,10 @@
         <v>359</v>
       </c>
       <c r="L58">
-        <v>172.90199999999999</v>
+        <v>93.280108891222127</v>
       </c>
       <c r="M58">
-        <v>0.20827742331853091</v>
+        <v>0.2084264052661127</v>
       </c>
       <c r="N58">
         <v>3</v>
@@ -10707,13 +10711,13 @@
         <v>359</v>
       </c>
       <c r="L59">
-        <v>384.08550000000002</v>
+        <v>134.39646864083346</v>
       </c>
       <c r="M59">
-        <v>0.20824412964706487</v>
+        <v>0.20828108896127498</v>
       </c>
       <c r="N59">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60" spans="2:14">
@@ -10745,13 +10749,13 @@
         <v>359</v>
       </c>
       <c r="L60">
-        <v>231.65774999999999</v>
+        <v>214.01423777373284</v>
       </c>
       <c r="M60">
-        <v>0.20814027222734993</v>
+        <v>0.20826833547719767</v>
       </c>
       <c r="N60">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61" spans="2:14">
@@ -10783,10 +10787,10 @@
         <v>359</v>
       </c>
       <c r="L61">
-        <v>245.13300000000001</v>
+        <v>140.63693164807583</v>
       </c>
       <c r="M61">
-        <v>0.20259080577575675</v>
+        <v>0.2026274643055502</v>
       </c>
       <c r="N61">
         <v>4</v>
@@ -10821,10 +10825,10 @@
         <v>359</v>
       </c>
       <c r="L62">
-        <v>340.78424999999999</v>
+        <v>179.1331150755403</v>
       </c>
       <c r="M62">
-        <v>0.20083623552133592</v>
+        <v>0.20076899524411115</v>
       </c>
       <c r="N62">
         <v>2</v>
@@ -10859,10 +10863,10 @@
         <v>359</v>
       </c>
       <c r="L63">
-        <v>408.00150000000002</v>
+        <v>208.57926465026705</v>
       </c>
       <c r="M63">
-        <v>0.20066871604533948</v>
+        <v>0.20060576465378926</v>
       </c>
       <c r="N63">
         <v>1</v>
@@ -10897,10 +10901,10 @@
         <v>359</v>
       </c>
       <c r="L64">
-        <v>398.64150000000001</v>
+        <v>212.73409522999611</v>
       </c>
       <c r="M64">
-        <v>0.19942973289589497</v>
+        <v>0.19939102376690931</v>
       </c>
       <c r="N64">
         <v>5</v>
@@ -10935,10 +10939,10 @@
         <v>359</v>
       </c>
       <c r="L65">
-        <v>189.74775</v>
+        <v>110.03746416770126</v>
       </c>
       <c r="M65">
-        <v>0.19898972331041526</v>
+        <v>0.19905574388900268</v>
       </c>
       <c r="N65">
         <v>3</v>
@@ -10973,10 +10977,10 @@
         <v>359</v>
       </c>
       <c r="L66">
-        <v>107.83199999999999</v>
+        <v>67.041154427327825</v>
       </c>
       <c r="M66">
-        <v>0.19110969094886296</v>
+        <v>0.19105712930809465</v>
       </c>
       <c r="N66">
         <v>3</v>
@@ -11011,10 +11015,10 @@
         <v>359</v>
       </c>
       <c r="L67">
-        <v>143.53874999999999</v>
+        <v>74.618308008333287</v>
       </c>
       <c r="M67">
-        <v>0.18996814456211233</v>
+        <v>0.18990285732488255</v>
       </c>
       <c r="N67">
         <v>4</v>
@@ -11049,10 +11053,10 @@
         <v>359</v>
       </c>
       <c r="L68">
-        <v>308.86124999999998</v>
+        <v>177.61102694013866</v>
       </c>
       <c r="M68">
-        <v>0.18963340463067677</v>
+        <v>0.18963059728940965</v>
       </c>
       <c r="N68">
         <v>1</v>
@@ -11087,10 +11091,10 @@
         <v>359</v>
       </c>
       <c r="L69">
-        <v>258.45375000000001</v>
+        <v>146.21701898862023</v>
       </c>
       <c r="M69">
-        <v>0.1896123570273531</v>
+        <v>0.18951606504970769</v>
       </c>
       <c r="N69">
         <v>2</v>
@@ -11125,10 +11129,10 @@
         <v>359</v>
       </c>
       <c r="L70">
-        <v>308.84100000000001</v>
+        <v>164.34555269496991</v>
       </c>
       <c r="M70">
-        <v>0.18909596190025746</v>
+        <v>0.18907323793491504</v>
       </c>
       <c r="N70">
         <v>5</v>
@@ -11163,10 +11167,10 @@
         <v>359</v>
       </c>
       <c r="L71">
-        <v>84.782250000000005</v>
+        <v>42.282877462294593</v>
       </c>
       <c r="M71">
-        <v>0.18160493644187736</v>
+        <v>0.18148990772445645</v>
       </c>
       <c r="N71">
         <v>2</v>
@@ -11201,10 +11205,10 @@
         <v>359</v>
       </c>
       <c r="L72">
-        <v>84.087000000000003</v>
+        <v>48.598351913530671</v>
       </c>
       <c r="M72">
-        <v>0.18131983448310798</v>
+        <v>0.18129095527046105</v>
       </c>
       <c r="N72">
         <v>1</v>
@@ -11239,10 +11243,10 @@
         <v>359</v>
       </c>
       <c r="L73">
-        <v>116.26725</v>
+        <v>66.65503571772625</v>
       </c>
       <c r="M73">
-        <v>0.1801802282024155</v>
+        <v>0.18014230311084634</v>
       </c>
       <c r="N73">
         <v>4</v>
@@ -11277,10 +11281,10 @@
         <v>359</v>
       </c>
       <c r="L74">
-        <v>169.47900000000001</v>
+        <v>93.075941513303292</v>
       </c>
       <c r="M74">
-        <v>0.17988505441887201</v>
+        <v>0.17978691950209208</v>
       </c>
       <c r="N74">
         <v>3</v>
@@ -11315,10 +11319,10 @@
         <v>359</v>
       </c>
       <c r="L75">
-        <v>113.91</v>
+        <v>60.914123071671568</v>
       </c>
       <c r="M75">
-        <v>0.17897855944162697</v>
+        <v>0.17893373354580613</v>
       </c>
       <c r="N75">
         <v>5</v>
@@ -11353,10 +11357,10 @@
         <v>359</v>
       </c>
       <c r="L76">
-        <v>91.073250000000002</v>
+        <v>55.019947819503642</v>
       </c>
       <c r="M76">
-        <v>0.17131350879357249</v>
+        <v>0.17126301426675622</v>
       </c>
       <c r="N76">
         <v>4</v>
@@ -11391,10 +11395,10 @@
         <v>359</v>
       </c>
       <c r="L77">
-        <v>54.046500000000002</v>
+        <v>31.612086235792539</v>
       </c>
       <c r="M77">
-        <v>0.17082171446809119</v>
+        <v>0.17080921986906547</v>
       </c>
       <c r="N77">
         <v>2</v>
@@ -11429,10 +11433,10 @@
         <v>359</v>
       </c>
       <c r="L78">
-        <v>82.926749999999998</v>
+        <v>50.327840297195486</v>
       </c>
       <c r="M78">
-        <v>0.17027972762115129</v>
+        <v>0.17024034727389359</v>
       </c>
       <c r="N78">
         <v>3</v>
@@ -11467,10 +11471,10 @@
         <v>359</v>
       </c>
       <c r="L79">
-        <v>68.312250000000006</v>
+        <v>40.879493722767563</v>
       </c>
       <c r="M79">
-        <v>0.16987839532797808</v>
+        <v>0.1697190594103927</v>
       </c>
       <c r="N79">
         <v>1</v>
@@ -11505,10 +11509,10 @@
         <v>359</v>
       </c>
       <c r="L80">
-        <v>105.15525</v>
+        <v>58.316421752232273</v>
       </c>
       <c r="M80">
-        <v>0.16925655541951998</v>
+        <v>0.16913305048169991</v>
       </c>
       <c r="N80">
         <v>5</v>
@@ -11543,10 +11547,10 @@
         <v>359</v>
       </c>
       <c r="L81">
-        <v>76.088999999999999</v>
+        <v>45.10641522859035</v>
       </c>
       <c r="M81">
-        <v>0.16215418412286095</v>
+        <v>0.16218211326042262</v>
       </c>
       <c r="N81">
         <v>1</v>
@@ -11581,10 +11585,10 @@
         <v>359</v>
       </c>
       <c r="L82">
-        <v>64.151250000000005</v>
+        <v>37.174722953757566</v>
       </c>
       <c r="M82">
-        <v>0.16088992704178279</v>
+        <v>0.16083375464250591</v>
       </c>
       <c r="N82">
         <v>4</v>
@@ -11619,10 +11623,10 @@
         <v>359</v>
       </c>
       <c r="L83">
-        <v>48.512250000000002</v>
+        <v>26.3661914614324</v>
       </c>
       <c r="M83">
-        <v>0.15983649589413942</v>
+        <v>0.15992886265967896</v>
       </c>
       <c r="N83">
         <v>3</v>
@@ -11657,10 +11661,10 @@
         <v>359</v>
       </c>
       <c r="L84">
-        <v>83.704499999999996</v>
+        <v>49.964840388086543</v>
       </c>
       <c r="M84">
-        <v>0.15899003652574437</v>
+        <v>0.15904212822299776</v>
       </c>
       <c r="N84">
         <v>2</v>
@@ -11695,10 +11699,10 @@
         <v>359</v>
       </c>
       <c r="L85">
-        <v>88.273499999999999</v>
+        <v>79.027650224463599</v>
       </c>
       <c r="M85">
-        <v>0.15652325105658774</v>
+        <v>0.15641870373558098</v>
       </c>
       <c r="N85">
         <v>5</v>
@@ -11733,13 +11737,13 @@
         <v>359</v>
       </c>
       <c r="L86">
-        <v>115.3245</v>
+        <v>51.263940039159834</v>
       </c>
       <c r="M86">
-        <v>0.15198337491531952</v>
+        <v>0.15213417193581313</v>
       </c>
       <c r="N86">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="87" spans="2:14">
@@ -11771,13 +11775,13 @@
         <v>359</v>
       </c>
       <c r="L87">
-        <v>60.727499999999999</v>
+        <v>63.887803016316283</v>
       </c>
       <c r="M87">
-        <v>0.15183654442551917</v>
+        <v>0.15207427435564799</v>
       </c>
       <c r="N87">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88" spans="2:14">
@@ -11809,10 +11813,10 @@
         <v>359</v>
       </c>
       <c r="L88">
-        <v>117.6345</v>
+        <v>115.27052126305254</v>
       </c>
       <c r="M88">
-        <v>0.15164727656573446</v>
+        <v>0.15168306502669798</v>
       </c>
       <c r="N88">
         <v>5</v>
@@ -11847,10 +11851,10 @@
         <v>359</v>
       </c>
       <c r="L89">
-        <v>54.167999999999999</v>
+        <v>28.620868308298846</v>
       </c>
       <c r="M89">
-        <v>0.14918845204096914</v>
+        <v>0.14926070992035551</v>
       </c>
       <c r="N89">
         <v>3</v>
@@ -11885,10 +11889,10 @@
         <v>359</v>
       </c>
       <c r="L90">
-        <v>70.337999999999994</v>
+        <v>36.849084950496611</v>
       </c>
       <c r="M90">
-        <v>0.14912818967646768</v>
+        <v>0.14913817202480104</v>
       </c>
       <c r="N90">
         <v>2</v>
@@ -11923,10 +11927,10 @@
         <v>359</v>
       </c>
       <c r="L91">
-        <v>7.0964999999999998</v>
+        <v>4.2756607891841867</v>
       </c>
       <c r="M91">
-        <v>0.14400573554648427</v>
+        <v>0.1440243613680908</v>
       </c>
       <c r="N91">
         <v>1</v>
@@ -11961,10 +11965,10 @@
         <v>359</v>
       </c>
       <c r="L92">
-        <v>9.4957499999999992</v>
+        <v>5.0439707866872885</v>
       </c>
       <c r="M92">
-        <v>0.14373654091803259</v>
+        <v>0.14373200767507308</v>
       </c>
       <c r="N92">
         <v>2</v>
@@ -11999,10 +12003,10 @@
         <v>359</v>
       </c>
       <c r="L93">
-        <v>12.54</v>
+        <v>7.1095738945794595</v>
       </c>
       <c r="M93">
-        <v>0.14250970840759442</v>
+        <v>0.14250061234980271</v>
       </c>
       <c r="N93">
         <v>3</v>
@@ -12037,13 +12041,13 @@
         <v>359</v>
       </c>
       <c r="L94">
-        <v>6.4552500000000004</v>
+        <v>3.011955171321997</v>
       </c>
       <c r="M94">
-        <v>0.14059227197793112</v>
+        <v>0.14067133413424482</v>
       </c>
       <c r="N94">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95" spans="2:14">
@@ -12075,13 +12079,13 @@
         <v>359</v>
       </c>
       <c r="L95">
-        <v>3.6412499999999999</v>
+        <v>3.791249112312236</v>
       </c>
       <c r="M95">
-        <v>0.14058878327300195</v>
+        <v>0.14062192986020322</v>
       </c>
       <c r="N95">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -12090,7 +12094,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4B4CCCA-2AC9-4679-8258-AF5CD512680E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6022B2D0-92D6-4A54-9157-DFBB152518D1}">
   <dimension ref="B9:AB291"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12211,10 +12215,10 @@
         <v>922</v>
       </c>
       <c r="L11">
-        <v>1.5E-3</v>
+        <v>1.0736360998258852E-3</v>
       </c>
       <c r="M11">
-        <v>0.70696625269541302</v>
+        <v>0.7069662508091753</v>
       </c>
       <c r="N11">
         <v>1</v>
@@ -12285,10 +12289,10 @@
         <v>922</v>
       </c>
       <c r="L12">
-        <v>3.7499999999999999E-3</v>
+        <v>2.6312367206388744E-3</v>
       </c>
       <c r="M12">
-        <v>0.70362289640146647</v>
+        <v>0.7036228952683532</v>
       </c>
       <c r="N12">
         <v>2</v>
@@ -12359,10 +12363,10 @@
         <v>922</v>
       </c>
       <c r="L13">
-        <v>2.775E-2</v>
+        <v>2.2441076487252125E-2</v>
       </c>
       <c r="M13">
-        <v>0.70003431599617194</v>
+        <v>0.70003431397615412</v>
       </c>
       <c r="N13">
         <v>1</v>
@@ -12433,10 +12437,10 @@
         <v>922</v>
       </c>
       <c r="L14">
-        <v>1.0649999999999999</v>
+        <v>0.76579300788744398</v>
       </c>
       <c r="M14">
-        <v>0.67991695793256413</v>
+        <v>0.67991695627885507</v>
       </c>
       <c r="N14">
         <v>1</v>
@@ -12472,7 +12476,7 @@
         <v>0.12525</v>
       </c>
       <c r="AA14">
-        <v>0.6406974854420544</v>
+        <v>0.64069748544205452</v>
       </c>
       <c r="AB14">
         <v>1</v>
@@ -12507,10 +12511,10 @@
         <v>922</v>
       </c>
       <c r="L15">
-        <v>0.22875000000000001</v>
+        <v>0.15696765266401752</v>
       </c>
       <c r="M15">
-        <v>0.64141594217681563</v>
+        <v>0.64141594080680686</v>
       </c>
       <c r="N15">
         <v>1</v>
@@ -12581,10 +12585,10 @@
         <v>922</v>
       </c>
       <c r="L16">
-        <v>0.28499999999999998</v>
+        <v>0.18133352701917488</v>
       </c>
       <c r="M16">
-        <v>0.61359108256605843</v>
+        <v>0.61359108077129387</v>
       </c>
       <c r="N16">
         <v>1</v>
@@ -12655,10 +12659,10 @@
         <v>922</v>
       </c>
       <c r="L17">
-        <v>0.12675</v>
+        <v>0.1179827945776851</v>
       </c>
       <c r="M17">
-        <v>0.59520875075804414</v>
+        <v>0.59520874890367614</v>
       </c>
       <c r="N17">
         <v>1</v>
@@ -12729,10 +12733,10 @@
         <v>922</v>
       </c>
       <c r="L18">
-        <v>1.5E-3</v>
+        <v>9.6959882992060176E-4</v>
       </c>
       <c r="M18">
-        <v>0.58666058887998351</v>
+        <v>0.58666058683006506</v>
       </c>
       <c r="N18">
         <v>2</v>
@@ -12803,10 +12807,10 @@
         <v>922</v>
       </c>
       <c r="L19">
-        <v>1.35E-2</v>
+        <v>1.171193713110949E-2</v>
       </c>
       <c r="M19">
-        <v>0.58660125423504295</v>
+        <v>0.58660125301217714</v>
       </c>
       <c r="N19">
         <v>1</v>
@@ -12877,10 +12881,10 @@
         <v>922</v>
       </c>
       <c r="L20">
-        <v>5.2500000000000003E-3</v>
+        <v>3.2065559991594872E-3</v>
       </c>
       <c r="M20">
-        <v>0.57979663962710037</v>
+        <v>0.57979663812993587</v>
       </c>
       <c r="N20">
         <v>2</v>
@@ -12951,10 +12955,10 @@
         <v>922</v>
       </c>
       <c r="L21">
-        <v>3.7499999999999999E-3</v>
+        <v>2.3230134516710578E-3</v>
       </c>
       <c r="M21">
-        <v>0.57568705471749548</v>
+        <v>0.57568705287290556</v>
       </c>
       <c r="N21">
         <v>1</v>
@@ -13025,10 +13029,10 @@
         <v>922</v>
       </c>
       <c r="L22">
-        <v>1.35E-2</v>
+        <v>1.2388696416761859E-2</v>
       </c>
       <c r="M22">
-        <v>0.5647722807262866</v>
+        <v>0.56475522576744797</v>
       </c>
       <c r="N22">
         <v>1</v>
@@ -13099,10 +13103,10 @@
         <v>922</v>
       </c>
       <c r="L23">
-        <v>3.7499999999999999E-3</v>
+        <v>2.401328008915305E-3</v>
       </c>
       <c r="M23">
-        <v>0.56388559831270835</v>
+        <v>0.56388559617533018</v>
       </c>
       <c r="N23">
         <v>2</v>
@@ -13173,10 +13177,10 @@
         <v>922</v>
       </c>
       <c r="L24">
-        <v>0.54149999999999998</v>
+        <v>0.4319170155121122</v>
       </c>
       <c r="M24">
-        <v>0.56237322854998939</v>
+        <v>0.56237322674936752</v>
       </c>
       <c r="N24">
         <v>5</v>
@@ -13247,10 +13251,10 @@
         <v>922</v>
       </c>
       <c r="L25">
-        <v>0.46124999999999999</v>
+        <v>0.38951433163922239</v>
       </c>
       <c r="M25">
-        <v>0.55710716413016503</v>
+        <v>0.55710716230137103</v>
       </c>
       <c r="N25">
         <v>3</v>
@@ -13321,10 +13325,10 @@
         <v>922</v>
       </c>
       <c r="L26">
-        <v>4.9500000000000002E-2</v>
+        <v>4.3215946809536276E-2</v>
       </c>
       <c r="M26">
-        <v>0.55635082012599812</v>
+        <v>0.55635081771492767</v>
       </c>
       <c r="N26">
         <v>4</v>
@@ -13360,7 +13364,7 @@
         <v>5.7404999999999999</v>
       </c>
       <c r="AA26">
-        <v>0.57239406110255531</v>
+        <v>0.57239406110255542</v>
       </c>
       <c r="AB26">
         <v>2</v>
@@ -13395,10 +13399,10 @@
         <v>922</v>
       </c>
       <c r="L27">
-        <v>0.15975</v>
+        <v>0.13092397622935031</v>
       </c>
       <c r="M27">
-        <v>0.545360149509863</v>
+        <v>0.54536014784355391</v>
       </c>
       <c r="N27">
         <v>1</v>
@@ -13469,10 +13473,10 @@
         <v>922</v>
       </c>
       <c r="L28">
-        <v>5.2499999999999998E-2</v>
+        <v>4.2996529332736233E-2</v>
       </c>
       <c r="M28">
-        <v>0.53432561998946648</v>
+        <v>0.53432561821500124</v>
       </c>
       <c r="N28">
         <v>1</v>
@@ -13546,7 +13550,7 @@
         <v>7.5000000000000002E-4</v>
       </c>
       <c r="M29">
-        <v>0.52865787228189332</v>
+        <v>0.52865787056997116</v>
       </c>
       <c r="N29">
         <v>2</v>
@@ -13620,7 +13624,7 @@
         <v>7.5000000000000002E-4</v>
       </c>
       <c r="M30">
-        <v>0.5215625542168375</v>
+        <v>0.52156255229486714</v>
       </c>
       <c r="N30">
         <v>2</v>
@@ -13691,10 +13695,10 @@
         <v>922</v>
       </c>
       <c r="L31">
-        <v>5.9340000000000002</v>
+        <v>3.341914764079148</v>
       </c>
       <c r="M31">
-        <v>0.51949433459974392</v>
+        <v>0.51949432908386783</v>
       </c>
       <c r="N31">
         <v>1</v>
@@ -13765,10 +13769,10 @@
         <v>922</v>
       </c>
       <c r="L32">
-        <v>0.30299999999999999</v>
+        <v>0.17379909840441307</v>
       </c>
       <c r="M32">
-        <v>0.51630420272381816</v>
+        <v>0.51630420077462136</v>
       </c>
       <c r="N32">
         <v>3</v>
@@ -13839,10 +13843,10 @@
         <v>922</v>
       </c>
       <c r="L33">
-        <v>5.8695000000000004</v>
+        <v>3.3044102416717789</v>
       </c>
       <c r="M33">
-        <v>0.5109109842815821</v>
+        <v>0.5109109791957519</v>
       </c>
       <c r="N33">
         <v>1</v>
@@ -13913,10 +13917,10 @@
         <v>922</v>
       </c>
       <c r="L34">
-        <v>5.8695000000000004</v>
+        <v>3.353761638058252</v>
       </c>
       <c r="M34">
-        <v>0.51063261051096276</v>
+        <v>0.51063260823194079</v>
       </c>
       <c r="N34">
         <v>3</v>
@@ -13987,10 +13991,10 @@
         <v>922</v>
       </c>
       <c r="L35">
-        <v>0.16500000000000001</v>
+        <v>0.13104981237138361</v>
       </c>
       <c r="M35">
-        <v>0.50721316092506397</v>
+        <v>0.5072131580863396</v>
       </c>
       <c r="N35">
         <v>4</v>
@@ -14061,10 +14065,10 @@
         <v>922</v>
       </c>
       <c r="L36">
-        <v>5.9340000000000002</v>
+        <v>3.3330770910312388</v>
       </c>
       <c r="M36">
-        <v>0.50614587446947323</v>
+        <v>0.50614587052557725</v>
       </c>
       <c r="N36">
         <v>2</v>
@@ -14135,13 +14139,13 @@
         <v>922</v>
       </c>
       <c r="L37">
-        <v>8.9842499999999994</v>
+        <v>0.66978303185533905</v>
       </c>
       <c r="M37">
-        <v>0.50106949989397553</v>
+        <v>0.5010038588662864</v>
       </c>
       <c r="N37">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P37" t="s">
         <v>182</v>
@@ -14209,13 +14213,13 @@
         <v>922</v>
       </c>
       <c r="L38">
-        <v>1.1040000000000001</v>
+        <v>5.7663806934649511</v>
       </c>
       <c r="M38">
-        <v>0.50086577222882922</v>
+        <v>0.50062886902026227</v>
       </c>
       <c r="N38">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P38" t="s">
         <v>182</v>
@@ -14283,10 +14287,10 @@
         <v>922</v>
       </c>
       <c r="L39">
-        <v>17.737500000000001</v>
+        <v>11.047664970219605</v>
       </c>
       <c r="M39">
-        <v>0.49965242910083491</v>
+        <v>0.49974674831820759</v>
       </c>
       <c r="N39">
         <v>1</v>
@@ -14357,10 +14361,10 @@
         <v>922</v>
       </c>
       <c r="L40">
-        <v>17.8065</v>
+        <v>10.102418427242224</v>
       </c>
       <c r="M40">
-        <v>0.49746567280892046</v>
+        <v>0.49755228962339199</v>
       </c>
       <c r="N40">
         <v>3</v>
@@ -14396,7 +14400,7 @@
         <v>1.7070000000000001</v>
       </c>
       <c r="AA40">
-        <v>0.53226675449350658</v>
+        <v>0.53226675449350669</v>
       </c>
       <c r="AB40">
         <v>4</v>
@@ -14431,10 +14435,10 @@
         <v>922</v>
       </c>
       <c r="L41">
-        <v>11.95725</v>
+        <v>7.6259026745860261</v>
       </c>
       <c r="M41">
-        <v>0.4969131365545662</v>
+        <v>0.49682416849777378</v>
       </c>
       <c r="N41">
         <v>2</v>
@@ -14505,13 +14509,13 @@
         <v>922</v>
       </c>
       <c r="L42">
-        <v>2.40225</v>
+        <v>10.605725881247682</v>
       </c>
       <c r="M42">
-        <v>0.48990515287413083</v>
+        <v>0.48999173413799507</v>
       </c>
       <c r="N42">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P42" t="s">
         <v>182</v>
@@ -14579,13 +14583,13 @@
         <v>922</v>
       </c>
       <c r="L43">
-        <v>17.741250000000001</v>
+        <v>1.6929633554586949</v>
       </c>
       <c r="M43">
-        <v>0.48989228081421565</v>
+        <v>0.48981567221041555</v>
       </c>
       <c r="N43">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P43" t="s">
         <v>182</v>
@@ -14653,10 +14657,10 @@
         <v>922</v>
       </c>
       <c r="L44">
-        <v>17.737500000000001</v>
+        <v>9.7838471042311674</v>
       </c>
       <c r="M44">
-        <v>0.48950101047308336</v>
+        <v>0.48956018082844749</v>
       </c>
       <c r="N44">
         <v>3</v>
@@ -14727,10 +14731,10 @@
         <v>922</v>
       </c>
       <c r="L45">
-        <v>13.148250000000001</v>
+        <v>7.1980253624324062</v>
       </c>
       <c r="M45">
-        <v>0.48916680623308012</v>
+        <v>0.48926145320762304</v>
       </c>
       <c r="N45">
         <v>4</v>
@@ -14801,10 +14805,10 @@
         <v>922</v>
       </c>
       <c r="L46">
-        <v>23.736000000000001</v>
+        <v>13.470416636338188</v>
       </c>
       <c r="M46">
-        <v>0.48835164203777615</v>
+        <v>0.48832239710288644</v>
       </c>
       <c r="N46">
         <v>1</v>
@@ -14875,10 +14879,10 @@
         <v>922</v>
       </c>
       <c r="L47">
-        <v>17.8065</v>
+        <v>10.433206238455002</v>
       </c>
       <c r="M47">
-        <v>0.48149588377168073</v>
+        <v>0.4814970504741054</v>
       </c>
       <c r="N47">
         <v>3</v>
@@ -14949,10 +14953,10 @@
         <v>922</v>
       </c>
       <c r="L48">
-        <v>5.9595000000000002</v>
+        <v>3.0723343217391972</v>
       </c>
       <c r="M48">
-        <v>0.48132863869019787</v>
+        <v>0.48132709994634049</v>
       </c>
       <c r="N48">
         <v>5</v>
@@ -15023,10 +15027,10 @@
         <v>922</v>
       </c>
       <c r="L49">
-        <v>17.486999999999998</v>
+        <v>11.471519563175688</v>
       </c>
       <c r="M49">
-        <v>0.48113125852755839</v>
+        <v>0.48029156528711514</v>
       </c>
       <c r="N49">
         <v>1</v>
@@ -15097,10 +15101,10 @@
         <v>922</v>
       </c>
       <c r="L50">
-        <v>17.802</v>
+        <v>10.762978994723088</v>
       </c>
       <c r="M50">
-        <v>0.47981215607404626</v>
+        <v>0.47978138498051776</v>
       </c>
       <c r="N50">
         <v>2</v>
@@ -15171,10 +15175,10 @@
         <v>922</v>
       </c>
       <c r="L51">
-        <v>17.802</v>
+        <v>9.6856472658291999</v>
       </c>
       <c r="M51">
-        <v>0.47921471220324302</v>
+        <v>0.47916767150003053</v>
       </c>
       <c r="N51">
         <v>4</v>
@@ -15245,10 +15249,10 @@
         <v>922</v>
       </c>
       <c r="L52">
-        <v>17.81025</v>
+        <v>10.353243843650327</v>
       </c>
       <c r="M52">
-        <v>0.47093127840862853</v>
+        <v>0.47096150098761563</v>
       </c>
       <c r="N52">
         <v>2</v>
@@ -15319,10 +15323,10 @@
         <v>922</v>
       </c>
       <c r="L53">
-        <v>17.81025</v>
+        <v>10.048953818959767</v>
       </c>
       <c r="M53">
-        <v>0.47083436407202045</v>
+        <v>0.47087389111461986</v>
       </c>
       <c r="N53">
         <v>4</v>
@@ -15393,10 +15397,10 @@
         <v>922</v>
       </c>
       <c r="L54">
-        <v>1.9957499999999999</v>
+        <v>1.0959650410157522</v>
       </c>
       <c r="M54">
-        <v>0.47031861757026105</v>
+        <v>0.47032443961340414</v>
       </c>
       <c r="N54">
         <v>5</v>
@@ -15432,7 +15436,7 @@
         <v>6.7904999999999998</v>
       </c>
       <c r="AA54">
-        <v>0.5065478060352695</v>
+        <v>0.50654780603526961</v>
       </c>
       <c r="AB54">
         <v>5</v>
@@ -15467,10 +15471,10 @@
         <v>922</v>
       </c>
       <c r="L55">
-        <v>23.606999999999999</v>
+        <v>13.329659152549908</v>
       </c>
       <c r="M55">
-        <v>0.46782044034589471</v>
+        <v>0.46782141133952077</v>
       </c>
       <c r="N55">
         <v>1</v>
@@ -15506,7 +15510,7 @@
         <v>17.891249999999999</v>
       </c>
       <c r="AA55">
-        <v>0.50114523544848988</v>
+        <v>0.50114523544848999</v>
       </c>
       <c r="AB55">
         <v>1</v>
@@ -15541,10 +15545,10 @@
         <v>922</v>
       </c>
       <c r="L56">
-        <v>17.676749999999998</v>
+        <v>10.157918749921553</v>
       </c>
       <c r="M56">
-        <v>0.46751238214871627</v>
+        <v>0.46753792020288976</v>
       </c>
       <c r="N56">
         <v>3</v>
@@ -15615,10 +15619,10 @@
         <v>922</v>
       </c>
       <c r="L57">
-        <v>23.739750000000001</v>
+        <v>13.348318927609375</v>
       </c>
       <c r="M57">
-        <v>0.4630498633155925</v>
+        <v>0.46302561890629701</v>
       </c>
       <c r="N57">
         <v>3</v>
@@ -15689,10 +15693,10 @@
         <v>922</v>
       </c>
       <c r="L58">
-        <v>23.740500000000001</v>
+        <v>13.325756766618852</v>
       </c>
       <c r="M58">
-        <v>0.46251130146504743</v>
+        <v>0.46258292434483883</v>
       </c>
       <c r="N58">
         <v>2</v>
@@ -15728,7 +15732,7 @@
         <v>15.951000000000001</v>
       </c>
       <c r="AA58">
-        <v>0.49767170863041427</v>
+        <v>0.49767170863041432</v>
       </c>
       <c r="AB58">
         <v>5</v>
@@ -15763,10 +15767,10 @@
         <v>922</v>
       </c>
       <c r="L59">
-        <v>23.478000000000002</v>
+        <v>13.300174659703368</v>
       </c>
       <c r="M59">
-        <v>0.45892139428395828</v>
+        <v>0.45901270013229029</v>
       </c>
       <c r="N59">
         <v>1</v>
@@ -15837,10 +15841,10 @@
         <v>922</v>
       </c>
       <c r="L60">
-        <v>5.0332499999999998</v>
+        <v>3.8188756211613413</v>
       </c>
       <c r="M60">
-        <v>0.45890857748424191</v>
+        <v>0.45898415105817908</v>
       </c>
       <c r="N60">
         <v>5</v>
@@ -15911,10 +15915,10 @@
         <v>922</v>
       </c>
       <c r="L61">
-        <v>17.741250000000001</v>
+        <v>9.2556124975512866</v>
       </c>
       <c r="M61">
-        <v>0.45885026920250094</v>
+        <v>0.45876671347099568</v>
       </c>
       <c r="N61">
         <v>4</v>
@@ -15985,10 +15989,10 @@
         <v>922</v>
       </c>
       <c r="L62">
-        <v>23.551500000000001</v>
+        <v>14.347221182137892</v>
       </c>
       <c r="M62">
-        <v>0.45149689710153873</v>
+        <v>0.45181631366694031</v>
       </c>
       <c r="N62">
         <v>2</v>
@@ -16024,7 +16028,7 @@
         <v>12.6675</v>
       </c>
       <c r="AA62">
-        <v>0.49036787062623266</v>
+        <v>0.49036787062623272</v>
       </c>
       <c r="AB62">
         <v>2</v>
@@ -16059,10 +16063,10 @@
         <v>922</v>
       </c>
       <c r="L63">
-        <v>13.03425</v>
+        <v>6.7210710821965503</v>
       </c>
       <c r="M63">
-        <v>0.45074982073872027</v>
+        <v>0.45080430732290749</v>
       </c>
       <c r="N63">
         <v>5</v>
@@ -16098,7 +16102,7 @@
         <v>13.0425</v>
       </c>
       <c r="AA63">
-        <v>0.4897335035411165</v>
+        <v>0.48973350354111655</v>
       </c>
       <c r="AB63">
         <v>1</v>
@@ -16133,10 +16137,10 @@
         <v>922</v>
       </c>
       <c r="L64">
-        <v>23.671500000000002</v>
+        <v>12.895480996194033</v>
       </c>
       <c r="M64">
-        <v>0.45057329810451024</v>
+        <v>0.45053511697748189</v>
       </c>
       <c r="N64">
         <v>3</v>
@@ -16207,10 +16211,10 @@
         <v>922</v>
       </c>
       <c r="L65">
-        <v>29.286000000000001</v>
+        <v>17.299459029043469</v>
       </c>
       <c r="M65">
-        <v>0.45011752256525617</v>
+        <v>0.44994641348037995</v>
       </c>
       <c r="N65">
         <v>1</v>
@@ -16246,7 +16250,7 @@
         <v>7.0694999999999997</v>
       </c>
       <c r="AA65">
-        <v>0.48403449265347154</v>
+        <v>0.48403449265347165</v>
       </c>
       <c r="AB65">
         <v>2</v>
@@ -16281,10 +16285,10 @@
         <v>922</v>
       </c>
       <c r="L66">
-        <v>23.679749999999999</v>
+        <v>12.470827979769073</v>
       </c>
       <c r="M66">
-        <v>0.44905615851425007</v>
+        <v>0.44904522705904526</v>
       </c>
       <c r="N66">
         <v>4</v>
@@ -16355,10 +16359,10 @@
         <v>922</v>
       </c>
       <c r="L67">
-        <v>23.706</v>
+        <v>16.193844741484405</v>
       </c>
       <c r="M67">
-        <v>0.4416479948213704</v>
+        <v>0.44184462177531375</v>
       </c>
       <c r="N67">
         <v>3</v>
@@ -16429,10 +16433,10 @@
         <v>922</v>
       </c>
       <c r="L68">
-        <v>23.765999999999998</v>
+        <v>14.827928324911245</v>
       </c>
       <c r="M68">
-        <v>0.43988028649983019</v>
+        <v>0.43965218995973987</v>
       </c>
       <c r="N68">
         <v>2</v>
@@ -16503,10 +16507,10 @@
         <v>922</v>
       </c>
       <c r="L69">
-        <v>16.77675</v>
+        <v>9.4373054286010927</v>
       </c>
       <c r="M69">
-        <v>0.43930702269053656</v>
+        <v>0.43930365377612329</v>
       </c>
       <c r="N69">
         <v>4</v>
@@ -16542,7 +16546,7 @@
         <v>7.3155000000000001</v>
       </c>
       <c r="AA69">
-        <v>0.4765418657283671</v>
+        <v>0.47654186572836715</v>
       </c>
       <c r="AB69">
         <v>4</v>
@@ -16577,10 +16581,10 @@
         <v>922</v>
       </c>
       <c r="L70">
-        <v>35.406750000000002</v>
+        <v>22.6491231405561</v>
       </c>
       <c r="M70">
-        <v>0.43919474350182042</v>
+        <v>0.43925232488713145</v>
       </c>
       <c r="N70">
         <v>1</v>
@@ -16651,10 +16655,10 @@
         <v>922</v>
       </c>
       <c r="L71">
-        <v>4.7685000000000004</v>
+        <v>3.2103674431472191</v>
       </c>
       <c r="M71">
-        <v>0.4386795614772121</v>
+        <v>0.43894273408378509</v>
       </c>
       <c r="N71">
         <v>5</v>
@@ -16725,10 +16729,10 @@
         <v>922</v>
       </c>
       <c r="L72">
-        <v>17.8065</v>
+        <v>9.9234549869009143</v>
       </c>
       <c r="M72">
-        <v>0.43114733236674907</v>
+        <v>0.43115514974838204</v>
       </c>
       <c r="N72">
         <v>1</v>
@@ -16799,10 +16803,10 @@
         <v>922</v>
       </c>
       <c r="L73">
-        <v>17.741250000000001</v>
+        <v>9.4994342733342645</v>
       </c>
       <c r="M73">
-        <v>0.42976464542140597</v>
+        <v>0.42975309551324303</v>
       </c>
       <c r="N73">
         <v>2</v>
@@ -16838,7 +16842,7 @@
         <v>6.4275000000000002</v>
       </c>
       <c r="AA73">
-        <v>0.46805797856755366</v>
+        <v>0.46805797856755371</v>
       </c>
       <c r="AB73">
         <v>1</v>
@@ -16873,10 +16877,10 @@
         <v>922</v>
       </c>
       <c r="L74">
-        <v>2.4239999999999999</v>
+        <v>1.4227544237807934</v>
       </c>
       <c r="M74">
-        <v>0.42830469748032096</v>
+        <v>0.42830005814755961</v>
       </c>
       <c r="N74">
         <v>5</v>
@@ -16947,10 +16951,10 @@
         <v>922</v>
       </c>
       <c r="L75">
-        <v>17.870999999999999</v>
+        <v>9.4008852473651299</v>
       </c>
       <c r="M75">
-        <v>0.42687980763490108</v>
+        <v>0.42692493403844806</v>
       </c>
       <c r="N75">
         <v>3</v>
@@ -17021,10 +17025,10 @@
         <v>922</v>
       </c>
       <c r="L76">
-        <v>5.8724999999999996</v>
+        <v>3.1703904737329776</v>
       </c>
       <c r="M76">
-        <v>0.42590251897690873</v>
+        <v>0.42590256665860216</v>
       </c>
       <c r="N76">
         <v>4</v>
@@ -17095,10 +17099,10 @@
         <v>922</v>
       </c>
       <c r="L77">
-        <v>16.413</v>
+        <v>8.5688781791325361</v>
       </c>
       <c r="M77">
-        <v>0.42157984655488412</v>
+        <v>0.42161285575070945</v>
       </c>
       <c r="N77">
         <v>5</v>
@@ -17169,10 +17173,10 @@
         <v>922</v>
       </c>
       <c r="L78">
-        <v>29.493749999999999</v>
+        <v>17.303180091586601</v>
       </c>
       <c r="M78">
-        <v>0.42143962829609694</v>
+        <v>0.42094158535265797</v>
       </c>
       <c r="N78">
         <v>2</v>
@@ -17243,10 +17247,10 @@
         <v>922</v>
       </c>
       <c r="L79">
-        <v>35.414250000000003</v>
+        <v>18.977798585665102</v>
       </c>
       <c r="M79">
-        <v>0.42082982066705193</v>
+        <v>0.42092804048998211</v>
       </c>
       <c r="N79">
         <v>3</v>
@@ -17317,10 +17321,10 @@
         <v>922</v>
       </c>
       <c r="L80">
-        <v>35.403750000000002</v>
+        <v>21.825808720333217</v>
       </c>
       <c r="M80">
-        <v>0.42030333378341062</v>
+        <v>0.41996865634729214</v>
       </c>
       <c r="N80">
         <v>1</v>
@@ -17391,10 +17395,10 @@
         <v>922</v>
       </c>
       <c r="L81">
-        <v>23.748000000000001</v>
+        <v>12.219159041356059</v>
       </c>
       <c r="M81">
-        <v>0.41944297765388372</v>
+        <v>0.41937195022412854</v>
       </c>
       <c r="N81">
         <v>4</v>
@@ -17465,10 +17469,10 @@
         <v>922</v>
       </c>
       <c r="L82">
-        <v>30.764250000000001</v>
+        <v>18.223383100809652</v>
       </c>
       <c r="M82">
-        <v>0.41323098400442321</v>
+        <v>0.41336707529684547</v>
       </c>
       <c r="N82">
         <v>4</v>
@@ -17539,10 +17543,10 @@
         <v>922</v>
       </c>
       <c r="L83">
-        <v>19.460999999999999</v>
+        <v>10.536151723524661</v>
       </c>
       <c r="M83">
-        <v>0.40962586208647273</v>
+        <v>0.40941311048281098</v>
       </c>
       <c r="N83">
         <v>5</v>
@@ -17613,10 +17617,10 @@
         <v>922</v>
       </c>
       <c r="L84">
-        <v>35.472000000000001</v>
+        <v>20.03073548531842</v>
       </c>
       <c r="M84">
-        <v>0.40958884965111214</v>
+        <v>0.40941092642806876</v>
       </c>
       <c r="N84">
         <v>2</v>
@@ -17652,7 +17656,7 @@
         <v>1.0785</v>
       </c>
       <c r="AA84">
-        <v>0.44899933226467581</v>
+        <v>0.44899933226467592</v>
       </c>
       <c r="AB84">
         <v>5</v>
@@ -17687,10 +17691,10 @@
         <v>922</v>
       </c>
       <c r="L85">
-        <v>41.498249999999999</v>
+        <v>24.821666198155651</v>
       </c>
       <c r="M85">
-        <v>0.4088568941222287</v>
+        <v>0.40892732477976118</v>
       </c>
       <c r="N85">
         <v>1</v>
@@ -17761,10 +17765,10 @@
         <v>922</v>
       </c>
       <c r="L86">
-        <v>23.72025</v>
+        <v>12.965360848715605</v>
       </c>
       <c r="M86">
-        <v>0.40770220593031037</v>
+        <v>0.40771293459767738</v>
       </c>
       <c r="N86">
         <v>3</v>
@@ -17835,10 +17839,10 @@
         <v>922</v>
       </c>
       <c r="L87">
-        <v>41.554499999999997</v>
+        <v>23.18717705428347</v>
       </c>
       <c r="M87">
-        <v>0.40098440951339731</v>
+        <v>0.40094156726404773</v>
       </c>
       <c r="N87">
         <v>1</v>
@@ -17909,10 +17913,10 @@
         <v>922</v>
       </c>
       <c r="L88">
-        <v>29.891249999999999</v>
+        <v>17.130346163442326</v>
       </c>
       <c r="M88">
-        <v>0.39978391956724274</v>
+        <v>0.39950712957218243</v>
       </c>
       <c r="N88">
         <v>3</v>
@@ -17983,10 +17987,10 @@
         <v>922</v>
       </c>
       <c r="L89">
-        <v>35.739750000000001</v>
+        <v>20.494671792745176</v>
       </c>
       <c r="M89">
-        <v>0.39862786865924016</v>
+        <v>0.39858720214068633</v>
       </c>
       <c r="N89">
         <v>2</v>
@@ -18057,10 +18061,10 @@
         <v>922</v>
       </c>
       <c r="L90">
-        <v>30.126750000000001</v>
+        <v>17.227124048907491</v>
       </c>
       <c r="M90">
-        <v>0.39775867469730281</v>
+        <v>0.39783780382631279</v>
       </c>
       <c r="N90">
         <v>4</v>
@@ -18131,10 +18135,10 @@
         <v>922</v>
       </c>
       <c r="L91">
-        <v>18.143249999999998</v>
+        <v>9.0939754139292202</v>
       </c>
       <c r="M91">
-        <v>0.39718977026524266</v>
+        <v>0.39714672529558576</v>
       </c>
       <c r="N91">
         <v>5</v>
@@ -18205,10 +18209,10 @@
         <v>922</v>
       </c>
       <c r="L92">
-        <v>46.96125</v>
+        <v>30.407733052479134</v>
       </c>
       <c r="M92">
-        <v>0.39118151610275709</v>
+        <v>0.39135874299273238</v>
       </c>
       <c r="N92">
         <v>1</v>
@@ -18244,7 +18248,7 @@
         <v>0.85799999999999998</v>
       </c>
       <c r="AA92">
-        <v>0.42871807904168541</v>
+        <v>0.42871807904168552</v>
       </c>
       <c r="AB92">
         <v>5</v>
@@ -18279,10 +18283,10 @@
         <v>922</v>
       </c>
       <c r="L93">
-        <v>41.219250000000002</v>
+        <v>21.755259375981495</v>
       </c>
       <c r="M93">
-        <v>0.39062965885933243</v>
+        <v>0.39061674889015757</v>
       </c>
       <c r="N93">
         <v>4</v>
@@ -18353,10 +18357,10 @@
         <v>922</v>
       </c>
       <c r="L94">
-        <v>41.553750000000001</v>
+        <v>22.022352292565671</v>
       </c>
       <c r="M94">
-        <v>0.38944460675085768</v>
+        <v>0.38940464262012414</v>
       </c>
       <c r="N94">
         <v>2</v>
@@ -18392,7 +18396,7 @@
         <v>1.5967499999999999</v>
       </c>
       <c r="AA94">
-        <v>0.42655410238306979</v>
+        <v>0.42655410238306984</v>
       </c>
       <c r="AB94">
         <v>4</v>
@@ -18427,10 +18431,10 @@
         <v>922</v>
       </c>
       <c r="L95">
-        <v>23.364000000000001</v>
+        <v>11.666752719288366</v>
       </c>
       <c r="M95">
-        <v>0.38849299529783043</v>
+        <v>0.38843940231152729</v>
       </c>
       <c r="N95">
         <v>5</v>
@@ -18466,7 +18470,7 @@
         <v>6.7575000000000003</v>
       </c>
       <c r="AA95">
-        <v>0.42309662134762832</v>
+        <v>0.42309662134762843</v>
       </c>
       <c r="AB95">
         <v>3</v>
@@ -18501,10 +18505,10 @@
         <v>922</v>
       </c>
       <c r="L96">
-        <v>41.413499999999999</v>
+        <v>21.744306295288464</v>
       </c>
       <c r="M96">
-        <v>0.38707060161567797</v>
+        <v>0.38706987762907791</v>
       </c>
       <c r="N96">
         <v>3</v>
@@ -18540,7 +18544,7 @@
         <v>14.321999999999999</v>
       </c>
       <c r="AA96">
-        <v>0.42291994675360034</v>
+        <v>0.4229199467536004</v>
       </c>
       <c r="AB96">
         <v>1</v>
@@ -18575,10 +18579,10 @@
         <v>922</v>
       </c>
       <c r="L97">
-        <v>59.119500000000002</v>
+        <v>32.953996481253249</v>
       </c>
       <c r="M97">
-        <v>0.3813461110865321</v>
+        <v>0.38106916272962216</v>
       </c>
       <c r="N97">
         <v>2</v>
@@ -18649,10 +18653,10 @@
         <v>922</v>
       </c>
       <c r="L98">
-        <v>59.019750000000002</v>
+        <v>29.958880260827321</v>
       </c>
       <c r="M98">
-        <v>0.38107281998592235</v>
+        <v>0.38104931836357381</v>
       </c>
       <c r="N98">
         <v>4</v>
@@ -18723,10 +18727,10 @@
         <v>922</v>
       </c>
       <c r="L99">
-        <v>58.838999999999999</v>
+        <v>36.312680266700461</v>
       </c>
       <c r="M99">
-        <v>0.37950051251458461</v>
+        <v>0.37957211788730438</v>
       </c>
       <c r="N99">
         <v>1</v>
@@ -18762,7 +18766,7 @@
         <v>8.7210000000000001</v>
       </c>
       <c r="AA99">
-        <v>0.41755003769793275</v>
+        <v>0.41755003769793281</v>
       </c>
       <c r="AB99">
         <v>5</v>
@@ -18797,10 +18801,10 @@
         <v>922</v>
       </c>
       <c r="L100">
-        <v>42.46575</v>
+        <v>24.886150918941393</v>
       </c>
       <c r="M100">
-        <v>0.37948859046251615</v>
+        <v>0.37925543822883045</v>
       </c>
       <c r="N100">
         <v>5</v>
@@ -18836,7 +18840,7 @@
         <v>2.823</v>
       </c>
       <c r="AA100">
-        <v>0.41117036009061475</v>
+        <v>0.41117036009061486</v>
       </c>
       <c r="AB100">
         <v>1</v>
@@ -18871,10 +18875,10 @@
         <v>922</v>
       </c>
       <c r="L101">
-        <v>47.300249999999998</v>
+        <v>25.255594944766283</v>
       </c>
       <c r="M101">
-        <v>0.37843995981140421</v>
+        <v>0.37834528155156893</v>
       </c>
       <c r="N101">
         <v>3</v>
@@ -18945,10 +18949,10 @@
         <v>922</v>
       </c>
       <c r="L102">
-        <v>77.404499999999999</v>
+        <v>42.273918168311852</v>
       </c>
       <c r="M102">
-        <v>0.37119226670004923</v>
+        <v>0.37110054829200473</v>
       </c>
       <c r="N102">
         <v>2</v>
@@ -18984,7 +18988,7 @@
         <v>15.22425</v>
       </c>
       <c r="AA102">
-        <v>0.41055528608792502</v>
+        <v>0.41055528608792508</v>
       </c>
       <c r="AB102">
         <v>2</v>
@@ -19019,10 +19023,10 @@
         <v>922</v>
       </c>
       <c r="L103">
-        <v>66.941999999999993</v>
+        <v>38.44297710574476</v>
       </c>
       <c r="M103">
-        <v>0.37024543509476515</v>
+        <v>0.37010452288068035</v>
       </c>
       <c r="N103">
         <v>5</v>
@@ -19093,10 +19097,10 @@
         <v>922</v>
       </c>
       <c r="L104">
-        <v>78.710999999999999</v>
+        <v>40.705144107883811</v>
       </c>
       <c r="M104">
-        <v>0.36944644578132163</v>
+        <v>0.36945149830372176</v>
       </c>
       <c r="N104">
         <v>4</v>
@@ -19167,10 +19171,10 @@
         <v>922</v>
       </c>
       <c r="L105">
-        <v>81.733500000000006</v>
+        <v>51.084350358754136</v>
       </c>
       <c r="M105">
-        <v>0.36942348320593565</v>
+        <v>0.36925954676245526</v>
       </c>
       <c r="N105">
         <v>1</v>
@@ -19206,7 +19210,7 @@
         <v>21.75375</v>
       </c>
       <c r="AA105">
-        <v>0.40189609626240203</v>
+        <v>0.40189609626240208</v>
       </c>
       <c r="AB105">
         <v>2</v>
@@ -19241,10 +19245,10 @@
         <v>922</v>
       </c>
       <c r="L106">
-        <v>83.291250000000005</v>
+        <v>42.935266883187538</v>
       </c>
       <c r="M106">
-        <v>0.36899186228202219</v>
+        <v>0.36898034891749865</v>
       </c>
       <c r="N106">
         <v>3</v>
@@ -19280,7 +19284,7 @@
         <v>7.0207499999999996</v>
       </c>
       <c r="AA106">
-        <v>0.39938411821735487</v>
+        <v>0.39938411821735492</v>
       </c>
       <c r="AB106">
         <v>5</v>
@@ -19315,10 +19319,10 @@
         <v>922</v>
       </c>
       <c r="L107">
-        <v>77.020499999999998</v>
+        <v>42.608191603357923</v>
       </c>
       <c r="M107">
-        <v>0.3616033931090909</v>
+        <v>0.36164460265992293</v>
       </c>
       <c r="N107">
         <v>1</v>
@@ -19389,10 +19393,10 @@
         <v>922</v>
       </c>
       <c r="L108">
-        <v>66.008250000000004</v>
+        <v>34.179867218390292</v>
       </c>
       <c r="M108">
-        <v>0.3607114446375434</v>
+        <v>0.36071575852664622</v>
       </c>
       <c r="N108">
         <v>2</v>
@@ -19463,10 +19467,10 @@
         <v>922</v>
       </c>
       <c r="L109">
-        <v>42.39</v>
+        <v>28.31812972121531</v>
       </c>
       <c r="M109">
-        <v>0.3601970216911618</v>
+        <v>0.36035353063665204</v>
       </c>
       <c r="N109">
         <v>5</v>
@@ -19537,10 +19541,10 @@
         <v>922</v>
       </c>
       <c r="L110">
-        <v>70.415999999999997</v>
+        <v>39.02873821267282</v>
       </c>
       <c r="M110">
-        <v>0.35928366363805941</v>
+        <v>0.35928012120836633</v>
       </c>
       <c r="N110">
         <v>3</v>
@@ -19611,10 +19615,10 @@
         <v>922</v>
       </c>
       <c r="L111">
-        <v>71.025750000000002</v>
+        <v>36.84068065231974</v>
       </c>
       <c r="M111">
-        <v>0.35814371426049924</v>
+        <v>0.35804151944481616</v>
       </c>
       <c r="N111">
         <v>4</v>
@@ -19685,10 +19689,10 @@
         <v>922</v>
       </c>
       <c r="L112">
-        <v>71.028750000000002</v>
+        <v>39.242744105869953</v>
       </c>
       <c r="M112">
-        <v>0.35092489759674045</v>
+        <v>0.35091563643356449</v>
       </c>
       <c r="N112">
         <v>2</v>
@@ -19724,7 +19728,7 @@
         <v>3.1604999999999999</v>
       </c>
       <c r="AA112">
-        <v>0.38977971714041637</v>
+        <v>0.38977971714041648</v>
       </c>
       <c r="AB112">
         <v>5</v>
@@ -19759,10 +19763,10 @@
         <v>922</v>
       </c>
       <c r="L113">
-        <v>64.624499999999998</v>
+        <v>32.138377620976584</v>
       </c>
       <c r="M113">
-        <v>0.35027313474305577</v>
+        <v>0.35029110311071943</v>
       </c>
       <c r="N113">
         <v>4</v>
@@ -19798,7 +19802,7 @@
         <v>11.132250000000001</v>
       </c>
       <c r="AA113">
-        <v>0.38924363673453144</v>
+        <v>0.38924363673453155</v>
       </c>
       <c r="AB113">
         <v>3</v>
@@ -19833,13 +19837,13 @@
         <v>922</v>
       </c>
       <c r="L114">
-        <v>70.877250000000004</v>
+        <v>25.537184747042165</v>
       </c>
       <c r="M114">
-        <v>0.34984700035493194</v>
+        <v>0.3499543099888896</v>
       </c>
       <c r="N114">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P114" t="s">
         <v>182</v>
@@ -19872,7 +19876,7 @@
         <v>8.1277500000000007</v>
       </c>
       <c r="AA114">
-        <v>0.38887930155903361</v>
+        <v>0.38887930155903372</v>
       </c>
       <c r="AB114">
         <v>4</v>
@@ -19907,13 +19911,13 @@
         <v>922</v>
       </c>
       <c r="L115">
-        <v>70.356750000000005</v>
+        <v>38.16220978791273</v>
       </c>
       <c r="M115">
-        <v>0.34984430983973785</v>
+        <v>0.34975920719770837</v>
       </c>
       <c r="N115">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P115" t="s">
         <v>182</v>
@@ -19981,13 +19985,13 @@
         <v>922</v>
       </c>
       <c r="L116">
-        <v>40.896749999999997</v>
+        <v>41.951580711940309</v>
       </c>
       <c r="M116">
-        <v>0.34958949757220614</v>
+        <v>0.34964441753332443</v>
       </c>
       <c r="N116">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P116" t="s">
         <v>182</v>
@@ -20055,13 +20059,13 @@
         <v>922</v>
       </c>
       <c r="L117">
-        <v>94.745249999999999</v>
+        <v>53.200102509498095</v>
       </c>
       <c r="M117">
-        <v>0.34015518491128016</v>
+        <v>0.34017040159656159</v>
       </c>
       <c r="N117">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P117" t="s">
         <v>182</v>
@@ -20129,13 +20133,13 @@
         <v>922</v>
       </c>
       <c r="L118">
-        <v>100.63200000000001</v>
+        <v>49.351681131628126</v>
       </c>
       <c r="M118">
-        <v>0.34012864073636589</v>
+        <v>0.33996305416884076</v>
       </c>
       <c r="N118">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P118" t="s">
         <v>182</v>
@@ -20203,10 +20207,10 @@
         <v>922</v>
       </c>
       <c r="L119">
-        <v>75.638999999999996</v>
+        <v>39.584340473432185</v>
       </c>
       <c r="M119">
-        <v>0.33988021267469376</v>
+        <v>0.33974528163945938</v>
       </c>
       <c r="N119">
         <v>5</v>
@@ -20242,7 +20246,7 @@
         <v>26.511749999999999</v>
       </c>
       <c r="AA119">
-        <v>0.37937884565930563</v>
+        <v>0.37937884565930569</v>
       </c>
       <c r="AB119">
         <v>2</v>
@@ -20277,10 +20281,10 @@
         <v>922</v>
       </c>
       <c r="L120">
-        <v>95.090249999999997</v>
+        <v>55.538971663240396</v>
       </c>
       <c r="M120">
-        <v>0.33943444486777308</v>
+        <v>0.33947533343302821</v>
       </c>
       <c r="N120">
         <v>1</v>
@@ -20316,7 +20320,7 @@
         <v>1.6897500000000001</v>
       </c>
       <c r="AA120">
-        <v>0.37392073169343748</v>
+        <v>0.37392073169343754</v>
       </c>
       <c r="AB120">
         <v>5</v>
@@ -20351,10 +20355,10 @@
         <v>922</v>
       </c>
       <c r="L121">
-        <v>94.86</v>
+        <v>53.304301331839063</v>
       </c>
       <c r="M121">
-        <v>0.33887544040528483</v>
+        <v>0.33896658312307171</v>
       </c>
       <c r="N121">
         <v>3</v>
@@ -20425,10 +20429,10 @@
         <v>922</v>
       </c>
       <c r="L122">
-        <v>53.286000000000001</v>
+        <v>26.759112324687965</v>
       </c>
       <c r="M122">
-        <v>0.33092718252940678</v>
+        <v>0.33076277823483596</v>
       </c>
       <c r="N122">
         <v>4</v>
@@ -20464,7 +20468,7 @@
         <v>6.6352500000000001</v>
       </c>
       <c r="AA122">
-        <v>0.37241340340320545</v>
+        <v>0.37241340340320556</v>
       </c>
       <c r="AB122">
         <v>3</v>
@@ -20499,10 +20503,10 @@
         <v>922</v>
       </c>
       <c r="L123">
-        <v>59.436</v>
+        <v>33.603230890274155</v>
       </c>
       <c r="M123">
-        <v>0.33086298005501658</v>
+        <v>0.33068230599000187</v>
       </c>
       <c r="N123">
         <v>1</v>
@@ -20538,7 +20542,7 @@
         <v>8.58</v>
       </c>
       <c r="AA123">
-        <v>0.37006727711506665</v>
+        <v>0.37006727711506676</v>
       </c>
       <c r="AB123">
         <v>4</v>
@@ -20573,10 +20577,10 @@
         <v>922</v>
       </c>
       <c r="L124">
-        <v>58.931249999999999</v>
+        <v>32.896233043608959</v>
       </c>
       <c r="M124">
-        <v>0.33001120149017982</v>
+        <v>0.32978117268196083</v>
       </c>
       <c r="N124">
         <v>2</v>
@@ -20612,7 +20616,7 @@
         <v>12.824999999999999</v>
       </c>
       <c r="AA124">
-        <v>0.36750616988492685</v>
+        <v>0.3675061698849269</v>
       </c>
       <c r="AB124">
         <v>2</v>
@@ -20647,13 +20651,13 @@
         <v>922</v>
       </c>
       <c r="L125">
-        <v>39.170999999999999</v>
+        <v>32.751571181111828</v>
       </c>
       <c r="M125">
-        <v>0.32974085660223451</v>
+        <v>0.32960318941176775</v>
       </c>
       <c r="N125">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P125" t="s">
         <v>182</v>
@@ -20721,13 +20725,13 @@
         <v>922</v>
       </c>
       <c r="L126">
-        <v>59.048999999999999</v>
+        <v>21.130869553020808</v>
       </c>
       <c r="M126">
-        <v>0.32951346580140822</v>
+        <v>0.32959827002215253</v>
       </c>
       <c r="N126">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P126" t="s">
         <v>182</v>
@@ -20795,10 +20799,10 @@
         <v>922</v>
       </c>
       <c r="L127">
-        <v>71.131500000000003</v>
+        <v>40.085652476306208</v>
       </c>
       <c r="M127">
-        <v>0.32036273743508448</v>
+        <v>0.32045105073361269</v>
       </c>
       <c r="N127">
         <v>1</v>
@@ -20869,10 +20873,10 @@
         <v>922</v>
       </c>
       <c r="L128">
-        <v>71.368499999999997</v>
+        <v>37.669823485156506</v>
       </c>
       <c r="M128">
-        <v>0.32009349967578732</v>
+        <v>0.32010600243370302</v>
       </c>
       <c r="N128">
         <v>2</v>
@@ -20908,7 +20912,7 @@
         <v>3.0945</v>
       </c>
       <c r="AA128">
-        <v>0.35772015097402765</v>
+        <v>0.35772015097402771</v>
       </c>
       <c r="AB128">
         <v>2</v>
@@ -20943,10 +20947,10 @@
         <v>922</v>
       </c>
       <c r="L129">
-        <v>63.828000000000003</v>
+        <v>32.077618164563916</v>
       </c>
       <c r="M129">
-        <v>0.31975520687153908</v>
+        <v>0.31983627866682268</v>
       </c>
       <c r="N129">
         <v>4</v>
@@ -20982,7 +20986,7 @@
         <v>8.4000000000000005E-2</v>
       </c>
       <c r="AA129">
-        <v>0.35622690324789652</v>
+        <v>0.35622690324789658</v>
       </c>
       <c r="AB129">
         <v>5</v>
@@ -21017,10 +21021,10 @@
         <v>922</v>
       </c>
       <c r="L130">
-        <v>53.203499999999998</v>
+        <v>27.160209741542147</v>
       </c>
       <c r="M130">
-        <v>0.3196702743240657</v>
+        <v>0.31974727606552916</v>
       </c>
       <c r="N130">
         <v>5</v>
@@ -21091,10 +21095,10 @@
         <v>922</v>
       </c>
       <c r="L131">
-        <v>64.962000000000003</v>
+        <v>33.805194924169228</v>
       </c>
       <c r="M131">
-        <v>0.31859830125340571</v>
+        <v>0.31843906852672871</v>
       </c>
       <c r="N131">
         <v>3</v>
@@ -21165,10 +21169,10 @@
         <v>922</v>
       </c>
       <c r="L132">
-        <v>71.277000000000001</v>
+        <v>37.521593073295762</v>
       </c>
       <c r="M132">
-        <v>0.31075558233528766</v>
+        <v>0.31084987126552316</v>
       </c>
       <c r="N132">
         <v>1</v>
@@ -21239,10 +21243,10 @@
         <v>922</v>
       </c>
       <c r="L133">
-        <v>67.995000000000005</v>
+        <v>41.141494286608506</v>
       </c>
       <c r="M133">
-        <v>0.31005773417071453</v>
+        <v>0.31010691441943339</v>
       </c>
       <c r="N133">
         <v>4</v>
@@ -21313,10 +21317,10 @@
         <v>922</v>
       </c>
       <c r="L134">
-        <v>71.139750000000006</v>
+        <v>39.216478948842472</v>
       </c>
       <c r="M134">
-        <v>0.30929414328643312</v>
+        <v>0.30917142764969396</v>
       </c>
       <c r="N134">
         <v>3</v>
@@ -21387,10 +21391,10 @@
         <v>922</v>
       </c>
       <c r="L135">
-        <v>71.15925</v>
+        <v>37.77151859340816</v>
       </c>
       <c r="M135">
-        <v>0.30880991387157924</v>
+        <v>0.30880285507938232</v>
       </c>
       <c r="N135">
         <v>2</v>
@@ -21461,10 +21465,10 @@
         <v>922</v>
       </c>
       <c r="L136">
-        <v>51.768749999999997</v>
+        <v>31.302438677717543</v>
       </c>
       <c r="M136">
-        <v>0.30841986999148591</v>
+        <v>0.30827856525919373</v>
       </c>
       <c r="N136">
         <v>5</v>
@@ -21535,10 +21539,10 @@
         <v>922</v>
       </c>
       <c r="L137">
-        <v>65.295000000000002</v>
+        <v>37.097669638785547</v>
       </c>
       <c r="M137">
-        <v>0.30124286676845452</v>
+        <v>0.30101913785402795</v>
       </c>
       <c r="N137">
         <v>1</v>
@@ -21609,10 +21613,10 @@
         <v>922</v>
       </c>
       <c r="L138">
-        <v>61.061999999999998</v>
+        <v>32.770146664552847</v>
       </c>
       <c r="M138">
-        <v>0.30044952285919008</v>
+        <v>0.30046993969416158</v>
       </c>
       <c r="N138">
         <v>2</v>
@@ -21683,13 +21687,13 @@
         <v>922</v>
       </c>
       <c r="L139">
-        <v>41.619750000000003</v>
+        <v>32.081112851878913</v>
       </c>
       <c r="M139">
-        <v>0.29992506546722875</v>
+        <v>0.2998752543683938</v>
       </c>
       <c r="N139">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P139" t="s">
         <v>182</v>
@@ -21757,13 +21761,13 @@
         <v>922</v>
       </c>
       <c r="L140">
-        <v>57.588749999999997</v>
+        <v>36.154129129437038</v>
       </c>
       <c r="M140">
-        <v>0.29990587239789068</v>
+        <v>0.29984953362719946</v>
       </c>
       <c r="N140">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P140" t="s">
         <v>182</v>
@@ -21831,13 +21835,13 @@
         <v>922</v>
       </c>
       <c r="L141">
-        <v>65.130750000000006</v>
+        <v>23.062898402080666</v>
       </c>
       <c r="M141">
-        <v>0.29985517826341712</v>
+        <v>0.29954553805027362</v>
       </c>
       <c r="N141">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P141" t="s">
         <v>182</v>
@@ -21905,10 +21909,10 @@
         <v>922</v>
       </c>
       <c r="L142">
-        <v>75.5685</v>
+        <v>44.882518758630461</v>
       </c>
       <c r="M142">
-        <v>0.29042830466947783</v>
+        <v>0.29061796963342829</v>
       </c>
       <c r="N142">
         <v>4</v>
@@ -21944,7 +21948,7 @@
         <v>5.742</v>
       </c>
       <c r="AA142">
-        <v>0.32419515610022792</v>
+        <v>0.32419515610022798</v>
       </c>
       <c r="AB142">
         <v>3</v>
@@ -21979,13 +21983,13 @@
         <v>922</v>
       </c>
       <c r="L143">
-        <v>76.794749999999993</v>
+        <v>42.248819582983813</v>
       </c>
       <c r="M143">
-        <v>0.29009207136591753</v>
+        <v>0.28999896581300139</v>
       </c>
       <c r="N143">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P143" t="s">
         <v>182</v>
@@ -22053,13 +22057,13 @@
         <v>922</v>
       </c>
       <c r="L144">
-        <v>80.862750000000005</v>
+        <v>44.051726893746462</v>
       </c>
       <c r="M144">
-        <v>0.29003486395218564</v>
+        <v>0.28995024139369102</v>
       </c>
       <c r="N144">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P144" t="s">
         <v>182</v>
@@ -22092,7 +22096,7 @@
         <v>11.417999999999999</v>
       </c>
       <c r="AA144">
-        <v>0.32207157769292166</v>
+        <v>0.32207157769292172</v>
       </c>
       <c r="AB144">
         <v>2</v>
@@ -22127,10 +22131,10 @@
         <v>922</v>
       </c>
       <c r="L145">
-        <v>64.896749999999997</v>
+        <v>37.668643433859806</v>
       </c>
       <c r="M145">
-        <v>0.28959206087958628</v>
+        <v>0.28966083669303883</v>
       </c>
       <c r="N145">
         <v>5</v>
@@ -22201,10 +22205,10 @@
         <v>922</v>
       </c>
       <c r="L146">
-        <v>83.191500000000005</v>
+        <v>46.321110326830578</v>
       </c>
       <c r="M146">
-        <v>0.28903684120495188</v>
+        <v>0.28912504224932872</v>
       </c>
       <c r="N146">
         <v>2</v>
@@ -22275,10 +22279,10 @@
         <v>922</v>
       </c>
       <c r="L147">
-        <v>76.480500000000006</v>
+        <v>43.957434857958482</v>
       </c>
       <c r="M147">
-        <v>0.28227033075074531</v>
+        <v>0.28242660016690763</v>
       </c>
       <c r="N147">
         <v>1</v>
@@ -22349,10 +22353,10 @@
         <v>922</v>
       </c>
       <c r="L148">
-        <v>70.747500000000002</v>
+        <v>39.396075653659189</v>
       </c>
       <c r="M148">
-        <v>0.27965779869906249</v>
+        <v>0.27969752229148609</v>
       </c>
       <c r="N148">
         <v>2</v>
@@ -22423,13 +22427,13 @@
         <v>922</v>
       </c>
       <c r="L149">
-        <v>67.861500000000007</v>
+        <v>40.426746267068559</v>
       </c>
       <c r="M149">
-        <v>0.27937041523893485</v>
+        <v>0.27908772503093937</v>
       </c>
       <c r="N149">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P149" t="s">
         <v>182</v>
@@ -22497,13 +22501,13 @@
         <v>922</v>
       </c>
       <c r="L150">
-        <v>70.594499999999996</v>
+        <v>44.791945837360494</v>
       </c>
       <c r="M150">
-        <v>0.27900210982047891</v>
+        <v>0.27903208950601016</v>
       </c>
       <c r="N150">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P150" t="s">
         <v>182</v>
@@ -22571,10 +22575,10 @@
         <v>922</v>
       </c>
       <c r="L151">
-        <v>68.489999999999995</v>
+        <v>48.670782373527679</v>
       </c>
       <c r="M151">
-        <v>0.27763230960227941</v>
+        <v>0.27749780034520866</v>
       </c>
       <c r="N151">
         <v>5</v>
@@ -22645,10 +22649,10 @@
         <v>922</v>
       </c>
       <c r="L152">
-        <v>64.451999999999998</v>
+        <v>43.021004297086357</v>
       </c>
       <c r="M152">
-        <v>0.27068675594097807</v>
+        <v>0.27025693569962167</v>
       </c>
       <c r="N152">
         <v>4</v>
@@ -22684,7 +22688,7 @@
         <v>4.0289999999999999</v>
       </c>
       <c r="AA152">
-        <v>0.30005406068807289</v>
+        <v>0.300054060688073</v>
       </c>
       <c r="AB152">
         <v>2</v>
@@ -22719,10 +22723,10 @@
         <v>922</v>
       </c>
       <c r="L153">
-        <v>71.185500000000005</v>
+        <v>40.622788271473731</v>
       </c>
       <c r="M153">
-        <v>0.27013849632272696</v>
+        <v>0.27004973924123432</v>
       </c>
       <c r="N153">
         <v>2</v>
@@ -22793,10 +22797,10 @@
         <v>922</v>
       </c>
       <c r="L154">
-        <v>66.293999999999997</v>
+        <v>41.831539943003555</v>
       </c>
       <c r="M154">
-        <v>0.26953160450870756</v>
+        <v>0.2698336004650968</v>
       </c>
       <c r="N154">
         <v>3</v>
@@ -22867,10 +22871,10 @@
         <v>922</v>
       </c>
       <c r="L155">
-        <v>77.153999999999996</v>
+        <v>43.994159513859145</v>
       </c>
       <c r="M155">
-        <v>0.26910349493226871</v>
+        <v>0.26949121559414296</v>
       </c>
       <c r="N155">
         <v>1</v>
@@ -22941,10 +22945,10 @@
         <v>922</v>
       </c>
       <c r="L156">
-        <v>68.285250000000005</v>
+        <v>40.264658934593825</v>
       </c>
       <c r="M156">
-        <v>0.26839794248594451</v>
+        <v>0.26815299146120741</v>
       </c>
       <c r="N156">
         <v>5</v>
@@ -23015,10 +23019,10 @@
         <v>922</v>
       </c>
       <c r="L157">
-        <v>74.643749999999997</v>
+        <v>45.842080126865888</v>
       </c>
       <c r="M157">
-        <v>0.26127536607919372</v>
+        <v>0.26138173704823275</v>
       </c>
       <c r="N157">
         <v>2</v>
@@ -23089,10 +23093,10 @@
         <v>922</v>
       </c>
       <c r="L158">
-        <v>76.639499999999998</v>
+        <v>41.430925800711201</v>
       </c>
       <c r="M158">
-        <v>0.25991675282737009</v>
+        <v>0.26003135347812856</v>
       </c>
       <c r="N158">
         <v>1</v>
@@ -23163,13 +23167,13 @@
         <v>922</v>
       </c>
       <c r="L159">
-        <v>63.564749999999997</v>
+        <v>39.581404785383704</v>
       </c>
       <c r="M159">
-        <v>0.25865159249709518</v>
+        <v>0.25877921904416862</v>
       </c>
       <c r="N159">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P159" t="s">
         <v>182</v>
@@ -23237,13 +23241,13 @@
         <v>922</v>
       </c>
       <c r="L160">
-        <v>70.174499999999995</v>
+        <v>40.077741624914921</v>
       </c>
       <c r="M160">
-        <v>0.25854548882114431</v>
+        <v>0.25873221540962749</v>
       </c>
       <c r="N160">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P160" t="s">
         <v>182</v>
@@ -23311,10 +23315,10 @@
         <v>922</v>
       </c>
       <c r="L161">
-        <v>76.890749999999997</v>
+        <v>46.803902895985502</v>
       </c>
       <c r="M161">
-        <v>0.25794692336676428</v>
+        <v>0.25804288882894522</v>
       </c>
       <c r="N161">
         <v>3</v>
@@ -23385,10 +23389,10 @@
         <v>922</v>
       </c>
       <c r="L162">
-        <v>100.35375000000001</v>
+        <v>61.784601230562089</v>
       </c>
       <c r="M162">
-        <v>0.25010931105011847</v>
+        <v>0.25025220026677775</v>
       </c>
       <c r="N162">
         <v>1</v>
@@ -23459,10 +23463,10 @@
         <v>922</v>
       </c>
       <c r="L163">
-        <v>93.423000000000002</v>
+        <v>59.999343070779695</v>
       </c>
       <c r="M163">
-        <v>0.25007976596143738</v>
+        <v>0.24993860840645035</v>
       </c>
       <c r="N163">
         <v>4</v>
@@ -23533,10 +23537,10 @@
         <v>922</v>
       </c>
       <c r="L164">
-        <v>93.729749999999996</v>
+        <v>66.712688443927362</v>
       </c>
       <c r="M164">
-        <v>0.24951175935550246</v>
+        <v>0.24949495320894904</v>
       </c>
       <c r="N164">
         <v>5</v>
@@ -23607,10 +23611,10 @@
         <v>922</v>
       </c>
       <c r="L165">
-        <v>98.216250000000002</v>
+        <v>55.520542123623308</v>
       </c>
       <c r="M165">
-        <v>0.2493970700666347</v>
+        <v>0.24947403795166334</v>
       </c>
       <c r="N165">
         <v>2</v>
@@ -23646,7 +23650,7 @@
         <v>0.129</v>
       </c>
       <c r="AA165">
-        <v>0.2408242734625084</v>
+        <v>0.24082427346250851</v>
       </c>
       <c r="AB165">
         <v>1</v>
@@ -23681,10 +23685,10 @@
         <v>922</v>
       </c>
       <c r="L166">
-        <v>94.001999999999995</v>
+        <v>48.134732730874347</v>
       </c>
       <c r="M166">
-        <v>0.24937191227441055</v>
+        <v>0.24918194702850471</v>
       </c>
       <c r="N166">
         <v>3</v>
@@ -23755,13 +23759,13 @@
         <v>922</v>
       </c>
       <c r="L167">
-        <v>106.44450000000001</v>
+        <v>67.817262925489672</v>
       </c>
       <c r="M167">
-        <v>0.2404304321115579</v>
+        <v>0.24040510928832309</v>
       </c>
       <c r="N167">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P167" t="s">
         <v>182</v>
@@ -23794,7 +23798,7 @@
         <v>7.9500000000000001E-2</v>
       </c>
       <c r="AA167">
-        <v>0.20849170347933607</v>
+        <v>0.20849170347933621</v>
       </c>
       <c r="AB167">
         <v>1</v>
@@ -23829,13 +23833,13 @@
         <v>922</v>
       </c>
       <c r="L168">
-        <v>112.83975</v>
+        <v>59.187486539449218</v>
       </c>
       <c r="M168">
-        <v>0.24037224778554761</v>
+        <v>0.24036344909011104</v>
       </c>
       <c r="N168">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P168" t="s">
         <v>182</v>
@@ -23903,13 +23907,13 @@
         <v>922</v>
       </c>
       <c r="L169">
-        <v>111.678</v>
+        <v>63.173867191182147</v>
       </c>
       <c r="M169">
-        <v>0.24018562726357687</v>
+        <v>0.24035358213025726</v>
       </c>
       <c r="N169">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P169" t="s">
         <v>182</v>
@@ -23942,7 +23946,7 @@
         <v>0.18</v>
       </c>
       <c r="AA169">
-        <v>0.1358628982964491</v>
+        <v>0.13586289829644921</v>
       </c>
       <c r="AB169">
         <v>1</v>
@@ -23977,10 +23981,10 @@
         <v>922</v>
       </c>
       <c r="L170">
-        <v>111.9465</v>
+        <v>66.523160001337672</v>
       </c>
       <c r="M170">
-        <v>0.23934588605425952</v>
+        <v>0.23927486161026282</v>
       </c>
       <c r="N170">
         <v>3</v>
@@ -24051,10 +24055,10 @@
         <v>922</v>
       </c>
       <c r="L171">
-        <v>102.99675000000001</v>
+        <v>73.579763229013253</v>
       </c>
       <c r="M171">
-        <v>0.23873129033030396</v>
+        <v>0.23844404404128539</v>
       </c>
       <c r="N171">
         <v>5</v>
@@ -24090,7 +24094,7 @@
         <v>1.8749999999999999E-2</v>
       </c>
       <c r="AA171">
-        <v>6.1235951634411902E-2</v>
+        <v>6.1235951634411992E-2</v>
       </c>
       <c r="AB171">
         <v>1</v>
@@ -24125,10 +24129,10 @@
         <v>922</v>
       </c>
       <c r="L172">
-        <v>111.51075</v>
+        <v>63.45633580352122</v>
       </c>
       <c r="M172">
-        <v>0.23030388707063323</v>
+        <v>0.23051175357339251</v>
       </c>
       <c r="N172">
         <v>1</v>
@@ -24199,10 +24203,10 @@
         <v>922</v>
       </c>
       <c r="L173">
-        <v>106.794</v>
+        <v>57.695787511472219</v>
       </c>
       <c r="M173">
-        <v>0.23007489447835161</v>
+        <v>0.23007151673516699</v>
       </c>
       <c r="N173">
         <v>3</v>
@@ -24237,13 +24241,13 @@
         <v>922</v>
       </c>
       <c r="L174">
-        <v>104.95050000000001</v>
+        <v>67.191418686662544</v>
       </c>
       <c r="M174">
-        <v>0.22961074495123515</v>
+        <v>0.22979908625228382</v>
       </c>
       <c r="N174">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="175" spans="2:28">
@@ -24275,13 +24279,13 @@
         <v>922</v>
       </c>
       <c r="L175">
-        <v>106.39575000000001</v>
+        <v>76.170584376684872</v>
       </c>
       <c r="M175">
-        <v>0.22948484036931299</v>
+        <v>0.22978107934442535</v>
       </c>
       <c r="N175">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="176" spans="2:28">
@@ -24313,10 +24317,10 @@
         <v>922</v>
       </c>
       <c r="L176">
-        <v>106.67925</v>
+        <v>56.521757717368374</v>
       </c>
       <c r="M176">
-        <v>0.22854429356342568</v>
+        <v>0.22869645985732845</v>
       </c>
       <c r="N176">
         <v>2</v>
@@ -24351,10 +24355,10 @@
         <v>922</v>
       </c>
       <c r="L177">
-        <v>130.76325</v>
+        <v>67.796768221889153</v>
       </c>
       <c r="M177">
-        <v>0.22054650766256972</v>
+        <v>0.22047557224279168</v>
       </c>
       <c r="N177">
         <v>2</v>
@@ -24389,10 +24393,10 @@
         <v>922</v>
       </c>
       <c r="L178">
-        <v>129.744</v>
+        <v>75.702849116588354</v>
       </c>
       <c r="M178">
-        <v>0.22013547541720771</v>
+        <v>0.22028987332766539</v>
       </c>
       <c r="N178">
         <v>1</v>
@@ -24427,10 +24431,10 @@
         <v>922</v>
       </c>
       <c r="L179">
-        <v>129.92699999999999</v>
+        <v>66.549939992405498</v>
       </c>
       <c r="M179">
-        <v>0.21978603938326063</v>
+        <v>0.21976514286692778</v>
       </c>
       <c r="N179">
         <v>3</v>
@@ -24465,10 +24469,10 @@
         <v>922</v>
       </c>
       <c r="L180">
-        <v>121.51425</v>
+        <v>74.435692193521035</v>
       </c>
       <c r="M180">
-        <v>0.21924843009415035</v>
+        <v>0.2195726561799998</v>
       </c>
       <c r="N180">
         <v>4</v>
@@ -24503,10 +24507,10 @@
         <v>922</v>
       </c>
       <c r="L181">
-        <v>118.6305</v>
+        <v>90.914809414224649</v>
       </c>
       <c r="M181">
-        <v>0.21864749739256178</v>
+        <v>0.21856156788778072</v>
       </c>
       <c r="N181">
         <v>5</v>
@@ -24541,10 +24545,10 @@
         <v>922</v>
       </c>
       <c r="L182">
-        <v>141.54300000000001</v>
+        <v>71.746089772282019</v>
       </c>
       <c r="M182">
-        <v>0.21066669733157894</v>
+        <v>0.21050236875079081</v>
       </c>
       <c r="N182">
         <v>3</v>
@@ -24579,10 +24583,10 @@
         <v>922</v>
       </c>
       <c r="L183">
-        <v>139.0215</v>
+        <v>78.955320558223946</v>
       </c>
       <c r="M183">
-        <v>0.20997275516005823</v>
+        <v>0.20985238466493736</v>
       </c>
       <c r="N183">
         <v>4</v>
@@ -24617,10 +24621,10 @@
         <v>922</v>
       </c>
       <c r="L184">
-        <v>148.58099999999999</v>
+        <v>80.953540793475298</v>
       </c>
       <c r="M184">
-        <v>0.2092436761532985</v>
+        <v>0.20913385963587078</v>
       </c>
       <c r="N184">
         <v>2</v>
@@ -24655,10 +24659,10 @@
         <v>922</v>
       </c>
       <c r="L185">
-        <v>146.8065</v>
+        <v>95.390229512718577</v>
       </c>
       <c r="M185">
-        <v>0.20906894705206797</v>
+        <v>0.20905538144353469</v>
       </c>
       <c r="N185">
         <v>1</v>
@@ -24693,10 +24697,10 @@
         <v>922</v>
       </c>
       <c r="L186">
-        <v>138.25874999999999</v>
+        <v>94.151230677942834</v>
       </c>
       <c r="M186">
-        <v>0.20873294621081717</v>
+        <v>0.20858418052938693</v>
       </c>
       <c r="N186">
         <v>5</v>
@@ -24731,10 +24735,10 @@
         <v>922</v>
       </c>
       <c r="L187">
-        <v>124.51649999999999</v>
+        <v>63.603697109689087</v>
       </c>
       <c r="M187">
-        <v>0.20037852282148819</v>
+        <v>0.2004050800720851</v>
       </c>
       <c r="N187">
         <v>3</v>
@@ -24769,13 +24773,13 @@
         <v>922</v>
       </c>
       <c r="L188">
-        <v>128.83799999999999</v>
+        <v>90.19165187268753</v>
       </c>
       <c r="M188">
-        <v>0.200252602072923</v>
+        <v>0.20014310490686166</v>
       </c>
       <c r="N188">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="189" spans="2:14">
@@ -24807,13 +24811,13 @@
         <v>922</v>
       </c>
       <c r="L189">
-        <v>123.01125</v>
+        <v>69.371354331303706</v>
       </c>
       <c r="M189">
-        <v>0.19999560901113311</v>
+        <v>0.20006764612396699</v>
       </c>
       <c r="N189">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="190" spans="2:14">
@@ -24845,13 +24849,13 @@
         <v>922</v>
       </c>
       <c r="L190">
-        <v>129.53625</v>
+        <v>79.461224952781222</v>
       </c>
       <c r="M190">
-        <v>0.19994137679432228</v>
+        <v>0.20001574968104116</v>
       </c>
       <c r="N190">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191" spans="2:14">
@@ -24883,13 +24887,13 @@
         <v>922</v>
       </c>
       <c r="L191">
-        <v>116.06699999999999</v>
+        <v>81.380259250207658</v>
       </c>
       <c r="M191">
-        <v>0.19988910160698808</v>
+        <v>0.199819452868402</v>
       </c>
       <c r="N191">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="192" spans="2:14">
@@ -24921,10 +24925,10 @@
         <v>922</v>
       </c>
       <c r="L192">
-        <v>105.79275</v>
+        <v>62.185692516148194</v>
       </c>
       <c r="M192">
-        <v>0.19139710018356973</v>
+        <v>0.19122862246105007</v>
       </c>
       <c r="N192">
         <v>4</v>
@@ -24959,10 +24963,10 @@
         <v>922</v>
       </c>
       <c r="L193">
-        <v>103.12875</v>
+        <v>69.683320213912836</v>
       </c>
       <c r="M193">
-        <v>0.19025633446641008</v>
+        <v>0.18990431723921442</v>
       </c>
       <c r="N193">
         <v>1</v>
@@ -24997,13 +25001,13 @@
         <v>922</v>
       </c>
       <c r="L194">
-        <v>105.4335</v>
+        <v>56.331136695754658</v>
       </c>
       <c r="M194">
-        <v>0.18978211083257557</v>
+        <v>0.18953580117487329</v>
       </c>
       <c r="N194">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="195" spans="2:14">
@@ -25035,13 +25039,13 @@
         <v>922</v>
       </c>
       <c r="L195">
-        <v>103.03274999999999</v>
+        <v>68.228317528033827</v>
       </c>
       <c r="M195">
-        <v>0.18963325925027866</v>
+        <v>0.18949575206313754</v>
       </c>
       <c r="N195">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="196" spans="2:14">
@@ -25073,13 +25077,13 @@
         <v>922</v>
       </c>
       <c r="L196">
-        <v>104.211</v>
+        <v>58.025196758535621</v>
       </c>
       <c r="M196">
-        <v>0.1892764884810528</v>
+        <v>0.18942894102588198</v>
       </c>
       <c r="N196">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="197" spans="2:14">
@@ -25111,10 +25115,10 @@
         <v>922</v>
       </c>
       <c r="L197">
-        <v>110.73824999999999</v>
+        <v>56.816285175900681</v>
       </c>
       <c r="M197">
-        <v>0.18035738903213464</v>
+        <v>0.18048882749784803</v>
       </c>
       <c r="N197">
         <v>3</v>
@@ -25149,10 +25153,10 @@
         <v>922</v>
       </c>
       <c r="L198">
-        <v>115.55025000000001</v>
+        <v>73.053414003019981</v>
       </c>
       <c r="M198">
-        <v>0.18005368626655621</v>
+        <v>0.18007618560355751</v>
       </c>
       <c r="N198">
         <v>1</v>
@@ -25187,10 +25191,10 @@
         <v>922</v>
       </c>
       <c r="L199">
-        <v>107.94750000000001</v>
+        <v>69.670308913819866</v>
       </c>
       <c r="M199">
-        <v>0.17984211877731737</v>
+        <v>0.17980924867380965</v>
       </c>
       <c r="N199">
         <v>4</v>
@@ -25225,10 +25229,10 @@
         <v>922</v>
       </c>
       <c r="L200">
-        <v>102.74025</v>
+        <v>71.012249317444287</v>
       </c>
       <c r="M200">
-        <v>0.179693339839889</v>
+        <v>0.17968953520716582</v>
       </c>
       <c r="N200">
         <v>5</v>
@@ -25263,10 +25267,10 @@
         <v>922</v>
       </c>
       <c r="L201">
-        <v>111.75825</v>
+        <v>62.275270142712358</v>
       </c>
       <c r="M201">
-        <v>0.1790314582190233</v>
+        <v>0.17885465686346641</v>
       </c>
       <c r="N201">
         <v>2</v>
@@ -25301,10 +25305,10 @@
         <v>922</v>
       </c>
       <c r="L202">
-        <v>94.304249999999996</v>
+        <v>54.508304913382872</v>
       </c>
       <c r="M202">
-        <v>0.1701581781868603</v>
+        <v>0.17009455781854479</v>
       </c>
       <c r="N202">
         <v>4</v>
@@ -25339,13 +25343,13 @@
         <v>922</v>
       </c>
       <c r="L203">
-        <v>91.818749999999994</v>
+        <v>53.280419290116406</v>
       </c>
       <c r="M203">
-        <v>0.16997699967545196</v>
+        <v>0.16995741863149941</v>
       </c>
       <c r="N203">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="204" spans="2:14">
@@ -25377,13 +25381,13 @@
         <v>922</v>
       </c>
       <c r="L204">
-        <v>92.834249999999997</v>
+        <v>60.843236900516402</v>
       </c>
       <c r="M204">
-        <v>0.16988225687678657</v>
+        <v>0.16987464716297265</v>
       </c>
       <c r="N204">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="205" spans="2:14">
@@ -25415,13 +25419,13 @@
         <v>922</v>
       </c>
       <c r="L205">
-        <v>91.228499999999997</v>
+        <v>52.057081451200304</v>
       </c>
       <c r="M205">
-        <v>0.16981967346737839</v>
+        <v>0.1697353808769024</v>
       </c>
       <c r="N205">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="206" spans="2:14">
@@ -25453,10 +25457,10 @@
         <v>922</v>
       </c>
       <c r="L206">
-        <v>83.873999999999995</v>
+        <v>57.838740313409509</v>
       </c>
       <c r="M206">
-        <v>0.16948972170461946</v>
+        <v>0.16933527407293797</v>
       </c>
       <c r="N206">
         <v>5</v>
@@ -25491,13 +25495,13 @@
         <v>922</v>
       </c>
       <c r="L207">
-        <v>102.36375</v>
+        <v>58.020632370770393</v>
       </c>
       <c r="M207">
-        <v>0.16030042328774485</v>
+        <v>0.16050516139544277</v>
       </c>
       <c r="N207">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="208" spans="2:14">
@@ -25529,13 +25533,13 @@
         <v>922</v>
       </c>
       <c r="L208">
-        <v>102.22875000000001</v>
+        <v>64.096677471286455</v>
       </c>
       <c r="M208">
-        <v>0.1602996835164526</v>
+        <v>0.15993749168277197</v>
       </c>
       <c r="N208">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="209" spans="2:14">
@@ -25567,13 +25571,13 @@
         <v>922</v>
       </c>
       <c r="L209">
-        <v>95.438999999999993</v>
+        <v>50.090285466422181</v>
       </c>
       <c r="M209">
-        <v>0.16025055306043393</v>
+        <v>0.15991171844853311</v>
       </c>
       <c r="N209">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="210" spans="2:14">
@@ -25605,10 +25609,10 @@
         <v>922</v>
       </c>
       <c r="L210">
-        <v>103.986</v>
+        <v>62.864003418057699</v>
       </c>
       <c r="M210">
-        <v>0.15976073572156493</v>
+        <v>0.15982212077940267</v>
       </c>
       <c r="N210">
         <v>2</v>
@@ -25643,10 +25647,10 @@
         <v>922</v>
       </c>
       <c r="L211">
-        <v>103.30800000000001</v>
+        <v>53.129951587730751</v>
       </c>
       <c r="M211">
-        <v>0.15933060685907471</v>
+        <v>0.15929159364310894</v>
       </c>
       <c r="N211">
         <v>4</v>
@@ -25681,10 +25685,10 @@
         <v>922</v>
       </c>
       <c r="L212">
-        <v>103.16249999999999</v>
+        <v>65.963542520320601</v>
       </c>
       <c r="M212">
-        <v>0.15101025934084378</v>
+        <v>0.15119822616974121</v>
       </c>
       <c r="N212">
         <v>4</v>
@@ -25719,10 +25723,10 @@
         <v>922</v>
       </c>
       <c r="L213">
-        <v>104.658</v>
+        <v>71.699918153803281</v>
       </c>
       <c r="M213">
-        <v>0.1504958301045797</v>
+        <v>0.15049500691527634</v>
       </c>
       <c r="N213">
         <v>1</v>
@@ -25757,10 +25761,10 @@
         <v>922</v>
       </c>
       <c r="L214">
-        <v>107.27475</v>
+        <v>65.353602059457828</v>
       </c>
       <c r="M214">
-        <v>0.15007008889248369</v>
+        <v>0.15029720405656002</v>
       </c>
       <c r="N214">
         <v>3</v>
@@ -25795,10 +25799,10 @@
         <v>922</v>
       </c>
       <c r="L215">
-        <v>102.753</v>
+        <v>63.349446593360874</v>
       </c>
       <c r="M215">
-        <v>0.14964678550530741</v>
+        <v>0.14971638906413695</v>
       </c>
       <c r="N215">
         <v>5</v>
@@ -25833,10 +25837,10 @@
         <v>922</v>
       </c>
       <c r="L216">
-        <v>116.10075000000001</v>
+        <v>72.165977485733293</v>
       </c>
       <c r="M216">
-        <v>0.14876152544146765</v>
+        <v>0.14896382474601497</v>
       </c>
       <c r="N216">
         <v>2</v>
@@ -25871,10 +25875,10 @@
         <v>922</v>
       </c>
       <c r="L217">
-        <v>91.441500000000005</v>
+        <v>44.924673592668924</v>
       </c>
       <c r="M217">
-        <v>0.14108922146771324</v>
+        <v>0.14098928370193611</v>
       </c>
       <c r="N217">
         <v>4</v>
@@ -25909,13 +25913,13 @@
         <v>922</v>
       </c>
       <c r="L218">
-        <v>80.470500000000001</v>
+        <v>48.662079266992926</v>
       </c>
       <c r="M218">
-        <v>0.14025254955107025</v>
+        <v>0.14035108100184654</v>
       </c>
       <c r="N218">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="219" spans="2:14">
@@ -25947,13 +25951,13 @@
         <v>922</v>
       </c>
       <c r="L219">
-        <v>90.263999999999996</v>
+        <v>48.080690916051431</v>
       </c>
       <c r="M219">
-        <v>0.14025170006062793</v>
+        <v>0.1400082036635171</v>
       </c>
       <c r="N219">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="220" spans="2:14">
@@ -25985,13 +25989,13 @@
         <v>922</v>
       </c>
       <c r="L220">
-        <v>88.491</v>
+        <v>51.979156633356389</v>
       </c>
       <c r="M220">
-        <v>0.14023468341829898</v>
+        <v>0.13988556774326388</v>
       </c>
       <c r="N220">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="221" spans="2:14">
@@ -26023,10 +26027,10 @@
         <v>922</v>
       </c>
       <c r="L221">
-        <v>87.510750000000002</v>
+        <v>65.332347723833578</v>
       </c>
       <c r="M221">
-        <v>0.13962808173356364</v>
+        <v>0.13960052385545602</v>
       </c>
       <c r="N221">
         <v>1</v>
@@ -26061,10 +26065,10 @@
         <v>922</v>
       </c>
       <c r="L222">
-        <v>88.392750000000007</v>
+        <v>57.632542249765322</v>
       </c>
       <c r="M222">
-        <v>0.13053906009998897</v>
+        <v>0.13069397049525711</v>
       </c>
       <c r="N222">
         <v>1</v>
@@ -26099,10 +26103,10 @@
         <v>922</v>
       </c>
       <c r="L223">
-        <v>87.285749999999993</v>
+        <v>50.714371654242001</v>
       </c>
       <c r="M223">
-        <v>0.1302697939566434</v>
+        <v>0.13017625530700874</v>
       </c>
       <c r="N223">
         <v>2</v>
@@ -26137,13 +26141,13 @@
         <v>922</v>
       </c>
       <c r="L224">
-        <v>80.771249999999995</v>
+        <v>45.749821815854745</v>
       </c>
       <c r="M224">
-        <v>0.12990821123698679</v>
+        <v>0.13017408057059085</v>
       </c>
       <c r="N224">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="225" spans="2:14">
@@ -26175,13 +26179,13 @@
         <v>922</v>
       </c>
       <c r="L225">
-        <v>74.461500000000001</v>
+        <v>45.129748256300886</v>
       </c>
       <c r="M225">
-        <v>0.12983991036234299</v>
+        <v>0.12979283391861857</v>
       </c>
       <c r="N225">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="226" spans="2:14">
@@ -26213,10 +26217,10 @@
         <v>922</v>
       </c>
       <c r="L226">
-        <v>84.236249999999998</v>
+        <v>49.758801266293844</v>
       </c>
       <c r="M226">
-        <v>0.1288303178258195</v>
+        <v>0.12873083532805274</v>
       </c>
       <c r="N226">
         <v>3</v>
@@ -26251,10 +26255,10 @@
         <v>922</v>
       </c>
       <c r="L227">
-        <v>53.802750000000003</v>
+        <v>28.593427651474947</v>
       </c>
       <c r="M227">
-        <v>0.12081243825764117</v>
+        <v>0.12100932779374758</v>
       </c>
       <c r="N227">
         <v>5</v>
@@ -26289,10 +26293,10 @@
         <v>922</v>
       </c>
       <c r="L228">
-        <v>79.399500000000003</v>
+        <v>56.68611009177031</v>
       </c>
       <c r="M228">
-        <v>0.12068757457792718</v>
+        <v>0.12040340466781752</v>
       </c>
       <c r="N228">
         <v>3</v>
@@ -26327,10 +26331,10 @@
         <v>922</v>
       </c>
       <c r="L229">
-        <v>84.295500000000004</v>
+        <v>58.427993467245514</v>
       </c>
       <c r="M229">
-        <v>0.12018759166669303</v>
+        <v>0.11996953749481581</v>
       </c>
       <c r="N229">
         <v>2</v>
@@ -26365,10 +26369,10 @@
         <v>922</v>
       </c>
       <c r="L230">
-        <v>70.612499999999997</v>
+        <v>45.907750587350904</v>
       </c>
       <c r="M230">
-        <v>0.11947799679063355</v>
+        <v>0.11946336789138953</v>
       </c>
       <c r="N230">
         <v>4</v>
@@ -26403,10 +26407,10 @@
         <v>922</v>
       </c>
       <c r="L231">
-        <v>79.869</v>
+        <v>52.911222442524313</v>
       </c>
       <c r="M231">
-        <v>0.11889786574813944</v>
+        <v>0.11893981245575272</v>
       </c>
       <c r="N231">
         <v>1</v>
@@ -26441,10 +26445,10 @@
         <v>922</v>
       </c>
       <c r="L232">
-        <v>100.7295</v>
+        <v>67.630574005177081</v>
       </c>
       <c r="M232">
-        <v>0.11115444236394832</v>
+        <v>0.11117816315415233</v>
       </c>
       <c r="N232">
         <v>3</v>
@@ -26479,10 +26483,10 @@
         <v>922</v>
       </c>
       <c r="L233">
-        <v>101.38800000000001</v>
+        <v>77.239416158028902</v>
       </c>
       <c r="M233">
-        <v>0.11014448154385255</v>
+        <v>0.11000883617639307</v>
       </c>
       <c r="N233">
         <v>2</v>
@@ -26517,10 +26521,10 @@
         <v>922</v>
       </c>
       <c r="L234">
-        <v>107.31975</v>
+        <v>71.921826097682626</v>
       </c>
       <c r="M234">
-        <v>0.11010210086004807</v>
+        <v>0.10993208427120232</v>
       </c>
       <c r="N234">
         <v>1</v>
@@ -26555,13 +26559,13 @@
         <v>922</v>
       </c>
       <c r="L235">
-        <v>87.939750000000004</v>
+        <v>46.667406819409976</v>
       </c>
       <c r="M235">
-        <v>0.1096882749329469</v>
+        <v>0.10964987704932175</v>
       </c>
       <c r="N235">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="236" spans="2:14">
@@ -26593,13 +26597,13 @@
         <v>922</v>
       </c>
       <c r="L236">
-        <v>88.442250000000001</v>
+        <v>55.660140599185752</v>
       </c>
       <c r="M236">
-        <v>0.10961468401770361</v>
+        <v>0.10941535606861322</v>
       </c>
       <c r="N236">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="237" spans="2:14">
@@ -26631,10 +26635,10 @@
         <v>922</v>
       </c>
       <c r="L237">
-        <v>81.154499999999999</v>
+        <v>50.057820345444206</v>
       </c>
       <c r="M237">
-        <v>0.10114773464862892</v>
+        <v>0.10094115735504439</v>
       </c>
       <c r="N237">
         <v>3</v>
@@ -26669,10 +26673,10 @@
         <v>922</v>
       </c>
       <c r="L238">
-        <v>77.394750000000002</v>
+        <v>39.538347482291591</v>
       </c>
       <c r="M238">
-        <v>0.10068717551348166</v>
+        <v>0.10073139766992807</v>
       </c>
       <c r="N238">
         <v>4</v>
@@ -26707,10 +26711,10 @@
         <v>922</v>
       </c>
       <c r="L239">
-        <v>43.650750000000002</v>
+        <v>18.740111470578487</v>
       </c>
       <c r="M239">
-        <v>0.10019970043248193</v>
+        <v>9.9941075784076197E-2</v>
       </c>
       <c r="N239">
         <v>5</v>
@@ -26745,10 +26749,10 @@
         <v>922</v>
       </c>
       <c r="L240">
-        <v>86.503500000000003</v>
+        <v>60.974767622362975</v>
       </c>
       <c r="M240">
-        <v>0.10014053854060526</v>
+        <v>9.9868687191735958E-2</v>
       </c>
       <c r="N240">
         <v>1</v>
@@ -26783,10 +26787,10 @@
         <v>922</v>
       </c>
       <c r="L241">
-        <v>79.555499999999995</v>
+        <v>55.637386811321697</v>
       </c>
       <c r="M241">
-        <v>0.10009103178453498</v>
+        <v>9.9842873430630349E-2</v>
       </c>
       <c r="N241">
         <v>2</v>
@@ -26821,10 +26825,10 @@
         <v>922</v>
       </c>
       <c r="L242">
-        <v>82.294499999999999</v>
+        <v>60.810339941605719</v>
       </c>
       <c r="M242">
-        <v>9.1008845998997376E-2</v>
+        <v>9.1101899598875741E-2</v>
       </c>
       <c r="N242">
         <v>2</v>
@@ -26859,10 +26863,10 @@
         <v>922</v>
       </c>
       <c r="L243">
-        <v>87.636750000000006</v>
+        <v>55.015815402356999</v>
       </c>
       <c r="M243">
-        <v>9.0741235634096876E-2</v>
+        <v>9.1019790460734315E-2</v>
       </c>
       <c r="N243">
         <v>3</v>
@@ -26897,10 +26901,10 @@
         <v>922</v>
       </c>
       <c r="L244">
-        <v>88.191749999999999</v>
+        <v>51.538455187639187</v>
       </c>
       <c r="M244">
-        <v>9.0523400395728232E-2</v>
+        <v>9.06370925700659E-2</v>
       </c>
       <c r="N244">
         <v>4</v>
@@ -26935,10 +26939,10 @@
         <v>922</v>
       </c>
       <c r="L245">
-        <v>57.311250000000001</v>
+        <v>30.992564605697858</v>
       </c>
       <c r="M245">
-        <v>9.0063125238238395E-2</v>
+        <v>8.993643044235046E-2</v>
       </c>
       <c r="N245">
         <v>5</v>
@@ -26973,10 +26977,10 @@
         <v>922</v>
       </c>
       <c r="L246">
-        <v>89.747249999999994</v>
+        <v>73.509722157989899</v>
       </c>
       <c r="M246">
-        <v>8.9628430425960526E-2</v>
+        <v>8.9488163152035005E-2</v>
       </c>
       <c r="N246">
         <v>1</v>
@@ -27011,10 +27015,10 @@
         <v>922</v>
       </c>
       <c r="L247">
-        <v>102.9285</v>
+        <v>66.960208563881224</v>
       </c>
       <c r="M247">
-        <v>8.0189762697607192E-2</v>
+        <v>8.0606271716150327E-2</v>
       </c>
       <c r="N247">
         <v>3</v>
@@ -27049,13 +27053,13 @@
         <v>922</v>
       </c>
       <c r="L248">
-        <v>92.186999999999998</v>
+        <v>30.71417159760572</v>
       </c>
       <c r="M248">
-        <v>8.0075909663592876E-2</v>
+        <v>8.0206905136150933E-2</v>
       </c>
       <c r="N248">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="249" spans="2:14">
@@ -27087,13 +27091,13 @@
         <v>922</v>
       </c>
       <c r="L249">
-        <v>66.227249999999998</v>
+        <v>59.84174282184329</v>
       </c>
       <c r="M249">
-        <v>7.9998990293488323E-2</v>
+        <v>7.9967783723850952E-2</v>
       </c>
       <c r="N249">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="250" spans="2:14">
@@ -27125,10 +27129,10 @@
         <v>922</v>
       </c>
       <c r="L250">
-        <v>106.85625</v>
+        <v>79.98560005570009</v>
       </c>
       <c r="M250">
-        <v>7.9543069786626425E-2</v>
+        <v>7.9379319763367109E-2</v>
       </c>
       <c r="N250">
         <v>1</v>
@@ -27163,10 +27167,10 @@
         <v>922</v>
       </c>
       <c r="L251">
-        <v>108.813</v>
+        <v>77.002193906426868</v>
       </c>
       <c r="M251">
-        <v>7.9479069017405035E-2</v>
+        <v>7.9237302482251221E-2</v>
       </c>
       <c r="N251">
         <v>2</v>
@@ -27201,10 +27205,10 @@
         <v>922</v>
       </c>
       <c r="L252">
-        <v>78.197249999999997</v>
+        <v>51.442425479065697</v>
       </c>
       <c r="M252">
-        <v>7.1067956235848426E-2</v>
+        <v>7.1516482973108975E-2</v>
       </c>
       <c r="N252">
         <v>4</v>
@@ -27239,10 +27243,10 @@
         <v>922</v>
       </c>
       <c r="L253">
-        <v>83.570999999999998</v>
+        <v>60.042708136037312</v>
       </c>
       <c r="M253">
-        <v>7.0254791285097276E-2</v>
+        <v>7.0282683284317943E-2</v>
       </c>
       <c r="N253">
         <v>3</v>
@@ -27277,10 +27281,10 @@
         <v>922</v>
       </c>
       <c r="L254">
-        <v>98.573250000000002</v>
+        <v>75.485335406091593</v>
       </c>
       <c r="M254">
-        <v>7.0096025604644965E-2</v>
+        <v>6.9986157686835207E-2</v>
       </c>
       <c r="N254">
         <v>1</v>
@@ -27315,10 +27319,10 @@
         <v>922</v>
       </c>
       <c r="L255">
-        <v>85.276499999999999</v>
+        <v>60.592402322209693</v>
       </c>
       <c r="M255">
-        <v>6.9013809038885723E-2</v>
+        <v>6.8947095582190324E-2</v>
       </c>
       <c r="N255">
         <v>2</v>
@@ -27353,10 +27357,10 @@
         <v>922</v>
       </c>
       <c r="L256">
-        <v>50.316749999999999</v>
+        <v>28.632989992159295</v>
       </c>
       <c r="M256">
-        <v>6.876187165455136E-2</v>
+        <v>6.8875336338198118E-2</v>
       </c>
       <c r="N256">
         <v>5</v>
@@ -27391,10 +27395,10 @@
         <v>922</v>
       </c>
       <c r="L257">
-        <v>59.758499999999998</v>
+        <v>37.445140731220128</v>
       </c>
       <c r="M257">
-        <v>6.0538654680054781E-2</v>
+        <v>6.070460863159375E-2</v>
       </c>
       <c r="N257">
         <v>4</v>
@@ -27429,10 +27433,10 @@
         <v>922</v>
       </c>
       <c r="L258">
-        <v>80.882249999999999</v>
+        <v>57.672690225632309</v>
       </c>
       <c r="M258">
-        <v>5.99183994497361E-2</v>
+        <v>6.0264007361494704E-2</v>
       </c>
       <c r="N258">
         <v>3</v>
@@ -27467,13 +27471,13 @@
         <v>922</v>
       </c>
       <c r="L259">
-        <v>70.213499999999996</v>
+        <v>58.237872618259544</v>
       </c>
       <c r="M259">
-        <v>5.9868398171550208E-2</v>
+        <v>5.9812457769000467E-2</v>
       </c>
       <c r="N259">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="260" spans="2:14">
@@ -27505,13 +27509,13 @@
         <v>922</v>
       </c>
       <c r="L260">
-        <v>74.768249999999995</v>
+        <v>50.691594715711538</v>
       </c>
       <c r="M260">
-        <v>5.9848888132270683E-2</v>
+        <v>5.9676522751628866E-2</v>
       </c>
       <c r="N260">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="261" spans="2:14">
@@ -27543,10 +27547,10 @@
         <v>922</v>
       </c>
       <c r="L261">
-        <v>42.612000000000002</v>
+        <v>20.998247444872128</v>
       </c>
       <c r="M261">
-        <v>5.8405981863056837E-2</v>
+        <v>5.8620786251783671E-2</v>
       </c>
       <c r="N261">
         <v>5</v>
@@ -27581,13 +27585,13 @@
         <v>922</v>
       </c>
       <c r="L262">
-        <v>73.776750000000007</v>
+        <v>56.761578968827919</v>
       </c>
       <c r="M262">
-        <v>5.0499010830373711E-2</v>
+        <v>5.0331535324680571E-2</v>
       </c>
       <c r="N262">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="263" spans="2:14">
@@ -27619,13 +27623,13 @@
         <v>922</v>
       </c>
       <c r="L263">
-        <v>74.816999999999993</v>
+        <v>54.912033661899599</v>
       </c>
       <c r="M263">
-        <v>5.0481436182142299E-2</v>
+        <v>5.0231005737113449E-2</v>
       </c>
       <c r="N263">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="264" spans="2:14">
@@ -27657,10 +27661,10 @@
         <v>922</v>
       </c>
       <c r="L264">
-        <v>68.048249999999996</v>
+        <v>46.121237096460838</v>
       </c>
       <c r="M264">
-        <v>4.9994143357109666E-2</v>
+        <v>4.9723183362540876E-2</v>
       </c>
       <c r="N264">
         <v>4</v>
@@ -27695,10 +27699,10 @@
         <v>922</v>
       </c>
       <c r="L265">
-        <v>46.305750000000003</v>
+        <v>23.896456880126667</v>
       </c>
       <c r="M265">
-        <v>4.9387728455150118E-2</v>
+        <v>4.93533959197257E-2</v>
       </c>
       <c r="N265">
         <v>5</v>
@@ -27733,10 +27737,10 @@
         <v>922</v>
       </c>
       <c r="L266">
-        <v>65.749499999999998</v>
+        <v>44.471111302299605</v>
       </c>
       <c r="M266">
-        <v>4.881590622079722E-2</v>
+        <v>4.8817560500261509E-2</v>
       </c>
       <c r="N266">
         <v>3</v>
@@ -27771,10 +27775,10 @@
         <v>922</v>
       </c>
       <c r="L267">
-        <v>49.520249999999997</v>
+        <v>40.918261760659952</v>
       </c>
       <c r="M267">
-        <v>4.0628515191599851E-2</v>
+        <v>4.074835282668389E-2</v>
       </c>
       <c r="N267">
         <v>2</v>
@@ -27809,10 +27813,10 @@
         <v>922</v>
       </c>
       <c r="L268">
-        <v>77.658749999999998</v>
+        <v>57.870015349570401</v>
       </c>
       <c r="M268">
-        <v>3.9799278348084298E-2</v>
+        <v>3.9858831091045523E-2</v>
       </c>
       <c r="N268">
         <v>1</v>
@@ -27847,13 +27851,13 @@
         <v>922</v>
       </c>
       <c r="L269">
-        <v>40.636499999999998</v>
+        <v>11.295372537374799</v>
       </c>
       <c r="M269">
-        <v>3.9239345300995175E-2</v>
+        <v>3.9122885609051063E-2</v>
       </c>
       <c r="N269">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="270" spans="2:14">
@@ -27885,13 +27889,13 @@
         <v>922</v>
       </c>
       <c r="L270">
-        <v>52.627499999999998</v>
+        <v>25.328103775255787</v>
       </c>
       <c r="M270">
-        <v>3.9068739152042703E-2</v>
+        <v>3.8917985665344712E-2</v>
       </c>
       <c r="N270">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="271" spans="2:14">
@@ -27923,13 +27927,13 @@
         <v>922</v>
       </c>
       <c r="L271">
-        <v>26.327249999999999</v>
+        <v>37.906156321558321</v>
       </c>
       <c r="M271">
-        <v>3.8758403151683378E-2</v>
+        <v>3.8888044975457579E-2</v>
       </c>
       <c r="N271">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="272" spans="2:14">
@@ -27961,10 +27965,10 @@
         <v>922</v>
       </c>
       <c r="L272">
-        <v>56.043750000000003</v>
+        <v>49.296394552109668</v>
       </c>
       <c r="M272">
-        <v>3.1760028503563437E-2</v>
+        <v>3.1872198211098143E-2</v>
       </c>
       <c r="N272">
         <v>1</v>
@@ -27999,10 +28003,10 @@
         <v>922</v>
       </c>
       <c r="L273">
-        <v>49.787999999999997</v>
+        <v>39.61339772780758</v>
       </c>
       <c r="M273">
-        <v>3.0654779219918788E-2</v>
+        <v>3.0697421999409023E-2</v>
       </c>
       <c r="N273">
         <v>2</v>
@@ -28037,10 +28041,10 @@
         <v>922</v>
       </c>
       <c r="L274">
-        <v>37.026000000000003</v>
+        <v>28.04123380657748</v>
       </c>
       <c r="M274">
-        <v>3.0085638729995121E-2</v>
+        <v>3.0267765712621044E-2</v>
       </c>
       <c r="N274">
         <v>4</v>
@@ -28075,13 +28079,13 @@
         <v>922</v>
       </c>
       <c r="L275">
-        <v>37.728749999999998</v>
+        <v>15.585983410484074</v>
       </c>
       <c r="M275">
-        <v>2.8596037904915189E-2</v>
+        <v>2.8634947466863112E-2</v>
       </c>
       <c r="N275">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="276" spans="2:14">
@@ -28113,13 +28117,13 @@
         <v>922</v>
       </c>
       <c r="L276">
-        <v>27.927</v>
+        <v>26.788946513679946</v>
       </c>
       <c r="M276">
-        <v>2.8345547687130251E-2</v>
+        <v>2.8591678421330882E-2</v>
       </c>
       <c r="N276">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="277" spans="2:14">
@@ -28151,10 +28155,10 @@
         <v>922</v>
       </c>
       <c r="L277">
-        <v>38.733750000000001</v>
+        <v>31.203047050610515</v>
       </c>
       <c r="M277">
-        <v>2.0525090636619055E-2</v>
+        <v>2.0634387051199486E-2</v>
       </c>
       <c r="N277">
         <v>3</v>
@@ -28189,10 +28193,10 @@
         <v>922</v>
       </c>
       <c r="L278">
-        <v>45.257249999999999</v>
+        <v>39.063391052672344</v>
       </c>
       <c r="M278">
-        <v>2.0261223164485857E-2</v>
+        <v>2.0291890063241228E-2</v>
       </c>
       <c r="N278">
         <v>2</v>
@@ -28227,10 +28231,10 @@
         <v>922</v>
       </c>
       <c r="L279">
-        <v>45.879750000000001</v>
+        <v>28.605913915041231</v>
       </c>
       <c r="M279">
-        <v>1.9986758703502607E-2</v>
+        <v>2.0159897817984867E-2</v>
       </c>
       <c r="N279">
         <v>4</v>
@@ -28265,10 +28269,10 @@
         <v>922</v>
       </c>
       <c r="L280">
-        <v>53.958750000000002</v>
+        <v>42.542093407083115</v>
       </c>
       <c r="M280">
-        <v>1.9839296398137522E-2</v>
+        <v>1.9635220023073541E-2</v>
       </c>
       <c r="N280">
         <v>1</v>
@@ -28303,10 +28307,10 @@
         <v>922</v>
       </c>
       <c r="L281">
-        <v>24.991499999999998</v>
+        <v>11.86528090621696</v>
       </c>
       <c r="M281">
-        <v>1.9376073822787439E-2</v>
+        <v>1.8961030765276221E-2</v>
       </c>
       <c r="N281">
         <v>5</v>
@@ -28341,10 +28345,10 @@
         <v>922</v>
       </c>
       <c r="L282">
-        <v>37.663499999999999</v>
+        <v>31.221960963438157</v>
       </c>
       <c r="M282">
-        <v>1.1267104709177181E-2</v>
+        <v>1.1355534025320182E-2</v>
       </c>
       <c r="N282">
         <v>1</v>
@@ -28379,10 +28383,10 @@
         <v>922</v>
       </c>
       <c r="L283">
-        <v>26.482500000000002</v>
+        <v>19.84808709270645</v>
       </c>
       <c r="M283">
-        <v>1.1120993089338605E-2</v>
+        <v>1.0896985834927783E-2</v>
       </c>
       <c r="N283">
         <v>3</v>
@@ -28417,10 +28421,10 @@
         <v>922</v>
       </c>
       <c r="L284">
-        <v>45.7395</v>
+        <v>35.979222003092062</v>
       </c>
       <c r="M284">
-        <v>1.0224172468162873E-2</v>
+        <v>1.0374533091010784E-2</v>
       </c>
       <c r="N284">
         <v>2</v>
@@ -28455,10 +28459,10 @@
         <v>922</v>
       </c>
       <c r="L285">
-        <v>12.27525</v>
+        <v>6.9042990619819848</v>
       </c>
       <c r="M285">
-        <v>9.8631506263682136E-3</v>
+        <v>1.0172333719812096E-2</v>
       </c>
       <c r="N285">
         <v>5</v>
@@ -28493,10 +28497,10 @@
         <v>922</v>
       </c>
       <c r="L286">
-        <v>17.72625</v>
+        <v>12.297160403338735</v>
       </c>
       <c r="M286">
-        <v>9.0368075995397902E-3</v>
+        <v>9.1932597142654858E-3</v>
       </c>
       <c r="N286">
         <v>4</v>
@@ -28531,13 +28535,13 @@
         <v>922</v>
       </c>
       <c r="L287">
-        <v>3.0720000000000001</v>
+        <v>4.3009492094437158</v>
       </c>
       <c r="M287">
-        <v>3.4790674458892146E-3</v>
+        <v>3.449780203441066E-3</v>
       </c>
       <c r="N287">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="288" spans="2:14">
@@ -28569,13 +28573,13 @@
         <v>922</v>
       </c>
       <c r="L288">
-        <v>4.8194999999999997</v>
+        <v>3.8681413610686506</v>
       </c>
       <c r="M288">
-        <v>3.4721781597795132E-3</v>
+        <v>3.3755137367802645E-3</v>
       </c>
       <c r="N288">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="289" spans="2:14">
@@ -28607,13 +28611,13 @@
         <v>922</v>
       </c>
       <c r="L289">
-        <v>3.9914999999999998</v>
+        <v>2.6570153220664654</v>
       </c>
       <c r="M289">
-        <v>3.3381318551142245E-3</v>
+        <v>3.2835490531447267E-3</v>
       </c>
       <c r="N289">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="290" spans="2:14">
@@ -28645,13 +28649,13 @@
         <v>922</v>
       </c>
       <c r="L290">
-        <v>2.9197500000000001</v>
+        <v>1.7634491749727768</v>
       </c>
       <c r="M290">
-        <v>3.2238116339487243E-3</v>
+        <v>3.114304227746373E-3</v>
       </c>
       <c r="N290">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="291" spans="2:14">
@@ -28683,10 +28687,10 @@
         <v>922</v>
       </c>
       <c r="L291">
-        <v>2.3984999999999999</v>
+        <v>2.1913455056899056</v>
       </c>
       <c r="M291">
-        <v>2.9864202737745426E-3</v>
+        <v>2.9748280303696266E-3</v>
       </c>
       <c r="N291">
         <v>4</v>
@@ -28698,7 +28702,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6964B0E8-398F-4160-8769-DFA436DFBCBA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{593C4010-CCB7-4043-AFB2-0B5CBAE9BA04}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_CHN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_CHN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{619517DE-D20F-481C-AEC9-E7008D5CEA60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{352508FC-F5ED-47F7-A530-F94EA04EC362}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8184,7 +8184,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{950D6A02-1146-4D17-925B-A2CFF6430D1A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D5E4C0B-8E9B-4A92-8BB1-E6D786379A88}">
   <dimension ref="B9:M146"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12997,7 +12997,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80EB0FC2-F1E8-41CB-9D87-11005EB020E8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3E10B50-3F14-4729-B749-CBA984C49B16}">
   <dimension ref="B9:Z124"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -18201,7 +18201,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A77B4A2E-B225-40D7-A10A-34109CD2CBDA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EDC0C24-4D85-4ECD-9FF3-9B39AB414A7B}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_CHN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_CHN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{352508FC-F5ED-47F7-A530-F94EA04EC362}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1F7AE6B6-2BCA-4555-9E29-525C2BB9366A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8184,7 +8184,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D5E4C0B-8E9B-4A92-8BB1-E6D786379A88}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27E45554-5C90-4C88-976F-68A07D79C223}">
   <dimension ref="B9:M146"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12997,7 +12997,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3E10B50-3F14-4729-B749-CBA984C49B16}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D2B2097-071E-4AFB-89E3-8AEB92B7FD27}">
   <dimension ref="B9:Z124"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -18201,7 +18201,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EDC0C24-4D85-4ECD-9FF3-9B39AB414A7B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19044F5A-00B8-4C29-9D99-BF140908D818}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_CHN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_CHN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1F7AE6B6-2BCA-4555-9E29-525C2BB9366A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CE8EA1DF-AFBE-4B3F-8AA6-FF921F5C680C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8184,7 +8184,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27E45554-5C90-4C88-976F-68A07D79C223}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCA6A096-CFF9-4B38-82F5-03844D37AD9B}">
   <dimension ref="B9:M146"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12997,7 +12997,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D2B2097-071E-4AFB-89E3-8AEB92B7FD27}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FFFE725-7A5E-405F-B323-4F92649362DF}">
   <dimension ref="B9:Z124"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -18201,7 +18201,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19044F5A-00B8-4C29-9D99-BF140908D818}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{843C4ABB-6A14-4255-B820-71F1573BE24C}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_CHN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_CHN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CE8EA1DF-AFBE-4B3F-8AA6-FF921F5C680C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6CED2041-C7DD-4AB2-82FD-E607662972E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8184,7 +8184,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCA6A096-CFF9-4B38-82F5-03844D37AD9B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52016D2F-3146-4FC2-BCD0-A890B6F0B1D6}">
   <dimension ref="B9:M146"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12997,7 +12997,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FFFE725-7A5E-405F-B323-4F92649362DF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E516BBD-CDEC-4864-9C96-E832F97834B8}">
   <dimension ref="B9:Z124"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -18201,7 +18201,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{843C4ABB-6A14-4255-B820-71F1573BE24C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D9D35A2-3C81-4A11-A966-C82BC1E324CA}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_CHN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_CHN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3705C7D8-8227-4445-AD25-6D8ECAB5324B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C6D6B862-8534-4519-8ACE-9BD07A707364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8001,7 +8001,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B72596C3-38EE-4195-B8F9-823E8476E027}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8E83BFB-8390-4E79-8D11-028217DF7411}">
   <dimension ref="B9:M146"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12814,7 +12814,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6545392-DC4E-427F-93F2-6CB925EE9A40}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{886C200B-4253-4A9E-9168-AE3E38208631}">
   <dimension ref="B9:Z124"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -18018,7 +18018,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10724901-D199-41A7-9CE3-FAC6DC16E215}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F6155E5-1F3C-4F3B-96AC-ED599E469913}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_CHN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_CHN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C6D6B862-8534-4519-8ACE-9BD07A707364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{36E6FBF9-44AE-4515-AFCA-4C9B9DEB7AA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8001,7 +8001,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8E83BFB-8390-4E79-8D11-028217DF7411}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C896C4DC-466B-46C5-ACAC-9F7BC8ECFD41}">
   <dimension ref="B9:M146"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12814,7 +12814,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{886C200B-4253-4A9E-9168-AE3E38208631}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD555617-4CD3-4DE4-A9E3-CF155C12F7D6}">
   <dimension ref="B9:Z124"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -18018,7 +18018,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F6155E5-1F3C-4F3B-96AC-ED599E469913}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFB40048-AC9C-4368-8750-0A1F817E024D}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_CHN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_CHN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{36E6FBF9-44AE-4515-AFCA-4C9B9DEB7AA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D5B69633-C6A0-4435-916F-A62E64EE98C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8001,7 +8001,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C896C4DC-466B-46C5-ACAC-9F7BC8ECFD41}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50AF16E3-1710-435F-8D16-96112F86222D}">
   <dimension ref="B9:M146"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -8077,10 +8077,10 @@
         <v>450</v>
       </c>
       <c r="L11">
-        <v>5.5781122738829723</v>
+        <v>111.54635273052318</v>
       </c>
       <c r="M11">
-        <v>0.15431352192830419</v>
+        <v>0.2016814714661522</v>
       </c>
     </row>
     <row r="12" spans="2:13">
@@ -8112,10 +8112,10 @@
         <v>451</v>
       </c>
       <c r="L12">
-        <v>5.7965691911238233</v>
+        <v>2.3408361540480946</v>
       </c>
       <c r="M12">
-        <v>0.16033669759690611</v>
+        <v>0.18141566184189031</v>
       </c>
     </row>
     <row r="13" spans="2:13">
@@ -8147,10 +8147,10 @@
         <v>452</v>
       </c>
       <c r="L13">
-        <v>13.988710737146491</v>
+        <v>31.310501478861372</v>
       </c>
       <c r="M13">
-        <v>0.15396751131924041</v>
+        <v>0.19840444322763739</v>
       </c>
     </row>
     <row r="14" spans="2:13">
@@ -8182,10 +8182,10 @@
         <v>453</v>
       </c>
       <c r="L14">
-        <v>1.1805103330963411</v>
+        <v>58.608565914978101</v>
       </c>
       <c r="M14">
-        <v>0.14282865294313099</v>
+        <v>0.18591509192463379</v>
       </c>
     </row>
     <row r="15" spans="2:13">
@@ -8217,10 +8217,10 @@
         <v>454</v>
       </c>
       <c r="L15">
-        <v>6.255362373556614</v>
+        <v>40.097268989680479</v>
       </c>
       <c r="M15">
-        <v>0.1412577745194466</v>
+        <v>0.18476784042621791</v>
       </c>
     </row>
     <row r="16" spans="2:13">
@@ -8252,10 +8252,10 @@
         <v>455</v>
       </c>
       <c r="L16">
-        <v>4.5645608490021292</v>
+        <v>45.825231283516445</v>
       </c>
       <c r="M16">
-        <v>0.15266553226973981</v>
+        <v>0.1914866881095135</v>
       </c>
     </row>
     <row r="17" spans="2:13">
@@ -8287,10 +8287,10 @@
         <v>456</v>
       </c>
       <c r="L17">
-        <v>5.4222822397567141</v>
+        <v>47.5907918209207</v>
       </c>
       <c r="M17">
-        <v>0.16466334256604551</v>
+        <v>0.17665584697488751</v>
       </c>
     </row>
     <row r="18" spans="2:13">
@@ -8322,10 +8322,10 @@
         <v>457</v>
       </c>
       <c r="L18">
-        <v>5.3189071819604825</v>
+        <v>17.232626888068001</v>
       </c>
       <c r="M18">
-        <v>0.14934479913076129</v>
+        <v>0.1703113840652809</v>
       </c>
     </row>
     <row r="19" spans="2:13">
@@ -8357,10 +8357,10 @@
         <v>458</v>
       </c>
       <c r="L19">
-        <v>11.327043102114228</v>
+        <v>49.250650189691129</v>
       </c>
       <c r="M19">
-        <v>0.1478245019599797</v>
+        <v>0.17619607399751239</v>
       </c>
     </row>
     <row r="20" spans="2:13">
@@ -8392,10 +8392,10 @@
         <v>459</v>
       </c>
       <c r="L20">
-        <v>15.537740525521572</v>
+        <v>60.612113001910174</v>
       </c>
       <c r="M20">
-        <v>0.1487157679255634</v>
+        <v>0.15575579176014021</v>
       </c>
     </row>
     <row r="21" spans="2:13">
@@ -8427,10 +8427,10 @@
         <v>460</v>
       </c>
       <c r="L21">
-        <v>4.3044456863585454</v>
+        <v>38.40128669115952</v>
       </c>
       <c r="M21">
-        <v>0.15331053583755511</v>
+        <v>0.1511057614772055</v>
       </c>
     </row>
     <row r="22" spans="2:13">
@@ -8462,10 +8462,10 @@
         <v>461</v>
       </c>
       <c r="L22">
-        <v>11.030507444660149</v>
+        <v>18.264400337507791</v>
       </c>
       <c r="M22">
-        <v>0.1457331821656582</v>
+        <v>0.15621955436497731</v>
       </c>
     </row>
     <row r="23" spans="2:13">
@@ -8497,10 +8497,10 @@
         <v>462</v>
       </c>
       <c r="L23">
-        <v>81.893516536472418</v>
+        <v>10.746337591157731</v>
       </c>
       <c r="M23">
-        <v>0.18898740317467461</v>
+        <v>0.15450190906127181</v>
       </c>
     </row>
     <row r="24" spans="2:13">
@@ -8532,10 +8532,10 @@
         <v>463</v>
       </c>
       <c r="L24">
-        <v>52.994574393157883</v>
+        <v>8.0626061132389442</v>
       </c>
       <c r="M24">
-        <v>0.18569622053526219</v>
+        <v>0.16342091910898751</v>
       </c>
     </row>
     <row r="25" spans="2:13">
@@ -8567,10 +8567,10 @@
         <v>464</v>
       </c>
       <c r="L25">
-        <v>95.049556056765766</v>
+        <v>49.72494449836644</v>
       </c>
       <c r="M25">
-        <v>0.20216029125036181</v>
+        <v>0.1535742812524005</v>
       </c>
     </row>
     <row r="26" spans="2:13">
@@ -8602,10 +8602,10 @@
         <v>465</v>
       </c>
       <c r="L26">
-        <v>31.913601498640876</v>
+        <v>28.896002929449889</v>
       </c>
       <c r="M26">
-        <v>0.1910120430850385</v>
+        <v>0.15061587756642369</v>
       </c>
     </row>
     <row r="27" spans="2:13">
@@ -8637,10 +8637,10 @@
         <v>466</v>
       </c>
       <c r="L27">
-        <v>7.3604156517936126</v>
+        <v>6.5473713493225807</v>
       </c>
       <c r="M27">
-        <v>0.2028415944231346</v>
+        <v>0.14859018689326589</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -8672,10 +8672,10 @@
         <v>467</v>
       </c>
       <c r="L28">
-        <v>15.816015931813871</v>
+        <v>2.8956601021736086</v>
       </c>
       <c r="M28">
-        <v>0.153808801665162</v>
+        <v>0.15848645011995299</v>
       </c>
     </row>
     <row r="29" spans="2:13">
@@ -8707,10 +8707,10 @@
         <v>468</v>
       </c>
       <c r="L29">
-        <v>3.5971845989322166</v>
+        <v>19.682276857753841</v>
       </c>
       <c r="M29">
-        <v>0.1786886837464404</v>
+        <v>0.1512081468511956</v>
       </c>
     </row>
     <row r="30" spans="2:13">
@@ -8742,10 +8742,10 @@
         <v>469</v>
       </c>
       <c r="L30">
-        <v>19.297831745554529</v>
+        <v>4.7190790580104824</v>
       </c>
       <c r="M30">
-        <v>0.15904459080854641</v>
+        <v>0.1402898637371488</v>
       </c>
     </row>
     <row r="31" spans="2:13">
@@ -8777,10 +8777,10 @@
         <v>470</v>
       </c>
       <c r="L31">
-        <v>2.6414965861460096</v>
+        <v>4.0867450657344051</v>
       </c>
       <c r="M31">
-        <v>0.15940145420515789</v>
+        <v>0.15511541282278779</v>
       </c>
     </row>
     <row r="32" spans="2:13">
@@ -8812,10 +8812,10 @@
         <v>471</v>
       </c>
       <c r="L32">
-        <v>65.396422517587069</v>
+        <v>7.1486544483008609</v>
       </c>
       <c r="M32">
-        <v>0.1539616118083689</v>
+        <v>0.15175632361117111</v>
       </c>
     </row>
     <row r="33" spans="2:13">
@@ -8847,10 +8847,10 @@
         <v>472</v>
       </c>
       <c r="L33">
-        <v>40.423157770246334</v>
+        <v>76.980139616281647</v>
       </c>
       <c r="M33">
-        <v>0.15172376615759059</v>
+        <v>0.1942330002128338</v>
       </c>
     </row>
     <row r="34" spans="2:13">
@@ -8882,10 +8882,10 @@
         <v>473</v>
       </c>
       <c r="L34">
-        <v>77.271497710065262</v>
+        <v>67.575478267611928</v>
       </c>
       <c r="M34">
-        <v>0.15329329670089931</v>
+        <v>0.18659143930349489</v>
       </c>
     </row>
     <row r="35" spans="2:13">
@@ -8917,10 +8917,10 @@
         <v>474</v>
       </c>
       <c r="L35">
-        <v>53.777482561070457</v>
+        <v>46.040740069491207</v>
       </c>
       <c r="M35">
-        <v>0.17496538488358879</v>
+        <v>0.1760388547923013</v>
       </c>
     </row>
     <row r="36" spans="2:13">
@@ -8952,10 +8952,10 @@
         <v>475</v>
       </c>
       <c r="L36">
-        <v>29.78299160195904</v>
+        <v>44.296173015366222</v>
       </c>
       <c r="M36">
-        <v>0.17361446620856419</v>
+        <v>0.1790477452195498</v>
       </c>
     </row>
     <row r="37" spans="2:13">
@@ -8987,10 +8987,10 @@
         <v>476</v>
       </c>
       <c r="L37">
-        <v>38.842671663125365</v>
+        <v>43.46901091863117</v>
       </c>
       <c r="M37">
-        <v>0.178561666593821</v>
+        <v>0.1845616964539607</v>
       </c>
     </row>
     <row r="38" spans="2:13">
@@ -9022,10 +9022,10 @@
         <v>477</v>
       </c>
       <c r="L38">
-        <v>3.5758157337367074</v>
+        <v>23.884229199301657</v>
       </c>
       <c r="M38">
-        <v>0.14460698470041761</v>
+        <v>0.1757473973029221</v>
       </c>
     </row>
     <row r="39" spans="2:13">
@@ -9092,10 +9092,10 @@
         <v>479</v>
       </c>
       <c r="L40">
-        <v>42.94349966899496</v>
+        <v>17.55977607125028</v>
       </c>
       <c r="M40">
-        <v>0.16575847872244959</v>
+        <v>0.15312395273416909</v>
       </c>
     </row>
     <row r="41" spans="2:13">
@@ -9127,10 +9127,10 @@
         <v>480</v>
       </c>
       <c r="L41">
-        <v>15.303111087709599</v>
+        <v>9.5174322357966137</v>
       </c>
       <c r="M41">
-        <v>0.1583636773047222</v>
+        <v>0.1455459951691031</v>
       </c>
     </row>
     <row r="42" spans="2:13">
@@ -9162,10 +9162,10 @@
         <v>481</v>
       </c>
       <c r="L42">
-        <v>32.051003640451057</v>
+        <v>37.982127117412865</v>
       </c>
       <c r="M42">
-        <v>0.16649145013662209</v>
+        <v>0.1659305980185237</v>
       </c>
     </row>
     <row r="43" spans="2:13">
@@ -9197,10 +9197,10 @@
         <v>482</v>
       </c>
       <c r="L43">
-        <v>17.55977607125028</v>
+        <v>15.303111087709599</v>
       </c>
       <c r="M43">
-        <v>0.15312395273416909</v>
+        <v>0.1583636773047222</v>
       </c>
     </row>
     <row r="44" spans="2:13">
@@ -9232,10 +9232,10 @@
         <v>483</v>
       </c>
       <c r="L44">
-        <v>36.439453052335175</v>
+        <v>4.3044456863585454</v>
       </c>
       <c r="M44">
-        <v>0.15847686712459691</v>
+        <v>0.15331053583755511</v>
       </c>
     </row>
     <row r="45" spans="2:13">
@@ -9267,10 +9267,10 @@
         <v>484</v>
       </c>
       <c r="L45">
-        <v>40.908150564159811</v>
+        <v>18.563241789884209</v>
       </c>
       <c r="M45">
-        <v>0.15046718240718751</v>
+        <v>0.1466991492404762</v>
       </c>
     </row>
     <row r="46" spans="2:13">
@@ -9302,10 +9302,10 @@
         <v>485</v>
       </c>
       <c r="L46">
-        <v>37.24541999925836</v>
+        <v>14.552685896526127</v>
       </c>
       <c r="M46">
-        <v>0.1620849813911808</v>
+        <v>0.1484386957038715</v>
       </c>
     </row>
     <row r="47" spans="2:13">
@@ -9337,10 +9337,10 @@
         <v>486</v>
       </c>
       <c r="L47">
-        <v>26.706527677700677</v>
+        <v>5.8141709422726464</v>
       </c>
       <c r="M47">
-        <v>0.15420412038603981</v>
+        <v>0.15422833000772099</v>
       </c>
     </row>
     <row r="48" spans="2:13">
@@ -9372,10 +9372,10 @@
         <v>487</v>
       </c>
       <c r="L48">
-        <v>29.86858977447794</v>
+        <v>9.6530289986273932</v>
       </c>
       <c r="M48">
-        <v>0.16786852013756109</v>
+        <v>0.17372813788122249</v>
       </c>
     </row>
     <row r="49" spans="2:13">
@@ -9407,10 +9407,10 @@
         <v>488</v>
       </c>
       <c r="L49">
-        <v>18.772169214519931</v>
+        <v>4.5727315411346687</v>
       </c>
       <c r="M49">
-        <v>0.16111729387323881</v>
+        <v>0.17078633409415589</v>
       </c>
     </row>
     <row r="50" spans="2:13">
@@ -9442,10 +9442,10 @@
         <v>489</v>
       </c>
       <c r="L50">
-        <v>29.226761749770567</v>
+        <v>21.065834982908772</v>
       </c>
       <c r="M50">
-        <v>0.1656000174756731</v>
+        <v>0.17545951405274851</v>
       </c>
     </row>
     <row r="51" spans="2:13">
@@ -9477,10 +9477,10 @@
         <v>490</v>
       </c>
       <c r="L51">
-        <v>7.4644014479301664</v>
+        <v>14.509086767572569</v>
       </c>
       <c r="M51">
-        <v>0.17357208838134119</v>
+        <v>0.16766348085819111</v>
       </c>
     </row>
     <row r="52" spans="2:13">
@@ -9512,10 +9512,10 @@
         <v>491</v>
       </c>
       <c r="L52">
-        <v>6.1820418640587835</v>
+        <v>12.576490877103915</v>
       </c>
       <c r="M52">
-        <v>0.16934719673245621</v>
+        <v>0.1649871531235465</v>
       </c>
     </row>
     <row r="53" spans="2:13">
@@ -9547,10 +9547,10 @@
         <v>492</v>
       </c>
       <c r="L53">
-        <v>21.065834982908772</v>
+        <v>33.080498934676434</v>
       </c>
       <c r="M53">
-        <v>0.17545951405274851</v>
+        <v>0.16695257862550919</v>
       </c>
     </row>
     <row r="54" spans="2:13">
@@ -9582,10 +9582,10 @@
         <v>493</v>
       </c>
       <c r="L54">
-        <v>15.144991322264906</v>
+        <v>14.170846644566792</v>
       </c>
       <c r="M54">
-        <v>0.1679241976694294</v>
+        <v>0.15325817144060461</v>
       </c>
     </row>
     <row r="55" spans="2:13">
@@ -9617,10 +9617,10 @@
         <v>494</v>
       </c>
       <c r="L55">
-        <v>10.736753105103476</v>
+        <v>37.24541999925836</v>
       </c>
       <c r="M55">
-        <v>0.1648843980798908</v>
+        <v>0.1620849813911808</v>
       </c>
     </row>
     <row r="56" spans="2:13">
@@ -9652,10 +9652,10 @@
         <v>495</v>
       </c>
       <c r="L56">
-        <v>76.980139616281647</v>
+        <v>58.259620298985368</v>
       </c>
       <c r="M56">
-        <v>0.1942330002128338</v>
+        <v>0.1679193658497497</v>
       </c>
     </row>
     <row r="57" spans="2:13">
@@ -9687,10 +9687,10 @@
         <v>496</v>
       </c>
       <c r="L57">
-        <v>67.575478267611928</v>
+        <v>34.55884381213928</v>
       </c>
       <c r="M57">
-        <v>0.18659143930349489</v>
+        <v>0.16245559975399679</v>
       </c>
     </row>
     <row r="58" spans="2:13">
@@ -9722,10 +9722,10 @@
         <v>497</v>
       </c>
       <c r="L58">
-        <v>43.46901091863117</v>
+        <v>10.064514737858641</v>
       </c>
       <c r="M58">
-        <v>0.1845616964539607</v>
+        <v>0.1782125290435467</v>
       </c>
     </row>
     <row r="59" spans="2:13">
@@ -9757,10 +9757,10 @@
         <v>498</v>
       </c>
       <c r="L59">
-        <v>19.141897016314882</v>
+        <v>34.250580806419769</v>
       </c>
       <c r="M59">
-        <v>0.1759881475863854</v>
+        <v>0.18677750076056901</v>
       </c>
     </row>
     <row r="60" spans="2:13">
@@ -9792,10 +9792,10 @@
         <v>499</v>
       </c>
       <c r="L60">
-        <v>44.296173015366222</v>
+        <v>36.756724994783454</v>
       </c>
       <c r="M60">
-        <v>0.1790477452195498</v>
+        <v>0.15811795770101539</v>
       </c>
     </row>
     <row r="61" spans="2:13">
@@ -9827,10 +9827,10 @@
         <v>500</v>
       </c>
       <c r="L61">
-        <v>52.566222697559198</v>
+        <v>47.687089697169917</v>
       </c>
       <c r="M61">
-        <v>0.17584129565459211</v>
+        <v>0.15219188096048419</v>
       </c>
     </row>
     <row r="62" spans="2:13">
@@ -9862,10 +9862,10 @@
         <v>501</v>
       </c>
       <c r="L62">
-        <v>62.536940060613063</v>
+        <v>29.450969020339425</v>
       </c>
       <c r="M62">
-        <v>0.1863185515331568</v>
+        <v>0.2002259396579224</v>
       </c>
     </row>
     <row r="63" spans="2:13">
@@ -9897,10 +9897,10 @@
         <v>502</v>
       </c>
       <c r="L63">
-        <v>35.407308507489127</v>
+        <v>30.446650112319261</v>
       </c>
       <c r="M63">
-        <v>0.19316143607249939</v>
+        <v>0.199109821920088</v>
       </c>
     </row>
     <row r="64" spans="2:13">
@@ -9932,10 +9932,10 @@
         <v>503</v>
       </c>
       <c r="L64">
-        <v>73.511967253798687</v>
+        <v>17.987672447370127</v>
       </c>
       <c r="M64">
-        <v>0.1893437985659718</v>
+        <v>0.20821004048159419</v>
       </c>
     </row>
     <row r="65" spans="2:13">
@@ -9967,10 +9967,10 @@
         <v>504</v>
       </c>
       <c r="L65">
-        <v>36.343836507988406</v>
+        <v>30.097408872140651</v>
       </c>
       <c r="M65">
-        <v>0.1972860253708511</v>
+        <v>0.20474189657099751</v>
       </c>
     </row>
     <row r="66" spans="2:13">
@@ -10002,10 +10002,10 @@
         <v>505</v>
       </c>
       <c r="L66">
-        <v>15.555065526006649</v>
+        <v>27.123432995585144</v>
       </c>
       <c r="M66">
-        <v>0.19351361790619129</v>
+        <v>0.19876008739927989</v>
       </c>
     </row>
     <row r="67" spans="2:13">
@@ -10037,10 +10037,10 @@
         <v>506</v>
       </c>
       <c r="L67">
-        <v>19.627861573037901</v>
+        <v>53.873895318635284</v>
       </c>
       <c r="M67">
-        <v>0.1900172849762663</v>
+        <v>0.1981168191382951</v>
       </c>
     </row>
     <row r="68" spans="2:13">
@@ -10072,10 +10072,10 @@
         <v>507</v>
       </c>
       <c r="L68">
-        <v>21.939960958659629</v>
+        <v>46.95289749110988</v>
       </c>
       <c r="M68">
-        <v>0.18708910898859191</v>
+        <v>0.210909043010298</v>
       </c>
     </row>
     <row r="69" spans="2:13">
@@ -10107,10 +10107,10 @@
         <v>508</v>
       </c>
       <c r="L69">
-        <v>38.329329922796383</v>
+        <v>49.108374048489274</v>
       </c>
       <c r="M69">
-        <v>0.199130716948445</v>
+        <v>0.2031232586420447</v>
       </c>
     </row>
     <row r="70" spans="2:13">
@@ -10142,10 +10142,10 @@
         <v>509</v>
       </c>
       <c r="L70">
-        <v>38.633614420819661</v>
+        <v>35.383539784496271</v>
       </c>
       <c r="M70">
-        <v>0.2017933273944324</v>
+        <v>0.20207111633609509</v>
       </c>
     </row>
     <row r="71" spans="2:13">
@@ -10177,10 +10177,10 @@
         <v>510</v>
       </c>
       <c r="L71">
-        <v>21.775605643070985</v>
+        <v>96.162057973148151</v>
       </c>
       <c r="M71">
-        <v>0.20116012411352879</v>
+        <v>0.1954935180327507</v>
       </c>
     </row>
     <row r="72" spans="2:13">
@@ -10212,10 +10212,10 @@
         <v>511</v>
       </c>
       <c r="L72">
-        <v>30.446650112319261</v>
+        <v>54.390035001527998</v>
       </c>
       <c r="M72">
-        <v>0.199109821920088</v>
+        <v>0.19138533080755779</v>
       </c>
     </row>
     <row r="73" spans="2:13">
@@ -10247,10 +10247,10 @@
         <v>512</v>
       </c>
       <c r="L73">
-        <v>33.067956850359536</v>
+        <v>41.631829564740578</v>
       </c>
       <c r="M73">
-        <v>0.19948033307117469</v>
+        <v>0.18735306464157331</v>
       </c>
     </row>
     <row r="74" spans="2:13">
@@ -10282,10 +10282,10 @@
         <v>513</v>
       </c>
       <c r="L74">
-        <v>37.91841582751514</v>
+        <v>37.300333480035924</v>
       </c>
       <c r="M74">
-        <v>0.2024779425192785</v>
+        <v>0.19504615999068811</v>
       </c>
     </row>
     <row r="75" spans="2:13">
@@ -10317,10 +10317,10 @@
         <v>514</v>
       </c>
       <c r="L75">
-        <v>48.238244896751475</v>
+        <v>51.809973437327038</v>
       </c>
       <c r="M75">
-        <v>0.20277423117452531</v>
+        <v>0.20078874278333661</v>
       </c>
     </row>
     <row r="76" spans="2:13">
@@ -10352,10 +10352,10 @@
         <v>515</v>
       </c>
       <c r="L76">
-        <v>43.246387592074967</v>
+        <v>65.626621731828337</v>
       </c>
       <c r="M76">
-        <v>0.1989176326295678</v>
+        <v>0.20730931349248</v>
       </c>
     </row>
     <row r="77" spans="2:13">
@@ -10387,10 +10387,10 @@
         <v>516</v>
       </c>
       <c r="L77">
-        <v>71.577746659444344</v>
+        <v>66.483178532863946</v>
       </c>
       <c r="M77">
-        <v>0.2139219328312395</v>
+        <v>0.2056891978530197</v>
       </c>
     </row>
     <row r="78" spans="2:13">
@@ -10422,10 +10422,10 @@
         <v>517</v>
       </c>
       <c r="L78">
-        <v>27.290562600154423</v>
+        <v>114.37648773077015</v>
       </c>
       <c r="M78">
-        <v>0.2072999034636912</v>
+        <v>0.2098947805289568</v>
       </c>
     </row>
     <row r="79" spans="2:13">
@@ -10457,10 +10457,10 @@
         <v>518</v>
       </c>
       <c r="L79">
-        <v>15.058507206639904</v>
+        <v>16.56797374935983</v>
       </c>
       <c r="M79">
-        <v>0.20242670955853831</v>
+        <v>0.19392918042899221</v>
       </c>
     </row>
     <row r="80" spans="2:13">
@@ -10492,10 +10492,10 @@
         <v>519</v>
       </c>
       <c r="L80">
-        <v>70.994458156111492</v>
+        <v>36.443267369753706</v>
       </c>
       <c r="M80">
-        <v>0.20320229377893859</v>
+        <v>0.1985358347882934</v>
       </c>
     </row>
     <row r="81" spans="2:13">
@@ -10527,10 +10527,10 @@
         <v>520</v>
       </c>
       <c r="L81">
-        <v>90.346324868285237</v>
+        <v>25.012815082390134</v>
       </c>
       <c r="M81">
-        <v>0.21103342832633221</v>
+        <v>0.21503442026567179</v>
       </c>
     </row>
     <row r="82" spans="2:13">
@@ -10562,10 +10562,10 @@
         <v>521</v>
       </c>
       <c r="L82">
-        <v>35.383539784496271</v>
+        <v>36.280333941708669</v>
       </c>
       <c r="M82">
-        <v>0.20207111633609509</v>
+        <v>0.21465727702035819</v>
       </c>
     </row>
     <row r="83" spans="2:13">
@@ -10597,10 +10597,10 @@
         <v>522</v>
       </c>
       <c r="L83">
-        <v>96.162057973148151</v>
+        <v>27.290562600154423</v>
       </c>
       <c r="M83">
-        <v>0.1954935180327507</v>
+        <v>0.2072999034636912</v>
       </c>
     </row>
     <row r="84" spans="2:13">
@@ -10632,10 +10632,10 @@
         <v>523</v>
       </c>
       <c r="L84">
-        <v>77.282669643239643</v>
+        <v>86.913257778164393</v>
       </c>
       <c r="M84">
-        <v>0.19814963316409229</v>
+        <v>0.21313674274492611</v>
       </c>
     </row>
     <row r="85" spans="2:13">
@@ -10667,10 +10667,10 @@
         <v>524</v>
       </c>
       <c r="L85">
-        <v>41.631829564740578</v>
+        <v>21.527733591016013</v>
       </c>
       <c r="M85">
-        <v>0.18735306464157331</v>
+        <v>0.193687449154858</v>
       </c>
     </row>
     <row r="86" spans="2:13">
@@ -10702,10 +10702,10 @@
         <v>525</v>
       </c>
       <c r="L86">
-        <v>54.390035001527998</v>
+        <v>39.154409268100238</v>
       </c>
       <c r="M86">
-        <v>0.19138533080755779</v>
+        <v>0.20043267140226859</v>
       </c>
     </row>
     <row r="87" spans="2:13">
@@ -10737,10 +10737,10 @@
         <v>526</v>
       </c>
       <c r="L87">
-        <v>54.605963762940704</v>
+        <v>38.034133416026243</v>
       </c>
       <c r="M87">
-        <v>0.22735107957779929</v>
+        <v>0.18851542464754689</v>
       </c>
     </row>
     <row r="88" spans="2:13">
@@ -10772,10 +10772,10 @@
         <v>527</v>
       </c>
       <c r="L88">
-        <v>175.12973688807696</v>
+        <v>74.34884208240716</v>
       </c>
       <c r="M88">
-        <v>0.23068034671789481</v>
+        <v>0.19271564492693199</v>
       </c>
     </row>
     <row r="89" spans="2:13">
@@ -10807,10 +10807,10 @@
         <v>528</v>
       </c>
       <c r="L89">
-        <v>67.200368566030306</v>
+        <v>21.695631963640611</v>
       </c>
       <c r="M89">
-        <v>0.2221875814870429</v>
+        <v>0.1865416469139253</v>
       </c>
     </row>
     <row r="90" spans="2:13">
@@ -10842,10 +10842,10 @@
         <v>529</v>
       </c>
       <c r="L90">
-        <v>38.537570866409204</v>
+        <v>50.954148411424029</v>
       </c>
       <c r="M90">
-        <v>0.24282251615404579</v>
+        <v>0.18647021730564081</v>
       </c>
     </row>
     <row r="91" spans="2:13">
@@ -10877,10 +10877,10 @@
         <v>530</v>
       </c>
       <c r="L91">
-        <v>127.78604768705938</v>
+        <v>13.136876522631956</v>
       </c>
       <c r="M91">
-        <v>0.2232922850044185</v>
+        <v>0.1869863724066749</v>
       </c>
     </row>
     <row r="92" spans="2:13">
@@ -10912,10 +10912,10 @@
         <v>531</v>
       </c>
       <c r="L92">
-        <v>220.1245054835791</v>
+        <v>21.347164069791887</v>
       </c>
       <c r="M92">
-        <v>0.25809435387120577</v>
+        <v>0.1899761010940321</v>
       </c>
     </row>
     <row r="93" spans="2:13">
@@ -10947,10 +10947,10 @@
         <v>532</v>
       </c>
       <c r="L93">
-        <v>125.0421936728755</v>
+        <v>71.694878454156282</v>
       </c>
       <c r="M93">
-        <v>0.25323200652297079</v>
+        <v>0.2315816292473174</v>
       </c>
     </row>
     <row r="94" spans="2:13">
@@ -10982,10 +10982,10 @@
         <v>533</v>
       </c>
       <c r="L94">
-        <v>106.50469456571774</v>
+        <v>64.91056981417421</v>
       </c>
       <c r="M94">
-        <v>0.2564312686188745</v>
+        <v>0.2348270149225701</v>
       </c>
     </row>
     <row r="95" spans="2:13">
@@ -11017,10 +11017,10 @@
         <v>534</v>
       </c>
       <c r="L95">
-        <v>93.623847561248198</v>
+        <v>14.810622051107686</v>
       </c>
       <c r="M95">
-        <v>0.2484988957546431</v>
+        <v>0.2146498990053326</v>
       </c>
     </row>
     <row r="96" spans="2:13">
@@ -11052,10 +11052,10 @@
         <v>535</v>
       </c>
       <c r="L96">
-        <v>134.74267221045218</v>
+        <v>167.45420030081794</v>
       </c>
       <c r="M96">
-        <v>0.25088249527357021</v>
+        <v>0.23426263205620779</v>
       </c>
     </row>
     <row r="97" spans="2:13">
@@ -11087,10 +11087,10 @@
         <v>536</v>
       </c>
       <c r="L97">
-        <v>122.81830894407922</v>
+        <v>209.36352339932586</v>
       </c>
       <c r="M97">
-        <v>0.26593712271619269</v>
+        <v>0.26047506359023109</v>
       </c>
     </row>
     <row r="98" spans="2:13">
@@ -11122,10 +11122,10 @@
         <v>537</v>
       </c>
       <c r="L98">
-        <v>184.59748150959012</v>
+        <v>125.0421936728755</v>
       </c>
       <c r="M98">
-        <v>0.26693517306225112</v>
+        <v>0.25323200652297079</v>
       </c>
     </row>
     <row r="99" spans="2:13">
@@ -11157,10 +11157,10 @@
         <v>538</v>
       </c>
       <c r="L99">
-        <v>44.315095544278407</v>
+        <v>106.50469456571774</v>
       </c>
       <c r="M99">
-        <v>0.18483228811876889</v>
+        <v>0.2564312686188745</v>
       </c>
     </row>
     <row r="100" spans="2:13">
@@ -11192,10 +11192,10 @@
         <v>539</v>
       </c>
       <c r="L100">
-        <v>232.8312308939355</v>
+        <v>237.30132193657082</v>
       </c>
       <c r="M100">
-        <v>0.2599721923522243</v>
+        <v>0.25992957830273011</v>
       </c>
     </row>
     <row r="101" spans="2:13">
@@ -11227,10 +11227,10 @@
         <v>540</v>
       </c>
       <c r="L101">
-        <v>237.3125947285518</v>
+        <v>134.36453257759621</v>
       </c>
       <c r="M101">
-        <v>0.2569796863330549</v>
+        <v>0.25455161792749548</v>
       </c>
     </row>
     <row r="102" spans="2:13">
@@ -11262,10 +11262,10 @@
         <v>541</v>
       </c>
       <c r="L102">
-        <v>117.7047993721967</v>
+        <v>136.31520207697037</v>
       </c>
       <c r="M102">
-        <v>0.26344010128890311</v>
+        <v>0.26557139759279652</v>
       </c>
     </row>
     <row r="103" spans="2:13">
@@ -11297,10 +11297,10 @@
         <v>542</v>
       </c>
       <c r="L103">
-        <v>164.21225956981655</v>
+        <v>244.07982797336319</v>
       </c>
       <c r="M103">
-        <v>0.26982501635886152</v>
+        <v>0.2652621550123801</v>
       </c>
     </row>
     <row r="104" spans="2:13">
@@ -11332,10 +11332,10 @@
         <v>543</v>
       </c>
       <c r="L104">
-        <v>10.488125435887309</v>
+        <v>67.200368566030306</v>
       </c>
       <c r="M104">
-        <v>0.2067559109554217</v>
+        <v>0.2221875814870429</v>
       </c>
     </row>
     <row r="105" spans="2:13">
@@ -11367,10 +11367,10 @@
         <v>544</v>
       </c>
       <c r="L105">
-        <v>5.0008905263973453</v>
+        <v>38.537570866409204</v>
       </c>
       <c r="M105">
-        <v>0.19503375193778411</v>
+        <v>0.24282251615404579</v>
       </c>
     </row>
     <row r="106" spans="2:13">
@@ -11402,10 +11402,10 @@
         <v>545</v>
       </c>
       <c r="L106">
-        <v>6.6840123845152251</v>
+        <v>127.78604768705938</v>
       </c>
       <c r="M106">
-        <v>0.2141200513124536</v>
+        <v>0.2232922850044185</v>
       </c>
     </row>
     <row r="107" spans="2:13">
@@ -11437,10 +11437,10 @@
         <v>546</v>
       </c>
       <c r="L107">
-        <v>12.395423246580084</v>
+        <v>54.605963762940704</v>
       </c>
       <c r="M107">
-        <v>0.18675995802731521</v>
+        <v>0.22735107957779929</v>
       </c>
     </row>
     <row r="108" spans="2:13">
@@ -11472,10 +11472,10 @@
         <v>547</v>
       </c>
       <c r="L108">
-        <v>1.1181040952551544</v>
+        <v>175.12973688807696</v>
       </c>
       <c r="M108">
-        <v>0.1943037729184805</v>
+        <v>0.23068034671789481</v>
       </c>
     </row>
     <row r="109" spans="2:13">
@@ -11507,10 +11507,10 @@
         <v>548</v>
       </c>
       <c r="L109">
-        <v>3.2512160306520941</v>
+        <v>135.6757784598411</v>
       </c>
       <c r="M109">
-        <v>0.17128851588860269</v>
+        <v>0.26557640883383399</v>
       </c>
     </row>
     <row r="110" spans="2:13">
@@ -11542,10 +11542,10 @@
         <v>549</v>
       </c>
       <c r="L110">
-        <v>19.968627786259088</v>
+        <v>155.12844663149514</v>
       </c>
       <c r="M110">
-        <v>0.18398820412312869</v>
+        <v>0.26625741973236589</v>
       </c>
     </row>
     <row r="111" spans="2:13">
@@ -11577,10 +11577,10 @@
         <v>550</v>
       </c>
       <c r="L111">
-        <v>2.1954042424006839</v>
+        <v>151.64055934417638</v>
       </c>
       <c r="M111">
-        <v>0.18636357582837329</v>
+        <v>0.24899338633215329</v>
       </c>
     </row>
     <row r="112" spans="2:13">
@@ -11612,10 +11612,10 @@
         <v>551</v>
       </c>
       <c r="L112">
-        <v>10.733218236351123</v>
+        <v>104.09850787411044</v>
       </c>
       <c r="M112">
-        <v>0.2114617430780634</v>
+        <v>0.25161303553359088</v>
       </c>
     </row>
     <row r="113" spans="2:13">
@@ -11647,10 +11647,10 @@
         <v>552</v>
       </c>
       <c r="L113">
-        <v>98.957410819089432</v>
+        <v>13.379525489675059</v>
       </c>
       <c r="M113">
-        <v>0.2080430400445048</v>
+        <v>0.2103685864960351</v>
       </c>
     </row>
     <row r="114" spans="2:13">
@@ -11682,10 +11682,10 @@
         <v>553</v>
       </c>
       <c r="L114">
-        <v>66.562100080130492</v>
+        <v>5.0008905263973453</v>
       </c>
       <c r="M114">
-        <v>0.20078938560855061</v>
+        <v>0.19503375193778411</v>
       </c>
     </row>
     <row r="115" spans="2:13">
@@ -11717,10 +11717,10 @@
         <v>554</v>
       </c>
       <c r="L115">
-        <v>46.543854173501828</v>
+        <v>3.7926123307274753</v>
       </c>
       <c r="M115">
-        <v>0.2051910322723923</v>
+        <v>0.20698955488970081</v>
       </c>
     </row>
     <row r="116" spans="2:13">
@@ -11752,10 +11752,10 @@
         <v>555</v>
       </c>
       <c r="L116">
-        <v>46.899383790804556</v>
+        <v>8.8929123508088175</v>
       </c>
       <c r="M116">
-        <v>0.20374984720815631</v>
+        <v>0.21381718170096059</v>
       </c>
     </row>
     <row r="117" spans="2:13">
@@ -11787,10 +11787,10 @@
         <v>556</v>
       </c>
       <c r="L117">
-        <v>52.165420911105102</v>
+        <v>3.540964421634488</v>
       </c>
       <c r="M117">
-        <v>0.20544382891806809</v>
+        <v>0.1826040712409368</v>
       </c>
     </row>
     <row r="118" spans="2:13">
@@ -11822,10 +11822,10 @@
         <v>557</v>
       </c>
       <c r="L118">
-        <v>27.771480493502811</v>
+        <v>7.8378680260708098</v>
       </c>
       <c r="M118">
-        <v>0.2124303886334892</v>
+        <v>0.17072991636977089</v>
       </c>
     </row>
     <row r="119" spans="2:13">
@@ -11857,10 +11857,10 @@
         <v>558</v>
       </c>
       <c r="L119">
-        <v>65.937821941086867</v>
+        <v>12.395423246580084</v>
       </c>
       <c r="M119">
-        <v>0.211053727222376</v>
+        <v>0.18675995802731521</v>
       </c>
     </row>
     <row r="120" spans="2:13">
@@ -11892,10 +11892,10 @@
         <v>559</v>
       </c>
       <c r="L120">
-        <v>17.987672447370127</v>
+        <v>4.0357101279429894</v>
       </c>
       <c r="M120">
-        <v>0.20821004048159419</v>
+        <v>0.19261813695505661</v>
       </c>
     </row>
     <row r="121" spans="2:13">
@@ -11927,10 +11927,10 @@
         <v>560</v>
       </c>
       <c r="L121">
-        <v>55.688391986147749</v>
+        <v>16.303431906674476</v>
       </c>
       <c r="M121">
-        <v>0.21208469420755149</v>
+        <v>0.1857784167557944</v>
       </c>
     </row>
     <row r="122" spans="2:13">
@@ -11962,10 +11962,10 @@
         <v>561</v>
       </c>
       <c r="L122">
-        <v>117.19163040859445</v>
+        <v>98.957410819089432</v>
       </c>
       <c r="M122">
-        <v>0.20971105792450609</v>
+        <v>0.2080430400445048</v>
       </c>
     </row>
     <row r="123" spans="2:13">
@@ -11997,10 +11997,10 @@
         <v>562</v>
       </c>
       <c r="L123">
-        <v>94.869571421541906</v>
+        <v>66.562100080130492</v>
       </c>
       <c r="M123">
-        <v>0.21957584983476219</v>
+        <v>0.20078938560855061</v>
       </c>
     </row>
     <row r="124" spans="2:13">
@@ -12032,10 +12032,10 @@
         <v>563</v>
       </c>
       <c r="L124">
-        <v>56.673777808988802</v>
+        <v>46.543854173501828</v>
       </c>
       <c r="M124">
-        <v>0.22618462403482081</v>
+        <v>0.2051910322723923</v>
       </c>
     </row>
     <row r="125" spans="2:13">
@@ -12067,10 +12067,10 @@
         <v>564</v>
       </c>
       <c r="L125">
-        <v>87.094495862899819</v>
+        <v>46.899383790804556</v>
       </c>
       <c r="M125">
-        <v>0.2182147368755028</v>
+        <v>0.20374984720815631</v>
       </c>
     </row>
     <row r="126" spans="2:13">
@@ -12102,10 +12102,10 @@
         <v>565</v>
       </c>
       <c r="L126">
-        <v>18.009923770498993</v>
+        <v>68.335245151937812</v>
       </c>
       <c r="M126">
-        <v>0.23885275205974249</v>
+        <v>0.2133456452392031</v>
       </c>
     </row>
     <row r="127" spans="2:13">
@@ -12137,10 +12137,10 @@
         <v>566</v>
       </c>
       <c r="L127">
-        <v>6.3563441369422042</v>
+        <v>52.165420911105102</v>
       </c>
       <c r="M127">
-        <v>0.2217302442008218</v>
+        <v>0.20544382891806809</v>
       </c>
     </row>
     <row r="128" spans="2:13">
@@ -12172,10 +12172,10 @@
         <v>567</v>
       </c>
       <c r="L128">
-        <v>76.988777125887211</v>
+        <v>27.771480493502811</v>
       </c>
       <c r="M128">
-        <v>0.24778976887935469</v>
+        <v>0.2124303886334892</v>
       </c>
     </row>
     <row r="129" spans="2:13">
@@ -12207,10 +12207,10 @@
         <v>568</v>
       </c>
       <c r="L129">
-        <v>80.635334153425532</v>
+        <v>85.201355568683795</v>
       </c>
       <c r="M129">
-        <v>0.24056496325694929</v>
+        <v>0.21774945747956209</v>
       </c>
     </row>
     <row r="130" spans="2:13">
@@ -12242,10 +12242,10 @@
         <v>569</v>
       </c>
       <c r="L130">
-        <v>56.480378608181226</v>
+        <v>65.017353068811516</v>
       </c>
       <c r="M130">
-        <v>0.23585104488225389</v>
+        <v>0.2212406873342358</v>
       </c>
     </row>
     <row r="131" spans="2:13">
@@ -12277,10 +12277,10 @@
         <v>570</v>
       </c>
       <c r="L131">
-        <v>145.78165986493678</v>
+        <v>56.673777808988802</v>
       </c>
       <c r="M131">
-        <v>0.24857144829471911</v>
+        <v>0.22618462403482081</v>
       </c>
     </row>
     <row r="132" spans="2:13">
@@ -12312,10 +12312,10 @@
         <v>571</v>
       </c>
       <c r="L132">
-        <v>127.24471060800822</v>
+        <v>33.910289077121611</v>
       </c>
       <c r="M132">
-        <v>0.23431281290271019</v>
+        <v>0.2356128082494863</v>
       </c>
     </row>
     <row r="133" spans="2:13">
@@ -12347,10 +12347,10 @@
         <v>572</v>
       </c>
       <c r="L133">
-        <v>72.369257489130703</v>
+        <v>120.69179902137029</v>
       </c>
       <c r="M133">
-        <v>0.2396892714131334</v>
+        <v>0.24484863738727439</v>
       </c>
     </row>
     <row r="134" spans="2:13">
@@ -12382,10 +12382,10 @@
         <v>573</v>
       </c>
       <c r="L134">
-        <v>118.52374047040144</v>
+        <v>186.58940322981067</v>
       </c>
       <c r="M134">
-        <v>0.24180258287082959</v>
+        <v>0.24731846680756769</v>
       </c>
     </row>
     <row r="135" spans="2:13">
@@ -12417,10 +12417,10 @@
         <v>574</v>
       </c>
       <c r="L135">
-        <v>46.352154031562087</v>
+        <v>105.39710589363379</v>
       </c>
       <c r="M135">
-        <v>0.23001042545744649</v>
+        <v>0.23994421883163031</v>
       </c>
     </row>
     <row r="136" spans="2:13">
@@ -12452,10 +12452,10 @@
         <v>575</v>
       </c>
       <c r="L136">
-        <v>53.231469618806599</v>
+        <v>93.387510011901071</v>
       </c>
       <c r="M136">
-        <v>0.2210385330909391</v>
+        <v>0.2411162759006428</v>
       </c>
     </row>
     <row r="137" spans="2:13">
@@ -12487,10 +12487,10 @@
         <v>576</v>
       </c>
       <c r="L137">
-        <v>14.810622051107686</v>
+        <v>70.580206577230754</v>
       </c>
       <c r="M137">
-        <v>0.2146498990053326</v>
+        <v>0.20987633572454861</v>
       </c>
     </row>
     <row r="138" spans="2:13">
@@ -12522,10 +12522,10 @@
         <v>577</v>
       </c>
       <c r="L138">
-        <v>87.52815306177925</v>
+        <v>66.33910154388785</v>
       </c>
       <c r="M138">
-        <v>0.23158446945738051</v>
+        <v>0.2092426717534783</v>
       </c>
     </row>
     <row r="139" spans="2:13">
@@ -12557,10 +12557,10 @@
         <v>578</v>
       </c>
       <c r="L139">
-        <v>147.87654035284154</v>
+        <v>47.141091988789746</v>
       </c>
       <c r="M139">
-        <v>0.2355601819263797</v>
+        <v>0.21946266003705239</v>
       </c>
     </row>
     <row r="140" spans="2:13">
@@ -12592,10 +12592,10 @@
         <v>579</v>
       </c>
       <c r="L140">
-        <v>34.67719391798564</v>
+        <v>80.821562968752872</v>
       </c>
       <c r="M140">
-        <v>0.21969320339597209</v>
+        <v>0.23179082785061439</v>
       </c>
     </row>
     <row r="141" spans="2:13">
@@ -12627,10 +12627,10 @@
         <v>580</v>
       </c>
       <c r="L141">
-        <v>13.929838457103745</v>
+        <v>31.601677138089638</v>
       </c>
       <c r="M141">
-        <v>0.19887898416449371</v>
+        <v>0.20062163822454471</v>
       </c>
     </row>
     <row r="142" spans="2:13">
@@ -12662,10 +12662,10 @@
         <v>581</v>
       </c>
       <c r="L142">
-        <v>55.5034437133694</v>
+        <v>8.11122871070679</v>
       </c>
       <c r="M142">
-        <v>0.2050911118780229</v>
+        <v>0.19860019106929819</v>
       </c>
     </row>
     <row r="143" spans="2:13">
@@ -12697,10 +12697,10 @@
         <v>582</v>
       </c>
       <c r="L143">
-        <v>28.815441471494655</v>
+        <v>7.832015876439665</v>
       </c>
       <c r="M143">
-        <v>0.21404925362950949</v>
+        <v>0.21689776343849121</v>
       </c>
     </row>
     <row r="144" spans="2:13">
@@ -12732,10 +12732,10 @@
         <v>583</v>
       </c>
       <c r="L144">
-        <v>58.765805134146412</v>
+        <v>81.180155151800534</v>
       </c>
       <c r="M144">
-        <v>0.2089141549077439</v>
+        <v>0.2346373276834133</v>
       </c>
     </row>
     <row r="145" spans="2:13">
@@ -12767,10 +12767,10 @@
         <v>584</v>
       </c>
       <c r="L145">
-        <v>32.603038781092835</v>
+        <v>35.131863609606697</v>
       </c>
       <c r="M145">
-        <v>0.2247000509552344</v>
+        <v>0.21249777523500629</v>
       </c>
     </row>
     <row r="146" spans="2:13">
@@ -12802,10 +12802,10 @@
         <v>585</v>
       </c>
       <c r="L146">
-        <v>70.580206577230754</v>
+        <v>44.151543827032945</v>
       </c>
       <c r="M146">
-        <v>0.20987633572454861</v>
+        <v>0.2217114670127418</v>
       </c>
     </row>
   </sheetData>
@@ -12814,7 +12814,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD555617-4CD3-4DE4-A9E3-CF155C12F7D6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEABED34-9C4D-4891-A9E4-FE6250814ED0}">
   <dimension ref="B9:Z124"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12929,10 +12929,10 @@
         <v>814</v>
       </c>
       <c r="L11">
-        <v>28.405496218485226</v>
+        <v>26.630947194643543</v>
       </c>
       <c r="M11">
-        <v>0.1274468566141789</v>
+        <v>0.1330107246767826</v>
       </c>
       <c r="O11" t="s">
         <v>171</v>
@@ -12997,10 +12997,10 @@
         <v>815</v>
       </c>
       <c r="L12">
-        <v>41.324048620902452</v>
+        <v>18.678286507640205</v>
       </c>
       <c r="M12">
-        <v>0.14883603887935401</v>
+        <v>9.9146390855766098E-2</v>
       </c>
       <c r="O12" t="s">
         <v>171</v>
@@ -13030,10 +13030,10 @@
         <v>997</v>
       </c>
       <c r="Y12">
-        <v>11.169750000000001</v>
+        <v>2.9205000000000001</v>
       </c>
       <c r="Z12">
-        <v>0.35618265805896843</v>
+        <v>0.33692562864079578</v>
       </c>
     </row>
     <row r="13" spans="2:26">
@@ -13065,10 +13065,10 @@
         <v>816</v>
       </c>
       <c r="L13">
-        <v>26.514335766194161</v>
+        <v>15.899438671120063</v>
       </c>
       <c r="M13">
-        <v>0.1617468027379507</v>
+        <v>0.1247096293119087</v>
       </c>
       <c r="O13" t="s">
         <v>171</v>
@@ -13098,10 +13098,10 @@
         <v>998</v>
       </c>
       <c r="Y13">
-        <v>46.060499999999998</v>
+        <v>8.24925</v>
       </c>
       <c r="Z13">
-        <v>0.62013697787600364</v>
+        <v>0.36300026625556497</v>
       </c>
     </row>
     <row r="14" spans="2:26">
@@ -13133,10 +13133,10 @@
         <v>817</v>
       </c>
       <c r="L14">
-        <v>31.750345361949169</v>
+        <v>12.882454041420184</v>
       </c>
       <c r="M14">
-        <v>0.12627514348516219</v>
+        <v>0.11462939982053159</v>
       </c>
       <c r="O14" t="s">
         <v>171</v>
@@ -13166,10 +13166,10 @@
         <v>999</v>
       </c>
       <c r="Y14">
-        <v>15.442500000000001</v>
+        <v>46.060499999999998</v>
       </c>
       <c r="Z14">
-        <v>0.58020399158725766</v>
+        <v>0.62013697787600364</v>
       </c>
     </row>
     <row r="15" spans="2:26">
@@ -13201,10 +13201,10 @@
         <v>818</v>
       </c>
       <c r="L15">
-        <v>74.620212768296852</v>
+        <v>25.481182734267183</v>
       </c>
       <c r="M15">
-        <v>0.2051905019556591</v>
+        <v>0.16686540071456679</v>
       </c>
       <c r="O15" t="s">
         <v>171</v>
@@ -13234,10 +13234,10 @@
         <v>1000</v>
       </c>
       <c r="Y15">
-        <v>81.801000000000002</v>
+        <v>15.442500000000001</v>
       </c>
       <c r="Z15">
-        <v>0.52136979412530338</v>
+        <v>0.58020399158725766</v>
       </c>
     </row>
     <row r="16" spans="2:26">
@@ -13269,10 +13269,10 @@
         <v>819</v>
       </c>
       <c r="L16">
-        <v>126.76290950485675</v>
+        <v>63.944973033631022</v>
       </c>
       <c r="M16">
-        <v>0.25051354653463281</v>
+        <v>0.2130050539275524</v>
       </c>
       <c r="O16" t="s">
         <v>171</v>
@@ -13302,10 +13302,10 @@
         <v>1001</v>
       </c>
       <c r="Y16">
-        <v>15.204750000000001</v>
+        <v>81.801000000000002</v>
       </c>
       <c r="Z16">
-        <v>0.41919766445259748</v>
+        <v>0.52136979412530338</v>
       </c>
     </row>
     <row r="17" spans="2:26">
@@ -13337,10 +13337,10 @@
         <v>820</v>
       </c>
       <c r="L17">
-        <v>26.630947194643543</v>
+        <v>50.213192681828922</v>
       </c>
       <c r="M17">
-        <v>0.1330107246767826</v>
+        <v>0.1790024310206553</v>
       </c>
       <c r="O17" t="s">
         <v>171</v>
@@ -13370,10 +13370,10 @@
         <v>1002</v>
       </c>
       <c r="Y17">
-        <v>69.680250000000001</v>
+        <v>15.204750000000001</v>
       </c>
       <c r="Z17">
-        <v>0.47891990064732709</v>
+        <v>0.41919766445259748</v>
       </c>
     </row>
     <row r="18" spans="2:26">
@@ -13405,10 +13405,10 @@
         <v>821</v>
       </c>
       <c r="L18">
-        <v>18.678286507640205</v>
+        <v>41.324048620902452</v>
       </c>
       <c r="M18">
-        <v>9.9146390855766098E-2</v>
+        <v>0.14883603887935401</v>
       </c>
       <c r="O18" t="s">
         <v>171</v>
@@ -13438,10 +13438,10 @@
         <v>1003</v>
       </c>
       <c r="Y18">
-        <v>14.664</v>
+        <v>69.680250000000001</v>
       </c>
       <c r="Z18">
-        <v>0.3937337447004795</v>
+        <v>0.47891990064732709</v>
       </c>
     </row>
     <row r="19" spans="2:26">
@@ -13473,10 +13473,10 @@
         <v>822</v>
       </c>
       <c r="L19">
-        <v>15.899438671120063</v>
+        <v>31.750345361949169</v>
       </c>
       <c r="M19">
-        <v>0.1247096293119087</v>
+        <v>0.12627514348516219</v>
       </c>
       <c r="O19" t="s">
         <v>171</v>
@@ -13506,10 +13506,10 @@
         <v>1004</v>
       </c>
       <c r="Y19">
-        <v>25.998750000000001</v>
+        <v>14.664</v>
       </c>
       <c r="Z19">
-        <v>0.45366588918610878</v>
+        <v>0.3937337447004795</v>
       </c>
     </row>
     <row r="20" spans="2:26">
@@ -13541,10 +13541,10 @@
         <v>823</v>
       </c>
       <c r="L20">
-        <v>12.882454041420184</v>
+        <v>56.726267538495932</v>
       </c>
       <c r="M20">
-        <v>0.11462939982053159</v>
+        <v>0.1920326480494578</v>
       </c>
       <c r="O20" t="s">
         <v>171</v>
@@ -13574,10 +13574,10 @@
         <v>1005</v>
       </c>
       <c r="Y20">
-        <v>25.856249999999999</v>
+        <v>25.998750000000001</v>
       </c>
       <c r="Z20">
-        <v>0.38429579113266549</v>
+        <v>0.45366588918610878</v>
       </c>
     </row>
     <row r="21" spans="2:26">
@@ -13609,10 +13609,10 @@
         <v>824</v>
       </c>
       <c r="L21">
-        <v>25.481182734267183</v>
+        <v>80.717822614082124</v>
       </c>
       <c r="M21">
-        <v>0.16686540071456679</v>
+        <v>0.25018299394421989</v>
       </c>
       <c r="O21" t="s">
         <v>171</v>
@@ -13642,10 +13642,10 @@
         <v>1006</v>
       </c>
       <c r="Y21">
-        <v>31.433250000000001</v>
+        <v>25.856249999999999</v>
       </c>
       <c r="Z21">
-        <v>0.3042117046162659</v>
+        <v>0.38429579113266549</v>
       </c>
     </row>
     <row r="22" spans="2:26">
@@ -13677,10 +13677,10 @@
         <v>825</v>
       </c>
       <c r="L22">
-        <v>63.944973033631022</v>
+        <v>74.620212768296852</v>
       </c>
       <c r="M22">
-        <v>0.2130050539275524</v>
+        <v>0.2051905019556591</v>
       </c>
       <c r="O22" t="s">
         <v>171</v>
@@ -13710,10 +13710,10 @@
         <v>1007</v>
       </c>
       <c r="Y22">
-        <v>14.226000000000001</v>
+        <v>31.433250000000001</v>
       </c>
       <c r="Z22">
-        <v>0.41151118139653681</v>
+        <v>0.3042117046162659</v>
       </c>
     </row>
     <row r="23" spans="2:26">
@@ -13745,10 +13745,10 @@
         <v>826</v>
       </c>
       <c r="L23">
-        <v>50.213192681828922</v>
+        <v>28.405496218485226</v>
       </c>
       <c r="M23">
-        <v>0.1790024310206553</v>
+        <v>0.1274468566141789</v>
       </c>
       <c r="O23" t="s">
         <v>171</v>
@@ -13778,10 +13778,10 @@
         <v>1008</v>
       </c>
       <c r="Y23">
-        <v>48.12</v>
+        <v>14.226000000000001</v>
       </c>
       <c r="Z23">
-        <v>0.43783548044510862</v>
+        <v>0.41151118139653681</v>
       </c>
     </row>
     <row r="24" spans="2:26">
@@ -13813,10 +13813,10 @@
         <v>827</v>
       </c>
       <c r="L24">
-        <v>40.67280815175436</v>
+        <v>73.988498738362708</v>
       </c>
       <c r="M24">
-        <v>0.15876099896130999</v>
+        <v>0.2954921762320073</v>
       </c>
       <c r="O24" t="s">
         <v>171</v>
@@ -13846,10 +13846,10 @@
         <v>1009</v>
       </c>
       <c r="Y24">
-        <v>62.766750000000002</v>
+        <v>48.12</v>
       </c>
       <c r="Z24">
-        <v>0.45367400709416011</v>
+        <v>0.43783548044510862</v>
       </c>
     </row>
     <row r="25" spans="2:26">
@@ -13881,10 +13881,10 @@
         <v>828</v>
       </c>
       <c r="L25">
-        <v>9.9181931459856116</v>
+        <v>22.804129520393388</v>
       </c>
       <c r="M25">
-        <v>0.1147819853151657</v>
+        <v>0.12498897865038</v>
       </c>
       <c r="O25" t="s">
         <v>171</v>
@@ -13914,10 +13914,10 @@
         <v>1010</v>
       </c>
       <c r="Y25">
-        <v>46.749749999999999</v>
+        <v>62.766750000000002</v>
       </c>
       <c r="Z25">
-        <v>0.40140041140439542</v>
+        <v>0.45367400709416011</v>
       </c>
     </row>
     <row r="26" spans="2:26">
@@ -13949,10 +13949,10 @@
         <v>829</v>
       </c>
       <c r="L26">
-        <v>29.124995479335983</v>
+        <v>158.21877625226711</v>
       </c>
       <c r="M26">
-        <v>0.16129881921565589</v>
+        <v>0.31868179863838719</v>
       </c>
       <c r="O26" t="s">
         <v>171</v>
@@ -13982,10 +13982,10 @@
         <v>1011</v>
       </c>
       <c r="Y26">
-        <v>3.5197500000000002</v>
+        <v>46.749749999999999</v>
       </c>
       <c r="Z26">
-        <v>0.43178402473128108</v>
+        <v>0.40140041140439542</v>
       </c>
     </row>
     <row r="27" spans="2:26">
@@ -14017,10 +14017,10 @@
         <v>830</v>
       </c>
       <c r="L27">
-        <v>16.315774503024212</v>
+        <v>61.993862801553377</v>
       </c>
       <c r="M27">
-        <v>0.14950384273806111</v>
+        <v>0.35099490777634579</v>
       </c>
       <c r="O27" t="s">
         <v>171</v>
@@ -14050,10 +14050,10 @@
         <v>1012</v>
       </c>
       <c r="Y27">
-        <v>36.492750000000001</v>
+        <v>3.5197500000000002</v>
       </c>
       <c r="Z27">
-        <v>0.43232919123723879</v>
+        <v>0.43178402473128108</v>
       </c>
     </row>
     <row r="28" spans="2:26">
@@ -14085,10 +14085,10 @@
         <v>831</v>
       </c>
       <c r="L28">
-        <v>17.93705990820202</v>
+        <v>99.116417974238118</v>
       </c>
       <c r="M28">
-        <v>0.1201911978179976</v>
+        <v>0.37106334887479647</v>
       </c>
       <c r="O28" t="s">
         <v>171</v>
@@ -14118,10 +14118,10 @@
         <v>1013</v>
       </c>
       <c r="Y28">
-        <v>21.201750000000001</v>
+        <v>36.492750000000001</v>
       </c>
       <c r="Z28">
-        <v>0.31263448106626313</v>
+        <v>0.43232919123723879</v>
       </c>
     </row>
     <row r="29" spans="2:26">
@@ -14153,10 +14153,10 @@
         <v>832</v>
       </c>
       <c r="L29">
-        <v>36.287941797211339</v>
+        <v>105.70151682237133</v>
       </c>
       <c r="M29">
-        <v>0.1579684761992117</v>
+        <v>0.30636201190762657</v>
       </c>
       <c r="O29" t="s">
         <v>171</v>
@@ -14186,10 +14186,10 @@
         <v>1014</v>
       </c>
       <c r="Y29">
-        <v>30.971250000000001</v>
+        <v>21.201750000000001</v>
       </c>
       <c r="Z29">
-        <v>0.35716948760405598</v>
+        <v>0.31263448106626313</v>
       </c>
     </row>
     <row r="30" spans="2:26">
@@ -14221,10 +14221,10 @@
         <v>833</v>
       </c>
       <c r="L30">
-        <v>43.093321601651922</v>
+        <v>69.370747472350871</v>
       </c>
       <c r="M30">
-        <v>0.23075989939714769</v>
+        <v>0.30954691641769738</v>
       </c>
       <c r="O30" t="s">
         <v>171</v>
@@ -14254,10 +14254,10 @@
         <v>1015</v>
       </c>
       <c r="Y30">
-        <v>88.458749999999995</v>
+        <v>30.971250000000001</v>
       </c>
       <c r="Z30">
-        <v>0.4918679318573792</v>
+        <v>0.35716948760405598</v>
       </c>
     </row>
     <row r="31" spans="2:26">
@@ -14289,10 +14289,10 @@
         <v>834</v>
       </c>
       <c r="L31">
-        <v>64.500984166275529</v>
+        <v>145.862696002733</v>
       </c>
       <c r="M31">
-        <v>0.18310419861318289</v>
+        <v>0.30560758582290709</v>
       </c>
       <c r="O31" t="s">
         <v>171</v>
@@ -14322,10 +14322,10 @@
         <v>1016</v>
       </c>
       <c r="Y31">
-        <v>8.2784999999999993</v>
+        <v>85.379249999999999</v>
       </c>
       <c r="Z31">
-        <v>0.4779410340065996</v>
+        <v>0.51401636839644316</v>
       </c>
     </row>
     <row r="32" spans="2:26">
@@ -14357,10 +14357,10 @@
         <v>835</v>
       </c>
       <c r="L32">
-        <v>65.621250000000003</v>
+        <v>29.177228298407282</v>
       </c>
       <c r="M32">
-        <v>0.20994057548272141</v>
+        <v>0.12968987264819559</v>
       </c>
       <c r="O32" t="s">
         <v>171</v>
@@ -14390,10 +14390,10 @@
         <v>1017</v>
       </c>
       <c r="Y32">
-        <v>22.671749999999999</v>
+        <v>51.349499999999999</v>
       </c>
       <c r="Z32">
-        <v>0.46793731309344361</v>
+        <v>0.54386805091229928</v>
       </c>
     </row>
     <row r="33" spans="2:26">
@@ -14425,10 +14425,10 @@
         <v>836</v>
       </c>
       <c r="L33">
-        <v>53.321249999999999</v>
+        <v>51.627484821987814</v>
       </c>
       <c r="M33">
-        <v>0.217403457782638</v>
+        <v>0.30504302621453577</v>
       </c>
       <c r="O33" t="s">
         <v>171</v>
@@ -14458,10 +14458,10 @@
         <v>1018</v>
       </c>
       <c r="Y33">
-        <v>51.349499999999999</v>
+        <v>96.570750000000004</v>
       </c>
       <c r="Z33">
-        <v>0.54386805091229928</v>
+        <v>0.49645598696069448</v>
       </c>
     </row>
     <row r="34" spans="2:26">
@@ -14493,10 +14493,10 @@
         <v>837</v>
       </c>
       <c r="L34">
-        <v>94.912499999999994</v>
+        <v>51.352856098196355</v>
       </c>
       <c r="M34">
-        <v>0.1647728176804078</v>
+        <v>0.21916033990843409</v>
       </c>
       <c r="O34" t="s">
         <v>171</v>
@@ -14526,10 +14526,10 @@
         <v>1019</v>
       </c>
       <c r="Y34">
-        <v>85.918499999999995</v>
+        <v>8.2784999999999993</v>
       </c>
       <c r="Z34">
-        <v>0.51349138769042857</v>
+        <v>0.4779410340065996</v>
       </c>
     </row>
     <row r="35" spans="2:26">
@@ -14561,10 +14561,10 @@
         <v>838</v>
       </c>
       <c r="L35">
-        <v>28.571692239731817</v>
+        <v>48.015448204779155</v>
       </c>
       <c r="M35">
-        <v>0.1050664932730062</v>
+        <v>0.15726905125434551</v>
       </c>
       <c r="O35" t="s">
         <v>171</v>
@@ -14594,10 +14594,10 @@
         <v>1020</v>
       </c>
       <c r="Y35">
-        <v>40.835999999999999</v>
+        <v>55.935000000000002</v>
       </c>
       <c r="Z35">
-        <v>0.50126817210144614</v>
+        <v>0.480516993659309</v>
       </c>
     </row>
     <row r="36" spans="2:26">
@@ -14629,10 +14629,10 @@
         <v>839</v>
       </c>
       <c r="L36">
-        <v>44.138666856188586</v>
+        <v>9.9181931459856116</v>
       </c>
       <c r="M36">
-        <v>0.19469721132302881</v>
+        <v>0.1147819853151657</v>
       </c>
       <c r="O36" t="s">
         <v>171</v>
@@ -14697,10 +14697,10 @@
         <v>840</v>
       </c>
       <c r="L37">
-        <v>24.664813931534447</v>
+        <v>29.124995479335983</v>
       </c>
       <c r="M37">
-        <v>0.2048128116290337</v>
+        <v>0.16129881921565589</v>
       </c>
       <c r="O37" t="s">
         <v>171</v>
@@ -14765,10 +14765,10 @@
         <v>841</v>
       </c>
       <c r="L38">
-        <v>75.61415938768593</v>
+        <v>16.315774503024212</v>
       </c>
       <c r="M38">
-        <v>0.2659220722327813</v>
+        <v>0.14950384273806111</v>
       </c>
       <c r="O38" t="s">
         <v>171</v>
@@ -14833,10 +14833,10 @@
         <v>842</v>
       </c>
       <c r="L39">
-        <v>77.661746661491676</v>
+        <v>17.93705990820202</v>
       </c>
       <c r="M39">
-        <v>0.27059473511745702</v>
+        <v>0.1201911978179976</v>
       </c>
       <c r="O39" t="s">
         <v>171</v>
@@ -14901,10 +14901,10 @@
         <v>843</v>
       </c>
       <c r="L40">
-        <v>68.428690375212113</v>
+        <v>28.945301744186541</v>
       </c>
       <c r="M40">
-        <v>0.2630477290884114</v>
+        <v>0.16024232806829081</v>
       </c>
       <c r="O40" t="s">
         <v>171</v>
@@ -14969,10 +14969,10 @@
         <v>844</v>
       </c>
       <c r="L41">
-        <v>19.438384614656908</v>
+        <v>43.093321601651922</v>
       </c>
       <c r="M41">
-        <v>0.11709966206087701</v>
+        <v>0.23075989939714769</v>
       </c>
       <c r="O41" t="s">
         <v>171</v>
@@ -15037,10 +15037,10 @@
         <v>845</v>
       </c>
       <c r="L42">
-        <v>69.816625293163739</v>
+        <v>64.500984166275529</v>
       </c>
       <c r="M42">
-        <v>0.28376623414713642</v>
+        <v>0.18310419861318289</v>
       </c>
       <c r="O42" t="s">
         <v>171</v>
@@ -15105,10 +15105,10 @@
         <v>846</v>
       </c>
       <c r="L43">
-        <v>18.142819719762098</v>
+        <v>65.621250000000003</v>
       </c>
       <c r="M43">
-        <v>0.1094823636689798</v>
+        <v>0.20994057548272141</v>
       </c>
       <c r="O43" t="s">
         <v>171</v>
@@ -15173,10 +15173,10 @@
         <v>847</v>
       </c>
       <c r="L44">
-        <v>33.03376654032008</v>
+        <v>53.321249999999999</v>
       </c>
       <c r="M44">
-        <v>0.21215414282086359</v>
+        <v>0.217403457782638</v>
       </c>
       <c r="O44" t="s">
         <v>171</v>
@@ -15241,10 +15241,10 @@
         <v>848</v>
       </c>
       <c r="L45">
-        <v>85.756886540266791</v>
+        <v>94.912499999999994</v>
       </c>
       <c r="M45">
-        <v>0.1216073056083411</v>
+        <v>0.1647728176804078</v>
       </c>
     </row>
     <row r="46" spans="2:26">
@@ -15276,10 +15276,10 @@
         <v>849</v>
       </c>
       <c r="L46">
-        <v>64.390420974973281</v>
+        <v>18.142819719762098</v>
       </c>
       <c r="M46">
-        <v>0.1453246126306782</v>
+        <v>0.1094823636689798</v>
       </c>
     </row>
     <row r="47" spans="2:26">
@@ -15311,10 +15311,10 @@
         <v>850</v>
       </c>
       <c r="L47">
-        <v>97.590415081529514</v>
+        <v>41.329303307857536</v>
       </c>
       <c r="M47">
-        <v>0.14305547725413789</v>
+        <v>0.22598264647495189</v>
       </c>
     </row>
     <row r="48" spans="2:26">
@@ -15346,10 +15346,10 @@
         <v>851</v>
       </c>
       <c r="L48">
-        <v>51.742157103441926</v>
+        <v>77.661746661491676</v>
       </c>
       <c r="M48">
-        <v>0.1618058465327539</v>
+        <v>0.27059473511745702</v>
       </c>
     </row>
     <row r="49" spans="2:13">
@@ -15381,10 +15381,10 @@
         <v>852</v>
       </c>
       <c r="L49">
-        <v>70.744888329363249</v>
+        <v>68.428690375212113</v>
       </c>
       <c r="M49">
-        <v>0.141633570700541</v>
+        <v>0.2630477290884114</v>
       </c>
     </row>
     <row r="50" spans="2:13">
@@ -15416,10 +15416,10 @@
         <v>853</v>
       </c>
       <c r="L50">
-        <v>72.335118085837053</v>
+        <v>28.571692239731817</v>
       </c>
       <c r="M50">
-        <v>0.11455703572265551</v>
+        <v>0.1050664932730062</v>
       </c>
     </row>
     <row r="51" spans="2:13">
@@ -15451,10 +15451,10 @@
         <v>854</v>
       </c>
       <c r="L51">
-        <v>70.435749494310869</v>
+        <v>44.138666856188586</v>
       </c>
       <c r="M51">
-        <v>0.1562005183996393</v>
+        <v>0.19469721132302881</v>
       </c>
     </row>
     <row r="52" spans="2:13">
@@ -15486,10 +15486,10 @@
         <v>855</v>
       </c>
       <c r="L52">
-        <v>61.508274867797745</v>
+        <v>24.664813931534447</v>
       </c>
       <c r="M52">
-        <v>0.1088337020768549</v>
+        <v>0.2048128116290337</v>
       </c>
     </row>
     <row r="53" spans="2:13">
@@ -15521,10 +15521,10 @@
         <v>856</v>
       </c>
       <c r="L53">
-        <v>60.066641662037199</v>
+        <v>75.61415938768593</v>
       </c>
       <c r="M53">
-        <v>0.1020937020406936</v>
+        <v>0.2659220722327813</v>
       </c>
     </row>
     <row r="54" spans="2:13">
@@ -15661,10 +15661,10 @@
         <v>860</v>
       </c>
       <c r="L57">
-        <v>49.838684423081602</v>
+        <v>61.508274867797745</v>
       </c>
       <c r="M57">
-        <v>0.14946854744676299</v>
+        <v>0.1088337020768549</v>
       </c>
     </row>
     <row r="58" spans="2:13">
@@ -15696,10 +15696,10 @@
         <v>861</v>
       </c>
       <c r="L58">
-        <v>58.749221667912352</v>
+        <v>49.838684423081602</v>
       </c>
       <c r="M58">
-        <v>0.1365826496496805</v>
+        <v>0.14946854744676299</v>
       </c>
     </row>
     <row r="59" spans="2:13">
@@ -15731,10 +15731,10 @@
         <v>862</v>
       </c>
       <c r="L59">
-        <v>139.48999651120684</v>
+        <v>58.749221667912352</v>
       </c>
       <c r="M59">
-        <v>0.2111084974965701</v>
+        <v>0.1365826496496805</v>
       </c>
     </row>
     <row r="60" spans="2:13">
@@ -15766,10 +15766,10 @@
         <v>863</v>
       </c>
       <c r="L60">
-        <v>90.856159298399803</v>
+        <v>139.48999651120684</v>
       </c>
       <c r="M60">
-        <v>0.2231389226548737</v>
+        <v>0.2111084974965701</v>
       </c>
     </row>
     <row r="61" spans="2:13">
@@ -15801,10 +15801,10 @@
         <v>864</v>
       </c>
       <c r="L61">
-        <v>16.378314248967396</v>
+        <v>90.856159298399803</v>
       </c>
       <c r="M61">
-        <v>0.41517302706983161</v>
+        <v>0.2231389226548737</v>
       </c>
     </row>
     <row r="62" spans="2:13">
@@ -15836,10 +15836,10 @@
         <v>865</v>
       </c>
       <c r="L62">
-        <v>33.802699723212591</v>
+        <v>16.378314248967396</v>
       </c>
       <c r="M62">
-        <v>0.13638143225199811</v>
+        <v>0.41517302706983161</v>
       </c>
     </row>
     <row r="63" spans="2:13">
@@ -15871,10 +15871,10 @@
         <v>866</v>
       </c>
       <c r="L63">
-        <v>9.4742229521404262</v>
+        <v>33.802699723212591</v>
       </c>
       <c r="M63">
-        <v>0.10050865170420969</v>
+        <v>0.13638143225199811</v>
       </c>
     </row>
     <row r="64" spans="2:13">
@@ -15906,10 +15906,10 @@
         <v>867</v>
       </c>
       <c r="L64">
-        <v>37.157522303808804</v>
+        <v>9.4742229521404262</v>
       </c>
       <c r="M64">
-        <v>0.1181414908382102</v>
+        <v>0.10050865170420969</v>
       </c>
     </row>
     <row r="65" spans="2:13">
@@ -15941,10 +15941,10 @@
         <v>868</v>
       </c>
       <c r="L65">
-        <v>74.685634238643516</v>
+        <v>37.157522303808804</v>
       </c>
       <c r="M65">
-        <v>0.16397324439306121</v>
+        <v>0.1181414908382102</v>
       </c>
     </row>
     <row r="66" spans="2:13">
@@ -15976,10 +15976,10 @@
         <v>869</v>
       </c>
       <c r="L66">
-        <v>65.363886597795386</v>
+        <v>74.685634238643516</v>
       </c>
       <c r="M66">
-        <v>0.18524831792575611</v>
+        <v>0.16397324439306121</v>
       </c>
     </row>
     <row r="67" spans="2:13">
@@ -16011,10 +16011,10 @@
         <v>870</v>
       </c>
       <c r="L67">
-        <v>89.236077354355544</v>
+        <v>65.363886597795386</v>
       </c>
       <c r="M67">
-        <v>0.18013737352020689</v>
+        <v>0.18524831792575611</v>
       </c>
     </row>
     <row r="68" spans="2:13">
@@ -16046,10 +16046,10 @@
         <v>871</v>
       </c>
       <c r="L68">
-        <v>168.02697637528368</v>
+        <v>89.236077354355544</v>
       </c>
       <c r="M68">
-        <v>0.2004477841597655</v>
+        <v>0.18013737352020689</v>
       </c>
     </row>
     <row r="69" spans="2:13">
@@ -16081,10 +16081,10 @@
         <v>872</v>
       </c>
       <c r="L69">
-        <v>267.08926342442135</v>
+        <v>60.066641662037199</v>
       </c>
       <c r="M69">
-        <v>0.34169476464107468</v>
+        <v>0.1020937020406936</v>
       </c>
     </row>
     <row r="70" spans="2:13">
@@ -16116,10 +16116,10 @@
         <v>873</v>
       </c>
       <c r="L70">
-        <v>87.958990695780145</v>
+        <v>56.623929587037502</v>
       </c>
       <c r="M70">
-        <v>0.39554990302209742</v>
+        <v>0.1265120771138443</v>
       </c>
     </row>
     <row r="71" spans="2:13">
@@ -16151,10 +16151,10 @@
         <v>874</v>
       </c>
       <c r="L71">
-        <v>60.159375226019094</v>
+        <v>82.548665550408757</v>
       </c>
       <c r="M71">
-        <v>0.31828955609396792</v>
+        <v>0.2410109369222953</v>
       </c>
     </row>
     <row r="72" spans="2:13">
@@ -16186,10 +16186,10 @@
         <v>875</v>
       </c>
       <c r="L72">
-        <v>119.24456914853579</v>
+        <v>43.580224589485219</v>
       </c>
       <c r="M72">
-        <v>0.24582986442000679</v>
+        <v>0.27230679726784879</v>
       </c>
     </row>
     <row r="73" spans="2:13">
@@ -16221,10 +16221,10 @@
         <v>876</v>
       </c>
       <c r="L73">
-        <v>101.54193407855358</v>
+        <v>85.756886540266791</v>
       </c>
       <c r="M73">
-        <v>0.20953256764552619</v>
+        <v>0.1216073056083411</v>
       </c>
     </row>
     <row r="74" spans="2:13">
@@ -16256,10 +16256,10 @@
         <v>877</v>
       </c>
       <c r="L74">
-        <v>88.050427811025685</v>
+        <v>64.390420974973281</v>
       </c>
       <c r="M74">
-        <v>0.2672490168135408</v>
+        <v>0.1453246126306782</v>
       </c>
     </row>
     <row r="75" spans="2:13">
@@ -16291,10 +16291,10 @@
         <v>878</v>
       </c>
       <c r="L75">
-        <v>128.72663708382663</v>
+        <v>97.590415081529514</v>
       </c>
       <c r="M75">
-        <v>0.2174697493781044</v>
+        <v>0.14305547725413789</v>
       </c>
     </row>
     <row r="76" spans="2:13">
@@ -16326,10 +16326,10 @@
         <v>879</v>
       </c>
       <c r="L76">
-        <v>142.69145220336142</v>
+        <v>51.742157103441926</v>
       </c>
       <c r="M76">
-        <v>0.2782304615232451</v>
+        <v>0.1618058465327539</v>
       </c>
     </row>
     <row r="77" spans="2:13">
@@ -16361,10 +16361,10 @@
         <v>880</v>
       </c>
       <c r="L77">
-        <v>167.69965469445484</v>
+        <v>70.744888329363249</v>
       </c>
       <c r="M77">
-        <v>0.2261337337218684</v>
+        <v>0.141633570700541</v>
       </c>
     </row>
     <row r="78" spans="2:13">
@@ -16396,10 +16396,10 @@
         <v>881</v>
       </c>
       <c r="L78">
-        <v>97.871188365433483</v>
+        <v>72.335118085837053</v>
       </c>
       <c r="M78">
-        <v>0.26589585773254748</v>
+        <v>0.11455703572265551</v>
       </c>
     </row>
     <row r="79" spans="2:13">
@@ -16431,10 +16431,10 @@
         <v>882</v>
       </c>
       <c r="L79">
-        <v>154.77050499648863</v>
+        <v>70.435749494310869</v>
       </c>
       <c r="M79">
-        <v>0.3498797964055943</v>
+        <v>0.1562005183996393</v>
       </c>
     </row>
     <row r="80" spans="2:13">
@@ -16466,10 +16466,10 @@
         <v>883</v>
       </c>
       <c r="L80">
-        <v>257.73939776854621</v>
+        <v>101.54193407855358</v>
       </c>
       <c r="M80">
-        <v>0.3568296844941039</v>
+        <v>0.20953256764552619</v>
       </c>
     </row>
     <row r="81" spans="2:13">
@@ -16501,10 +16501,10 @@
         <v>884</v>
       </c>
       <c r="L81">
-        <v>66.325002919301426</v>
+        <v>88.050427811025685</v>
       </c>
       <c r="M81">
-        <v>0.2822316523455814</v>
+        <v>0.2672490168135408</v>
       </c>
     </row>
     <row r="82" spans="2:13">
@@ -16536,10 +16536,10 @@
         <v>885</v>
       </c>
       <c r="L82">
-        <v>122.60935049759807</v>
+        <v>128.72663708382663</v>
       </c>
       <c r="M82">
-        <v>0.27691206289185349</v>
+        <v>0.2174697493781044</v>
       </c>
     </row>
     <row r="83" spans="2:13">
@@ -16571,10 +16571,10 @@
         <v>886</v>
       </c>
       <c r="L83">
-        <v>60.54172933348449</v>
+        <v>142.69145220336142</v>
       </c>
       <c r="M83">
-        <v>0.19719230286203379</v>
+        <v>0.2782304615232451</v>
       </c>
     </row>
     <row r="84" spans="2:13">
@@ -16606,10 +16606,10 @@
         <v>887</v>
       </c>
       <c r="L84">
-        <v>142.38964293012813</v>
+        <v>93.821069856018553</v>
       </c>
       <c r="M84">
-        <v>0.1568852567911127</v>
+        <v>0.22627927922505589</v>
       </c>
     </row>
     <row r="85" spans="2:13">
@@ -16641,10 +16641,10 @@
         <v>888</v>
       </c>
       <c r="L85">
-        <v>177.10338506506997</v>
+        <v>116.53803697566987</v>
       </c>
       <c r="M85">
-        <v>0.2530718934117635</v>
+        <v>0.22586236142724461</v>
       </c>
     </row>
     <row r="86" spans="2:13">
@@ -16676,10 +16676,10 @@
         <v>889</v>
       </c>
       <c r="L86">
-        <v>255.24629746088723</v>
+        <v>142.38964293012813</v>
       </c>
       <c r="M86">
-        <v>0.22793105455675111</v>
+        <v>0.1568852567911127</v>
       </c>
     </row>
     <row r="87" spans="2:13">
@@ -16711,10 +16711,10 @@
         <v>890</v>
       </c>
       <c r="L87">
-        <v>131.81606568227213</v>
+        <v>97.871188365433483</v>
       </c>
       <c r="M87">
-        <v>0.31989150505851199</v>
+        <v>0.26589585773254748</v>
       </c>
     </row>
     <row r="88" spans="2:13">
@@ -16746,10 +16746,10 @@
         <v>891</v>
       </c>
       <c r="L88">
-        <v>61.993862801553377</v>
+        <v>122.60935049759807</v>
       </c>
       <c r="M88">
-        <v>0.35099490777634579</v>
+        <v>0.27691206289185349</v>
       </c>
     </row>
     <row r="89" spans="2:13">
@@ -16781,10 +16781,10 @@
         <v>892</v>
       </c>
       <c r="L89">
-        <v>113.54503059044421</v>
+        <v>126.82069394920552</v>
       </c>
       <c r="M89">
-        <v>0.36249703080770018</v>
+        <v>0.26905499196692001</v>
       </c>
     </row>
     <row r="90" spans="2:13">
@@ -16816,10 +16816,10 @@
         <v>893</v>
       </c>
       <c r="L90">
-        <v>105.70151682237133</v>
+        <v>103.54261819537919</v>
       </c>
       <c r="M90">
-        <v>0.30636201190762657</v>
+        <v>0.30967921205323318</v>
       </c>
     </row>
     <row r="91" spans="2:13">
@@ -16851,10 +16851,10 @@
         <v>894</v>
       </c>
       <c r="L91">
-        <v>69.370747472350871</v>
+        <v>112.41415206081683</v>
       </c>
       <c r="M91">
-        <v>0.30954691641769738</v>
+        <v>0.23742411236384961</v>
       </c>
     </row>
     <row r="92" spans="2:13">
@@ -16886,10 +16886,10 @@
         <v>895</v>
       </c>
       <c r="L92">
-        <v>82.033280308745745</v>
+        <v>225.6559648895221</v>
       </c>
       <c r="M92">
-        <v>0.34216346343929699</v>
+        <v>0.21542662811510649</v>
       </c>
     </row>
     <row r="93" spans="2:13">
@@ -16921,10 +16921,10 @@
         <v>896</v>
       </c>
       <c r="L93">
-        <v>75.803513647776157</v>
+        <v>62.059978436207963</v>
       </c>
       <c r="M93">
-        <v>0.26887003228404172</v>
+        <v>0.1091164418969883</v>
       </c>
     </row>
     <row r="94" spans="2:13">
@@ -16956,10 +16956,10 @@
         <v>897</v>
       </c>
       <c r="L94">
-        <v>29.177228298407282</v>
+        <v>38.26626864227196</v>
       </c>
       <c r="M94">
-        <v>0.12968987264819559</v>
+        <v>0.10783606583766529</v>
       </c>
     </row>
     <row r="95" spans="2:13">
@@ -16991,10 +16991,10 @@
         <v>898</v>
       </c>
       <c r="L95">
-        <v>51.627484821987814</v>
+        <v>60.992148128410847</v>
       </c>
       <c r="M95">
-        <v>0.30504302621453577</v>
+        <v>0.22101211408164931</v>
       </c>
     </row>
     <row r="96" spans="2:13">
@@ -17026,10 +17026,10 @@
         <v>899</v>
       </c>
       <c r="L96">
-        <v>51.352856098196355</v>
+        <v>61.332365360387051</v>
       </c>
       <c r="M96">
-        <v>0.21916033990843409</v>
+        <v>0.1047273957777045</v>
       </c>
     </row>
     <row r="97" spans="2:13">
@@ -17061,10 +17061,10 @@
         <v>900</v>
       </c>
       <c r="L97">
-        <v>268.99810358926845</v>
+        <v>45.98828906790623</v>
       </c>
       <c r="M97">
-        <v>0.42238375021817848</v>
+        <v>0.13350668327998419</v>
       </c>
     </row>
     <row r="98" spans="2:13">
@@ -17096,10 +17096,10 @@
         <v>901</v>
       </c>
       <c r="L98">
-        <v>175.34139382511415</v>
+        <v>87.706339968779687</v>
       </c>
       <c r="M98">
-        <v>0.41021397562536088</v>
+        <v>0.116467954325171</v>
       </c>
     </row>
     <row r="99" spans="2:13">
@@ -17131,10 +17131,10 @@
         <v>902</v>
       </c>
       <c r="L99">
-        <v>169.00576471280846</v>
+        <v>82.09145616123692</v>
       </c>
       <c r="M99">
-        <v>0.45009147084629531</v>
+        <v>0.18881971192587471</v>
       </c>
     </row>
     <row r="100" spans="2:13">
@@ -17166,10 +17166,10 @@
         <v>903</v>
       </c>
       <c r="L100">
-        <v>10.385475508924948</v>
+        <v>112.04245507343492</v>
       </c>
       <c r="M100">
-        <v>0.24520539437298841</v>
+        <v>0.14670363792414659</v>
       </c>
     </row>
     <row r="101" spans="2:13">
@@ -17201,10 +17201,10 @@
         <v>904</v>
       </c>
       <c r="L101">
-        <v>33.795085119651624</v>
+        <v>90.339447767234844</v>
       </c>
       <c r="M101">
-        <v>0.28248710962945328</v>
+        <v>0.13542788605013159</v>
       </c>
     </row>
     <row r="102" spans="2:13">
@@ -17236,10 +17236,10 @@
         <v>905</v>
       </c>
       <c r="L102">
-        <v>51.909188820891352</v>
+        <v>74.036055832907422</v>
       </c>
       <c r="M102">
-        <v>0.25883945370527411</v>
+        <v>0.16286067210288219</v>
       </c>
     </row>
     <row r="103" spans="2:13">
@@ -17271,10 +17271,10 @@
         <v>906</v>
       </c>
       <c r="L103">
-        <v>35.156972742938514</v>
+        <v>80.672619123124335</v>
       </c>
       <c r="M103">
-        <v>0.1455286223785075</v>
+        <v>0.20164661247125931</v>
       </c>
     </row>
     <row r="104" spans="2:13">
@@ -17306,10 +17306,10 @@
         <v>907</v>
       </c>
       <c r="L104">
-        <v>51.50609753452504</v>
+        <v>131.77159630662092</v>
       </c>
       <c r="M104">
-        <v>0.16076137643720079</v>
+        <v>0.27102088308517108</v>
       </c>
     </row>
     <row r="105" spans="2:13">
@@ -17621,10 +17621,10 @@
         <v>916</v>
       </c>
       <c r="L113">
-        <v>62.059978436207963</v>
+        <v>230.47670641898489</v>
       </c>
       <c r="M113">
-        <v>0.1091164418969883</v>
+        <v>0.4245744701917743</v>
       </c>
     </row>
     <row r="114" spans="2:13">
@@ -17656,10 +17656,10 @@
         <v>917</v>
       </c>
       <c r="L114">
-        <v>38.26626864227196</v>
+        <v>142.66303664252501</v>
       </c>
       <c r="M114">
-        <v>0.10783606583766529</v>
+        <v>0.38422486535033262</v>
       </c>
     </row>
     <row r="115" spans="2:13">
@@ -17691,10 +17691,10 @@
         <v>918</v>
       </c>
       <c r="L115">
-        <v>60.992148128410847</v>
+        <v>141.35321604259073</v>
       </c>
       <c r="M115">
-        <v>0.22101211408164931</v>
+        <v>0.46142061586686323</v>
       </c>
     </row>
     <row r="116" spans="2:13">
@@ -17726,10 +17726,10 @@
         <v>919</v>
       </c>
       <c r="L116">
-        <v>61.332365360387051</v>
+        <v>105.89850127788448</v>
       </c>
       <c r="M116">
-        <v>0.1047273957777045</v>
+        <v>0.43353472506368917</v>
       </c>
     </row>
     <row r="117" spans="2:13">
@@ -17761,10 +17761,10 @@
         <v>920</v>
       </c>
       <c r="L117">
-        <v>45.98828906790623</v>
+        <v>154.77050499648863</v>
       </c>
       <c r="M117">
-        <v>0.13350668327998419</v>
+        <v>0.3498797964055943</v>
       </c>
     </row>
     <row r="118" spans="2:13">
@@ -17796,10 +17796,10 @@
         <v>921</v>
       </c>
       <c r="L118">
-        <v>87.706339968779687</v>
+        <v>95.858861878747391</v>
       </c>
       <c r="M118">
-        <v>0.116467954325171</v>
+        <v>0.38267718196403011</v>
       </c>
     </row>
     <row r="119" spans="2:13">
@@ -17831,10 +17831,10 @@
         <v>922</v>
       </c>
       <c r="L119">
-        <v>82.09145616123692</v>
+        <v>220.62449912440621</v>
       </c>
       <c r="M119">
-        <v>0.18881971192587471</v>
+        <v>0.35895555373620108</v>
       </c>
     </row>
     <row r="120" spans="2:13">
@@ -17866,10 +17866,10 @@
         <v>923</v>
       </c>
       <c r="L120">
-        <v>112.04245507343492</v>
+        <v>168.02697637528368</v>
       </c>
       <c r="M120">
-        <v>0.14670363792414659</v>
+        <v>0.2004477841597655</v>
       </c>
     </row>
     <row r="121" spans="2:13">
@@ -17901,10 +17901,10 @@
         <v>924</v>
       </c>
       <c r="L121">
-        <v>90.339447767234844</v>
+        <v>69.916785281316834</v>
       </c>
       <c r="M121">
-        <v>0.13542788605013159</v>
+        <v>0.30331171615911018</v>
       </c>
     </row>
     <row r="122" spans="2:13">
@@ -17936,10 +17936,10 @@
         <v>925</v>
       </c>
       <c r="L122">
-        <v>74.036055832907422</v>
+        <v>174.51103915086307</v>
       </c>
       <c r="M122">
-        <v>0.16286067210288219</v>
+        <v>0.36375037143637229</v>
       </c>
     </row>
     <row r="123" spans="2:13">
@@ -17971,10 +17971,10 @@
         <v>926</v>
       </c>
       <c r="L123">
-        <v>131.77159630662092</v>
+        <v>60.159375226019094</v>
       </c>
       <c r="M123">
-        <v>0.27102088308517108</v>
+        <v>0.31828955609396792</v>
       </c>
     </row>
     <row r="124" spans="2:13">
@@ -18006,10 +18006,10 @@
         <v>927</v>
       </c>
       <c r="L124">
-        <v>87.718817377918285</v>
+        <v>119.24456914853579</v>
       </c>
       <c r="M124">
-        <v>0.21038320908484101</v>
+        <v>0.24582986442000679</v>
       </c>
     </row>
   </sheetData>
@@ -18018,7 +18018,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFB40048-AC9C-4368-8750-0A1F817E024D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CC9A66A-7441-45F4-871B-0F33069D4555}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_CHN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_CHN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D5B69633-C6A0-4435-916F-A62E64EE98C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A022711-56C8-4E9B-B131-2BACEEB85660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8001,7 +8001,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50AF16E3-1710-435F-8D16-96112F86222D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3BFD382-6AEA-4A13-9E49-CF2AE064BAC2}">
   <dimension ref="B9:M146"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12814,7 +12814,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEABED34-9C4D-4891-A9E4-FE6250814ED0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18C474B3-D42F-4727-909B-4FCAEEF059AD}">
   <dimension ref="B9:Z124"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -18018,7 +18018,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CC9A66A-7441-45F4-871B-0F33069D4555}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28086F5E-4BD6-4EB0-A2A2-52DCD188D92D}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_CHN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_CHN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A022711-56C8-4E9B-B131-2BACEEB85660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{831759D6-4F7E-42C0-B375-FEB2B7FC7F52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8001,7 +8001,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3BFD382-6AEA-4A13-9E49-CF2AE064BAC2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B76C81CA-B903-4111-8637-A73CC402A159}">
   <dimension ref="B9:M146"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12814,7 +12814,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18C474B3-D42F-4727-909B-4FCAEEF059AD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A84FB5A2-02E5-4B73-9692-A1A85C00F762}">
   <dimension ref="B9:Z124"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -18018,7 +18018,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28086F5E-4BD6-4EB0-A2A2-52DCD188D92D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8EDAA3A-D671-4C92-9FE6-D246E164EE11}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_CHN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_CHN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{831759D6-4F7E-42C0-B375-FEB2B7FC7F52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D0B219A1-25A8-4FBD-A8AB-3DC752F26DDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8001,7 +8001,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B76C81CA-B903-4111-8637-A73CC402A159}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A80BCF1-2868-42C6-95FF-655EC6A84746}">
   <dimension ref="B9:M146"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12814,7 +12814,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A84FB5A2-02E5-4B73-9692-A1A85C00F762}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FD9BD2C-390B-4F2F-B1C7-324952C310DD}">
   <dimension ref="B9:Z124"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -18018,7 +18018,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8EDAA3A-D671-4C92-9FE6-D246E164EE11}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87C40815-254D-48F7-A9A5-35887A96A901}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_CHN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_CHN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D0B219A1-25A8-4FBD-A8AB-3DC752F26DDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{212B6F8B-86D0-4759-99F9-C95F84326DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8001,7 +8001,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A80BCF1-2868-42C6-95FF-655EC6A84746}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74FE8B61-5493-413D-89F6-C683DBD15A69}">
   <dimension ref="B9:M146"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12814,7 +12814,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FD9BD2C-390B-4F2F-B1C7-324952C310DD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A0B75CC-A24D-435F-A2B0-D4429A870926}">
   <dimension ref="B9:Z124"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -18018,7 +18018,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87C40815-254D-48F7-A9A5-35887A96A901}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{907D1AEA-E8DA-4A8F-877A-7C4F3B6A13B0}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_CHN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_CHN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{212B6F8B-86D0-4759-99F9-C95F84326DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1652876D-8FFE-423F-B491-E14FFF860AAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8001,7 +8001,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74FE8B61-5493-413D-89F6-C683DBD15A69}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CDBFD6C-6110-4C08-A616-55E6A1FCE51F}">
   <dimension ref="B9:M146"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12814,7 +12814,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A0B75CC-A24D-435F-A2B0-D4429A870926}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C523C-2049-4A19-B35A-BC4B028B0FAB}">
   <dimension ref="B9:Z124"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -18018,7 +18018,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{907D1AEA-E8DA-4A8F-877A-7C4F3B6A13B0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D21D5E5-D87E-4589-8A5E-B2F600205637}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_CHN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_CHN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1652876D-8FFE-423F-B491-E14FFF860AAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC4B5D12-5E30-4FFF-AA49-08B0AF510921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8001,7 +8001,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CDBFD6C-6110-4C08-A616-55E6A1FCE51F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D94B013-0C20-4F1D-9E18-5CB9608BD1E1}">
   <dimension ref="B9:M146"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12814,7 +12814,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C523C-2049-4A19-B35A-BC4B028B0FAB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C5D8651-76CD-4435-8B7C-0EAB93467884}">
   <dimension ref="B9:Z124"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -18018,7 +18018,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D21D5E5-D87E-4589-8A5E-B2F600205637}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4606B4CD-B721-43C8-BEBA-6FC0DEC3DDC8}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_CHN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_CHN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC4B5D12-5E30-4FFF-AA49-08B0AF510921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5BC1782D-D7E7-4F60-8173-E975FA8418AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8001,7 +8001,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D94B013-0C20-4F1D-9E18-5CB9608BD1E1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A36C151-F787-40CE-BCF8-CB95BF650C10}">
   <dimension ref="B9:M146"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12814,7 +12814,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C5D8651-76CD-4435-8B7C-0EAB93467884}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F33FFD4-0C49-4DD2-86FB-2C4B55098DC9}">
   <dimension ref="B9:Z124"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -18018,7 +18018,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4606B4CD-B721-43C8-BEBA-6FC0DEC3DDC8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60D03314-6A9D-43DB-8380-94B2AAB9E1C6}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
